--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E157"/>
+  <dimension ref="A1:E158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2062,17 +2062,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2087,17 +2087,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:54:00 +0900</t>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2162,17 +2162,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2187,17 +2187,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2212,17 +2212,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2237,22 +2237,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 06:02:00 +0900</t>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>072.jpg</t>
         </is>
       </c>
     </row>
@@ -2262,22 +2262,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 15:02:00 +0900</t>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>073.jpg</t>
+          <t>실패</t>
         </is>
       </c>
     </row>
@@ -2287,17 +2287,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 11:30:00 +0900</t>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2312,17 +2312,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 06:00:00 +0900</t>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2337,17 +2337,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>“한·일 함정 분야 경쟁 가능성”</t>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2387,17 +2387,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2437,17 +2437,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2487,17 +2487,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2512,17 +2512,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2537,17 +2537,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2562,17 +2562,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2587,17 +2587,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>087.jpg</t>
         </is>
       </c>
     </row>
@@ -2637,22 +2637,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>088.jpg</t>
+          <t>실패</t>
         </is>
       </c>
     </row>
@@ -2662,17 +2662,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2687,17 +2687,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2575581</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -2812,22 +2812,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>095.jpg</t>
         </is>
       </c>
     </row>
@@ -2837,17 +2837,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>http://amenews.kr/news/view.php?idx=66331</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>097.jpg</t>
+          <t>실패</t>
         </is>
       </c>
     </row>
@@ -2887,17 +2887,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -2912,17 +2912,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -2937,17 +2937,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -2987,22 +2987,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>102.jpg</t>
         </is>
       </c>
     </row>
@@ -3012,22 +3012,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2573034</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>103.jpg</t>
+          <t>실패</t>
         </is>
       </c>
     </row>
@@ -3037,17 +3037,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3062,22 +3062,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>105.jpg</t>
         </is>
       </c>
     </row>
@@ -3087,22 +3087,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>106.jpg</t>
+          <t>실패</t>
         </is>
       </c>
     </row>
@@ -3112,17 +3112,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260401154708093</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3162,17 +3162,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
+          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2571395</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3187,17 +3187,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
+          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
+          <t>https://www.etoday.co.kr/news/view/2571395</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
+          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3237,17 +3237,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
+          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
+          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3262,17 +3262,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
+          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3287,17 +3287,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
+          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3312,17 +3312,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260326500334</t>
+          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
+          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3337,22 +3337,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
+          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
+          <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
+          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>116.jpg</t>
         </is>
       </c>
     </row>
@@ -3362,22 +3362,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
+          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>117.jpg</t>
+          <t>실패</t>
         </is>
       </c>
     </row>
@@ -3387,17 +3387,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
+          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3412,17 +3412,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
+          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
+          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3437,22 +3437,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
+          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
+          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
+          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>120.jpg</t>
         </is>
       </c>
     </row>
@@ -3462,17 +3462,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
+          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
+          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3487,22 +3487,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
+          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
+          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
+          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>122.jpg</t>
+          <t>실패</t>
         </is>
       </c>
     </row>
@@ -3512,17 +3512,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
+          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
+          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3537,17 +3537,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
+          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
+          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3562,17 +3562,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
+          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -3587,17 +3587,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
+          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
+          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
+          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -3612,22 +3612,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
+          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
+          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>127.jpg</t>
         </is>
       </c>
     </row>
@@ -3637,22 +3637,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
+          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260310153628801</t>
+          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
+          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>128.jpg</t>
+          <t>실패</t>
         </is>
       </c>
     </row>
@@ -3662,17 +3662,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
+          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
+          <t>https://www.ajunews.com/view/20260310153628801</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
+          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -3687,17 +3687,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
+          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
+          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -3712,17 +3712,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
+          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
+          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
+          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260227150934536</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -3812,17 +3812,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
+          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
+          <t>https://www.ajunews.com/view/20260227150934536</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -3837,17 +3837,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
+          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
+          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
+          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -3862,22 +3862,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
+          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
+          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>137.jpg</t>
         </is>
       </c>
     </row>
@@ -3887,22 +3887,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
+          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>138.jpg</t>
+          <t>실패</t>
         </is>
       </c>
     </row>
@@ -3912,17 +3912,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
+          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
+          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
+          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -3937,17 +3937,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
+          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
+          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -3962,17 +3962,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
+          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
+          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -3987,17 +3987,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
+          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
+          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
+          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4012,17 +4012,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
+          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
+          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
+          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
+          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
+          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4062,17 +4062,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
+          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
+          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4087,17 +4087,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
+          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
+          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4112,17 +4112,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
+          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
+          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4137,17 +4137,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>'60조 잠수함' 끌어올 현대차 떴다… 韓-獨 벼랑끝 '국가 대항전'</t>
+          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003499499?sid=101</t>
+          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 05:00:00 +0900</t>
+          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4162,17 +4162,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>[로드픽] 핵잠 논의, 기술 아닌 '국가 통제의 문제'로 옮겨갔다</t>
+          <t>'60조 잠수함' 끌어올 현대차 떴다… 韓-獨 벼랑끝 '국가 대항전'</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>http://www.newsroad.co.kr/news/articleView.html?idxno=53361</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003499499?sid=101</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 23:06:00 +0900</t>
+          <t>Wed, 28 Jan 2026 05:00:00 +0900</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4187,17 +4187,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>[단독]방사청, 방산기업들에 ‘생성형 AI 해킹’ 주의 공문 발송</t>
+          <t>[로드픽] 핵잠 논의, 기술 아닌 '국가 통제의 문제'로 옮겨갔다</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002591811?sid=101</t>
+          <t>http://www.newsroad.co.kr/news/articleView.html?idxno=53361</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 17:06:00 +0900</t>
+          <t>Tue, 27 Jan 2026 23:06:00 +0900</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>외교 경쟁 넘은 방산 수주전… 韓 '민관협력' 패키지로 차별화</t>
+          <t>[단독]방사청, 방산기업들에 ‘생성형 AI 해킹’ 주의 공문 발송</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260127010012312</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002591811?sid=101</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 18:06:00 +0900</t>
+          <t>Tue, 27 Jan 2026 17:06:00 +0900</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4237,17 +4237,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>&amp;quot;무기입찰인줄 알았는데&amp;quot;···60조 캐나다 잠수함 '국가 산업 총력전'</t>
+          <t>외교 경쟁 넘은 방산 수주전… 韓 '민관협력' 패키지로 차별화</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2384464</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260127010012312</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Thu, 22 Jan 2026 08:00:00 +0900</t>
+          <t>Mon, 26 Jan 2026 18:06:00 +0900</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4262,17 +4262,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>전북대 학생들, 무기체계 자립도 평가 입체적 지표 제시 '학계 주목'</t>
+          <t>&amp;quot;무기입찰인줄 알았는데&amp;quot;···60조 캐나다 잠수함 '국가 산업 총력전'</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260119082719729</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2384464</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:32:00 +0900</t>
+          <t>Thu, 22 Jan 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4287,17 +4287,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>전북대 학생들, '무기체계 자립도' 새로운 지표 제시 '주목'</t>
+          <t>전북대 학생들, 무기체계 자립도 평가 입체적 지표 제시 '학계 주목'</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542654</t>
+          <t>https://www.ajunews.com/view/20260119082719729</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 14:52:00 +0900</t>
+          <t>Mon, 19 Jan 2026 08:32:00 +0900</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4312,17 +4312,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>전북대 학생들 ‘무기체계 자립도’ 새 지표 제시 눈길</t>
+          <t>전북대 학생들, '무기체계 자립도' 새로운 지표 제시 '주목'</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/022/0004098361?sid=102</t>
+          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542654</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 06:35:00 +0900</t>
+          <t>Sun, 18 Jan 2026 14:52:00 +0900</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4337,22 +4337,47 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
+          <t>전북대 학생들 ‘무기체계 자립도’ 새 지표 제시 눈길</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/022/0004098361?sid=102</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 06:35:00 +0900</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>156.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
           <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D158" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>156.jpg</t>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>157.jpg</t>
         </is>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E158"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>이미지저장</t>
+          <t>이미지보기</t>
         </is>
       </c>
     </row>
@@ -475,10 +475,9 @@
           <t>Tue, 19 May 2026 14:01:00 +0900</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>001.jpg</t>
-        </is>
+      <c r="E2">
+        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -500,10 +499,9 @@
           <t>Sun, 17 May 2026 22:30:00 +0900</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>002.jpg</t>
-        </is>
+      <c r="E3">
+        <f>IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -525,10 +523,9 @@
           <t>Sun, 17 May 2026 07:56:00 +0900</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>003.jpg</t>
-        </is>
+      <c r="E4">
+        <f>IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -550,10 +547,9 @@
           <t>Fri, 15 May 2026 16:20:00 +0900</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>004.jpg</t>
-        </is>
+      <c r="E5">
+        <f>IMAGE("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -575,10 +571,9 @@
           <t>Fri, 15 May 2026 14:38:00 +0900</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>005.jpg</t>
-        </is>
+      <c r="E6">
+        <f>IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -600,10 +595,9 @@
           <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>006.jpg</t>
-        </is>
+      <c r="E7">
+        <f>IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -625,10 +619,9 @@
           <t>Fri, 15 May 2026 12:56:00 +0900</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>007.jpg</t>
-        </is>
+      <c r="E8">
+        <f>IMAGE("https://www.jeonmae.co.kr/news/thumbnail/202605/1256767_976877_187_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -650,10 +643,9 @@
           <t>Fri, 15 May 2026 12:01:00 +0900</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>008.jpg</t>
-        </is>
+      <c r="E9">
+        <f>IMAGE("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -675,10 +667,9 @@
           <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>009.jpg</t>
-        </is>
+      <c r="E10">
+        <f>IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -700,10 +691,9 @@
           <t>Fri, 15 May 2026 11:18:00 +0900</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>010.jpg</t>
-        </is>
+      <c r="E11">
+        <f>IMAGE("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -725,10 +715,9 @@
           <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>011.jpg</t>
-        </is>
+      <c r="E12">
+        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -750,10 +739,9 @@
           <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>012.jpg</t>
-        </is>
+      <c r="E13">
+        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -762,23 +750,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>추추선대위' 후보직속 13개 특별위 가동...&amp;quot;핵심 공약 직접 챙긴다&amp;quot;</t>
+          <t>[뉴공 아카이브]강은호 전 방위사업청장·전북대 첨단방위산업학과 교수...</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.newspim.com/news/view/20260501000131</t>
+          <t>http://www.ddanzi.com/879846987</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fri, 01 May 2026 16:37:00 +0900</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>013.jpg</t>
-        </is>
+          <t>Mon, 27 Apr 2026 11:42:00 +0900</t>
+        </is>
+      </c>
+      <c r="E14">
+        <f>IMAGE("https://www.ddanzi.com/./files/attach/images/1176663/987/846/879/e3d94bdf26e8a3de4247826410f25b3e.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -787,23 +774,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>전북발전연합회 &amp;quot;군산·김제·부안을, 강은호 전략공천&amp;quot; 촉구</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004141994?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:23:00 +0900</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>014.jpg</t>
-        </is>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+        </is>
+      </c>
+      <c r="E15">
+        <f>IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -812,23 +798,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[뉴공 아카이브]강은호 전 방위사업청장·전북대 첨단방위산업학과 교수...</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>http://www.ddanzi.com/879846987</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 11:42:00 +0900</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>015.jpg</t>
-        </is>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E16">
+        <f>IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -837,23 +822,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>016.jpg</t>
-        </is>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+        </is>
+      </c>
+      <c r="E17">
+        <f>IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -862,23 +846,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>017.jpg</t>
-        </is>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E18">
+        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -887,23 +870,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>018.jpg</t>
-        </is>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+        </is>
+      </c>
+      <c r="E19">
+        <f>IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -912,23 +894,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>[뉴공 아카이브]강은호 전 방위사업청장·전북대 첨단방위산업학과 교수...</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>http://www.ddanzi.com/879301743</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>019.jpg</t>
-        </is>
+          <t>Mon, 20 Apr 2026 11:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E20">
+        <f>IMAGE("https://www.ddanzi.com/./files/attach/images/1176663/743/301/879/1c5e3c5a58fddbcdf694eb20a336a880.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -937,23 +918,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>020.jpg</t>
-        </is>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E21">
+        <f>IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -962,23 +942,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>021.jpg</t>
-        </is>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+        </is>
+      </c>
+      <c r="E22">
+        <f>IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -987,23 +966,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[뉴공 아카이브]강은호 전 방위사업청장·전북대 첨단방위산업학과 교수...</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>http://www.ddanzi.com/879301743</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 11:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>022.jpg</t>
-        </is>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+        </is>
+      </c>
+      <c r="E23">
+        <f>IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1012,23 +990,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>023.jpg</t>
-        </is>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+        </is>
+      </c>
+      <c r="E24">
+        <f>IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1037,23 +1014,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>국회의원 2곳도 재보궐…'미니 총선'</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://jtv.co.kr/2021/?c=3/10&amp;uid=2201864</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>024.jpg</t>
-        </is>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+        </is>
+      </c>
+      <c r="E25">
+        <f>IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1062,23 +1038,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>025.jpg</t>
-        </is>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E26">
+        <f>IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1087,23 +1062,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>보선 열리면 결국 전략공천…'군산·김제·부안을'에 강은호 하마평</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008895953?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 11:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>026.jpg</t>
-        </is>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E27">
+        <f>IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1112,23 +1086,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>강은호 전 방위사업청장, '군산·김제·부안을' 전략공천 급부상</t>
+          <t>[뉴공 아카이브]강은호 전 방위사업청장·전북대 첨단방위산업학과 교수...</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026041700362431125</t>
+          <t>http://www.ddanzi.com/878494144</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 09:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>027.jpg</t>
-        </is>
+          <t>Fri, 10 Apr 2026 12:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E28">
+        <f>IMAGE("https://www.ddanzi.com/./files/attach/images/1176663/144/494/878/b2ada78cb3b317b58717884e9ae1e6e1.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1137,23 +1110,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>028.jpg</t>
-        </is>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E29">
+        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1162,23 +1134,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>[뉴공 아카이브]강은호 전 방위사업청장·전북대 첨단방위산업학과 교수...</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>http://www.ddanzi.com/877818479</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>029.jpg</t>
-        </is>
+          <t>Fri, 03 Apr 2026 12:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E30">
+        <f>IMAGE("https://www.ddanzi.com/./files/attach/images/1176663/479/818/877/c16820231793e69cba35df2fa3e117c4.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1187,23 +1158,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E31">
+        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1212,23 +1182,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>031.jpg</t>
-        </is>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E32">
+        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1237,23 +1206,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>032.jpg</t>
-        </is>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E33">
+        <f>IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -1262,23 +1230,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>033.jpg</t>
-        </is>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E34">
+        <f>IMAGE("https://static.naeil.com/img/rect_logo.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -1287,23 +1254,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[뉴공 아카이브]강은호 전 방위사업청장·전북대 첨단방위산업학과 교수...</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>http://www.ddanzi.com/878494144</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 12:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>034.jpg</t>
-        </is>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+        </is>
+      </c>
+      <c r="E35">
+        <f>IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -1312,23 +1278,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>035.jpg</t>
-        </is>
+          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
+        </is>
+      </c>
+      <c r="E36">
+        <f>IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -1337,23 +1302,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[뉴공 아카이브]강은호 전 방위사업청장·전북대 첨단방위산업학과 교수...</t>
+          <t>“AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>http://www.ddanzi.com/877818479</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 12:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>036.jpg</t>
-        </is>
+          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
+        </is>
+      </c>
+      <c r="E37">
+        <f>IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -1362,23 +1326,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>037.jpg</t>
-        </is>
+          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E38">
+        <f>IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -1387,23 +1350,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>전북대 71억 규모 '첨단인재양성 부트캠프 사업' 선정</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>http://www.veritas-a.com/news/articleView.html?idxno=600409</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>038.jpg</t>
-        </is>
+          <t>Wed, 04 Mar 2026 14:34:00 +0900</t>
+        </is>
+      </c>
+      <c r="E39">
+        <f>IMAGE("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -1412,23 +1374,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>전북대, 첨단산업 인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001010129?sid=102</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>039.jpg</t>
-        </is>
+          <t>Wed, 04 Mar 2026 12:37:00 +0900</t>
+        </is>
+      </c>
+      <c r="E40">
+        <f>IMAGE("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -1437,23 +1398,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>040.jpg</t>
-        </is>
+          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E41">
+        <f>IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -1462,23 +1422,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>041.jpg</t>
-        </is>
+          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E42">
+        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -1487,23 +1446,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
+          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>042.jpg</t>
-        </is>
+          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E43">
+        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -1512,23 +1470,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>“AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
+          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>043.jpg</t>
-        </is>
+          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E44">
+        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -1537,23 +1494,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
+          <t>전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>044.jpg</t>
-        </is>
+          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E45">
+        <f>IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -1562,23 +1518,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>전북대 71억 규모 '첨단인재양성 부트캠프 사업' 선정</t>
+          <t>전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>http://www.veritas-a.com/news/articleView.html?idxno=600409</t>
+          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 14:34:00 +0900</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>045.jpg</t>
-        </is>
+          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
+        </is>
+      </c>
+      <c r="E46">
+        <f>IMAGE("https://static.naeil.com/img/rect_logo.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -1587,23 +1542,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>전북대, 첨단산업 인재양성 부트캠프 사업 선정</t>
+          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001010129?sid=102</t>
+          <t>http://www.kyosu.net/news/articleView.html?idxno=155230</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 12:37:00 +0900</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>046.jpg</t>
-        </is>
+          <t>Thu, 15 Jan 2026 21:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E47">
+        <f>IMAGE("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png")</f>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -1612,23 +1566,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
+          <t>전북대, 방산 AI 유니콘 '쉴드 AI'와 협력 추진</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=432185</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>047.jpg</t>
-        </is>
+          <t>Thu, 15 Jan 2026 20:08:00 +0900</t>
+        </is>
+      </c>
+      <c r="E48">
+        <f>IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -1637,23 +1590,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
+          <t>전북대, 글로벌 방산 AI 유니콘 쉴드 AI와 피지컬 AI 협력 추진</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
+          <t>https://www.betanews.net/article/view/beta202601150086</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>048.jpg</t>
-        </is>
+          <t>Thu, 15 Jan 2026 19:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E49">
+        <f>IMAGE("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -1662,23 +1614,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 체계 구축한다</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
+          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542514</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>049.jpg</t>
-        </is>
+          <t>Thu, 15 Jan 2026 18:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E50">
+        <f>IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -1687,23 +1638,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진...피지컬...</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
+          <t>http://www.jbsori.com/news/articleView.html?idxno=16762</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>050.jpg</t>
-        </is>
+          <t>Thu, 15 Jan 2026 15:50:00 +0900</t>
+        </is>
+      </c>
+      <c r="E51">
+        <f>IMAGE("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -1712,23 +1662,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
+          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>051.jpg</t>
-        </is>
+          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
+        </is>
+      </c>
+      <c r="E52">
+        <f>IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png")</f>
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -1737,23 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
+          <t>https://www.gukjenews.com/news/articleView.html?idxno=3481565</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>052.jpg</t>
-        </is>
+          <t>Thu, 15 Jan 2026 14:06:00 +0900</t>
+        </is>
+      </c>
+      <c r="E53">
+        <f>IMAGE("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -1767,18 +1715,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>http://www.kyosu.net/news/articleView.html?idxno=155230</t>
+          <t>http://www.veritas-a.com/news/articleView.html?idxno=594342</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 21:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>053.jpg</t>
-        </is>
+          <t>Thu, 15 Jan 2026 12:22:00 +0900</t>
+        </is>
+      </c>
+      <c r="E54">
+        <f>IMAGE("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -1787,23 +1734,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>전북대, 방산 AI 유니콘 '쉴드 AI'와 협력 추진</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=432185</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003390311?sid=102</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 20:08:00 +0900</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>054.jpg</t>
-        </is>
+          <t>Thu, 15 Jan 2026 12:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E55">
+        <f>IMAGE("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -1812,23 +1758,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>전북대, 글로벌 방산 AI 유니콘 쉴드 AI와 피지컬 AI 협력 추진</t>
+          <t>전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202601150086</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 19:26:00 +0900</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>055.jpg</t>
-        </is>
+          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
+        </is>
+      </c>
+      <c r="E56">
+        <f>IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -1837,23 +1782,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 체계 구축한다</t>
+          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542514</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=588811</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 18:24:00 +0900</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>056.jpg</t>
-        </is>
+          <t>Thu, 15 Jan 2026 10:36:00 +0900</t>
+        </is>
+      </c>
+      <c r="E57">
+        <f>IMAGE("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -1862,23 +1806,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진...피지컬...</t>
+          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>http://www.jbsori.com/news/articleView.html?idxno=16762</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:50:00 +0900</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>057.jpg</t>
-        </is>
+          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E58">
+        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -1887,23 +1830,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>058.jpg</t>
-        </is>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E59">
+        <f>IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -1912,23 +1854,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.gukjenews.com/news/articleView.html?idxno=3481565</t>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 14:06:00 +0900</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>059.jpg</t>
-        </is>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E60">
+        <f>IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -1937,23 +1878,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>http://www.veritas-a.com/news/articleView.html?idxno=594342</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:22:00 +0900</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>060.jpg</t>
-        </is>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E61">
+        <f>IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -1962,23 +1902,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003390311?sid=102</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>061.jpg</t>
-        </is>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E62">
+        <f>IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556")</f>
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -1987,23 +1926,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>062.jpg</t>
-        </is>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E63">
+        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -2012,23 +1950,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력</t>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=588811</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:36:00 +0900</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>063.jpg</t>
-        </is>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E64">
+        <f>IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -2037,23 +1974,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>064.jpg</t>
-        </is>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E65">
+        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -2062,23 +1998,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 10:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>065.jpg</t>
-        </is>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+        </is>
+      </c>
+      <c r="E66">
+        <f>IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -2087,22 +2022,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>066.jpg</t>
+          <t>이미지 없음</t>
         </is>
       </c>
     </row>
@@ -2112,23 +2047,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>067.jpg</t>
-        </is>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E68">
+        <f>IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -2137,23 +2071,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>068.jpg</t>
-        </is>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E69">
+        <f>IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -2162,23 +2095,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:54:00 +0900</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>069.jpg</t>
-        </is>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E70">
+        <f>IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -2187,23 +2119,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>070.jpg</t>
-        </is>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E71">
+        <f>IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -2212,23 +2143,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 07:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>071.jpg</t>
-        </is>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+        </is>
+      </c>
+      <c r="E72">
+        <f>IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -2237,23 +2167,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 16:58:00 +0900</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>072.jpg</t>
-        </is>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+        </is>
+      </c>
+      <c r="E73">
+        <f>IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -2262,23 +2191,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E74">
+        <f>IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -2287,23 +2215,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 15:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>074.jpg</t>
-        </is>
+          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+        </is>
+      </c>
+      <c r="E75">
+        <f>IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="76">
@@ -2312,23 +2239,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 11:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>075.jpg</t>
-        </is>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E76">
+        <f>IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -2337,23 +2263,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 06:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>076.jpg</t>
-        </is>
+          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E77">
+        <f>IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -2362,23 +2287,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>077.jpg</t>
-        </is>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E78">
+        <f>IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -2387,23 +2311,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>“한·일 함정 분야 경쟁 가능성”</t>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>078.jpg</t>
-        </is>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E79">
+        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -2412,23 +2335,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>079.jpg</t>
-        </is>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E80">
+        <f>IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -2437,23 +2359,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>080.jpg</t>
-        </is>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E81">
+        <f>IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="82">
@@ -2462,22 +2383,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>081.jpg</t>
+          <t>이미지 없음</t>
         </is>
       </c>
     </row>
@@ -2487,23 +2408,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>082.jpg</t>
-        </is>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E83">
+        <f>IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549")</f>
+        <v/>
       </c>
     </row>
     <row r="84">
@@ -2512,23 +2432,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>083.jpg</t>
-        </is>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E84">
+        <f>IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -2537,23 +2456,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>084.jpg</t>
-        </is>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E85">
+        <f>IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -2562,23 +2480,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>085.jpg</t>
-        </is>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E86">
+        <f>IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -2587,23 +2504,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>086.jpg</t>
-        </is>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E87">
+        <f>IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="88">
@@ -2612,23 +2528,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>087.jpg</t>
-        </is>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E88">
+        <f>IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="89">
@@ -2637,23 +2552,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+        </is>
+      </c>
+      <c r="E89">
+        <f>IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -2662,22 +2576,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>089.jpg</t>
+          <t>이미지 없음</t>
         </is>
       </c>
     </row>
@@ -2687,23 +2601,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>090.jpg</t>
-        </is>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E91">
+        <f>IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="92">
@@ -2712,23 +2625,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>091.jpg</t>
-        </is>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
+        </is>
+      </c>
+      <c r="E92">
+        <f>IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="93">
@@ -2737,23 +2649,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2575581</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>092.jpg</t>
-        </is>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
+        </is>
+      </c>
+      <c r="E93">
+        <f>IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="94">
@@ -2762,23 +2673,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>093.jpg</t>
-        </is>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E94">
+        <f>IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -2787,23 +2697,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>094.jpg</t>
-        </is>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E95">
+        <f>IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="96">
@@ -2812,23 +2721,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>095.jpg</t>
-        </is>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+        </is>
+      </c>
+      <c r="E96">
+        <f>IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -2837,23 +2745,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E97">
+        <f>IMAGE("https://www.businesspost.co.kr/news/photo/202603/20260325115129_24184.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="98">
@@ -2862,23 +2769,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>http://amenews.kr/news/view.php?idx=66331</t>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E98">
+        <f>IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="99">
@@ -2887,23 +2793,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>098.jpg</t>
-        </is>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E99">
+        <f>IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="100">
@@ -2912,22 +2817,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>099.jpg</t>
+          <t>이미지 없음</t>
         </is>
       </c>
     </row>
@@ -2937,23 +2842,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>100.jpg</t>
-        </is>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E101">
+        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="102">
@@ -2962,23 +2866,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>101.jpg</t>
-        </is>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E102">
+        <f>IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="103">
@@ -2987,23 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>102.jpg</t>
-        </is>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E103">
+        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="104">
@@ -3012,23 +2914,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+          <t>https://www.etoday.co.kr/news/view/2571395</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
+          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E104">
+        <f>IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="105">
@@ -3037,23 +2938,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2573034</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>104.jpg</t>
-        </is>
+          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E105">
+        <f>IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="106">
@@ -3062,23 +2962,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>105.jpg</t>
-        </is>
+          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
+        </is>
+      </c>
+      <c r="E106">
+        <f>IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="107">
@@ -3087,23 +2986,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
+          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E107">
+        <f>IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="108">
@@ -3112,23 +3010,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>107.jpg</t>
-        </is>
+          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E108">
+        <f>IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="109">
@@ -3137,23 +3034,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260401154708093</t>
+          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>108.jpg</t>
-        </is>
+          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+        </is>
+      </c>
+      <c r="E109">
+        <f>IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="110">
@@ -3162,23 +3058,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+          <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>109.jpg</t>
-        </is>
+          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E110">
+        <f>IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png")</f>
+        <v/>
       </c>
     </row>
     <row r="111">
@@ -3187,23 +3082,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
+          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2571395</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>110.jpg</t>
-        </is>
+          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E111">
+        <f>IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="112">
@@ -3212,23 +3106,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
+          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>111.jpg</t>
-        </is>
+          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+        </is>
+      </c>
+      <c r="E112">
+        <f>IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="113">
@@ -3237,23 +3130,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
+          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
+          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>112.jpg</t>
-        </is>
+          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E113">
+        <f>IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="114">
@@ -3262,23 +3154,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
+          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
+          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>113.jpg</t>
-        </is>
+          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E114">
+        <f>IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="115">
@@ -3287,22 +3178,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
+          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>114.jpg</t>
+          <t>이미지 없음</t>
         </is>
       </c>
     </row>
@@ -3312,22 +3203,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
+          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
+          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>115.jpg</t>
+          <t>이미지 없음</t>
         </is>
       </c>
     </row>
@@ -3337,23 +3228,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260326500334</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>116.jpg</t>
-        </is>
+          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
+        </is>
+      </c>
+      <c r="E117">
+        <f>IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="118">
@@ -3362,23 +3252,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
+          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
+          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E118">
+        <f>IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="119">
@@ -3387,23 +3276,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
+          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>118.jpg</t>
-        </is>
+          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E119">
+        <f>IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="120">
@@ -3412,23 +3300,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
+          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
+          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>119.jpg</t>
-        </is>
+          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+        </is>
+      </c>
+      <c r="E120">
+        <f>IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="121">
@@ -3437,23 +3324,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
+          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>120.jpg</t>
-        </is>
+          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E121">
+        <f>IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="122">
@@ -3462,22 +3348,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
+          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
+          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
+          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>이미지 없음</t>
         </is>
       </c>
     </row>
@@ -3487,23 +3373,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
+          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
+          <t>https://www.ajunews.com/view/20260310153628801</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
+          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
+        </is>
+      </c>
+      <c r="E123">
+        <f>IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="124">
@@ -3512,23 +3397,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
+          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>123.jpg</t>
-        </is>
+          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E124">
+        <f>IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -3537,23 +3421,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
+          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>124.jpg</t>
-        </is>
+          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E125">
+        <f>IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="126">
@@ -3562,23 +3445,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>125.jpg</t>
-        </is>
+          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E126">
+        <f>IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="127">
@@ -3587,23 +3469,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>126.jpg</t>
-        </is>
+          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
+        </is>
+      </c>
+      <c r="E127">
+        <f>IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -3612,23 +3493,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>127.jpg</t>
-        </is>
+          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E128">
+        <f>IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="129">
@@ -3637,23 +3517,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
+          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
+          <t>https://www.ajunews.com/view/20260227150934536</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
+          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+        </is>
+      </c>
+      <c r="E129">
+        <f>IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="130">
@@ -3662,23 +3541,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
+          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260310153628801</t>
+          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>129.jpg</t>
-        </is>
+          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E130">
+        <f>IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="131">
@@ -3687,23 +3565,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
+          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>130.jpg</t>
-        </is>
+          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E131">
+        <f>IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="132">
@@ -3712,22 +3589,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
+          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
+          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>131.jpg</t>
+          <t>이미지 없음</t>
         </is>
       </c>
     </row>
@@ -3737,23 +3614,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
+          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>132.jpg</t>
-        </is>
+          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E133">
+        <f>IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="134">
@@ -3762,22 +3638,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
+          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>133.jpg</t>
+          <t>이미지 없음</t>
         </is>
       </c>
     </row>
@@ -3787,23 +3663,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>134.jpg</t>
-        </is>
+          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E135">
+        <f>IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="136">
@@ -3812,23 +3687,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
+          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260227150934536</t>
+          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>135.jpg</t>
-        </is>
+          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E136">
+        <f>IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="137">
@@ -3837,23 +3711,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
+          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
+          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>136.jpg</t>
-        </is>
+          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E137">
+        <f>IMAGE("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="138">
@@ -3862,23 +3735,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
+          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>137.jpg</t>
-        </is>
+          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
+        </is>
+      </c>
+      <c r="E138">
+        <f>IMAGE("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="139">
@@ -3887,23 +3759,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
+          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
+          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
+        </is>
+      </c>
+      <c r="E139">
+        <f>IMAGE("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="140">
@@ -3912,23 +3783,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
+          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>139.jpg</t>
-        </is>
+          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
+        </is>
+      </c>
+      <c r="E140">
+        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="141">
@@ -3937,23 +3807,22 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
+          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>140.jpg</t>
-        </is>
+          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E141">
+        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="142">
@@ -3962,23 +3831,22 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
+          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
+          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>141.jpg</t>
-        </is>
+          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
+        </is>
+      </c>
+      <c r="E142">
+        <f>IMAGE("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png")</f>
+        <v/>
       </c>
     </row>
     <row r="143">
@@ -3987,23 +3855,22 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
+          <t>'60조 잠수함' 끌어올 현대차 떴다… 韓-獨 벼랑끝 '국가 대항전'</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003499499?sid=101</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>142.jpg</t>
-        </is>
+          <t>Wed, 28 Jan 2026 05:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E143">
+        <f>IMAGE("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="144">
@@ -4012,23 +3879,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
+          <t>[로드픽] 핵잠 논의, 기술 아닌 '국가 통제의 문제'로 옮겨갔다</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
+          <t>http://www.newsroad.co.kr/news/articleView.html?idxno=53361</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>143.jpg</t>
-        </is>
+          <t>Tue, 27 Jan 2026 23:06:00 +0900</t>
+        </is>
+      </c>
+      <c r="E144">
+        <f>IMAGE("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="145">
@@ -4037,23 +3903,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
+          <t>[단독]방사청, 방산기업들에 ‘생성형 AI 해킹’ 주의 공문 발송</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002591811?sid=101</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>144.jpg</t>
-        </is>
+          <t>Tue, 27 Jan 2026 17:06:00 +0900</t>
+        </is>
+      </c>
+      <c r="E145">
+        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/01/27/0002591811_001_20260128090813263.png?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="146">
@@ -4062,23 +3927,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
+          <t>외교 경쟁 넘은 방산 수주전… 韓 '민관협력' 패키지로 차별화</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260127010012312</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>145.jpg</t>
-        </is>
+          <t>Mon, 26 Jan 2026 18:06:00 +0900</t>
+        </is>
+      </c>
+      <c r="E146">
+        <f>IMAGE("https://img.asiatoday.co.kr/file/2026y/01m/27d/20260127010012312_1769482157_1.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="147">
@@ -4087,23 +3951,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
+          <t>&amp;quot;무기입찰인줄 알았는데&amp;quot;···60조 캐나다 잠수함 '국가 산업 총력전'</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2384464</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>146.jpg</t>
-        </is>
+          <t>Thu, 22 Jan 2026 08:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E147">
+        <f>IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202601/2384464_1213799_3517_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="148">
@@ -4112,23 +3975,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
+          <t>전북대 학생들, 무기체계 자립도 평가 입체적 지표 제시 '학계 주목'</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
+          <t>https://www.ajunews.com/view/20260119082719729</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>147.jpg</t>
-        </is>
+          <t>Mon, 19 Jan 2026 08:32:00 +0900</t>
+        </is>
+      </c>
+      <c r="E148">
+        <f>IMAGE("https://image.ajunews.com/content/image/2026/01/19/20260119082811702593.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="149">
@@ -4137,23 +3999,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
+          <t>전북대 학생들, '무기체계 자립도' 새로운 지표 제시 '주목'</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
+          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542654</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>148.jpg</t>
-        </is>
+          <t>Sun, 18 Jan 2026 14:52:00 +0900</t>
+        </is>
+      </c>
+      <c r="E149">
+        <f>IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542654_744874_597_v150.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="150">
@@ -4162,23 +4023,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>'60조 잠수함' 끌어올 현대차 떴다… 韓-獨 벼랑끝 '국가 대항전'</t>
+          <t>전북대 학생들 ‘무기체계 자립도’ 새 지표 제시 눈길</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003499499?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/022/0004098361?sid=102</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 05:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>149.jpg</t>
-        </is>
+          <t>Sun, 18 Jan 2026 06:35:00 +0900</t>
+        </is>
+      </c>
+      <c r="E150">
+        <f>IMAGE("https://imgnews.pstatic.net/image/022/2026/01/18/20260116511422_20260118063511077.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="151">
@@ -4187,198 +4047,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>[로드픽] 핵잠 논의, 기술 아닌 '국가 통제의 문제'로 옮겨갔다</t>
+          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>http://www.newsroad.co.kr/news/articleView.html?idxno=53361</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 23:06:00 +0900</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>150.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>151</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>[단독]방사청, 방산기업들에 ‘생성형 AI 해킹’ 주의 공문 발송</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002591811?sid=101</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Tue, 27 Jan 2026 17:06:00 +0900</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>151.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>152</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>외교 경쟁 넘은 방산 수주전… 韓 '민관협력' 패키지로 차별화</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260127010012312</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Mon, 26 Jan 2026 18:06:00 +0900</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>152.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>&amp;quot;무기입찰인줄 알았는데&amp;quot;···60조 캐나다 잠수함 '국가 산업 총력전'</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2384464</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Thu, 22 Jan 2026 08:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>153.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>154</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>전북대 학생들, 무기체계 자립도 평가 입체적 지표 제시 '학계 주목'</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>https://www.ajunews.com/view/20260119082719729</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Mon, 19 Jan 2026 08:32:00 +0900</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>154.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>155</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>전북대 학생들, '무기체계 자립도' 새로운 지표 제시 '주목'</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542654</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Sun, 18 Jan 2026 14:52:00 +0900</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>155.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>전북대 학생들 ‘무기체계 자립도’ 새 지표 제시 눈길</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/022/0004098361?sid=102</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Sun, 18 Jan 2026 06:35:00 +0900</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>156.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
           <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>157.jpg</t>
-        </is>
+      <c r="E151">
+        <f>IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -4418,7 +4102,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>이미지저장</t>
+          <t>이미지보기</t>
         </is>
       </c>
     </row>
@@ -4441,10 +4125,9 @@
           <t>Thu, 23 Apr 2026 04:31:00 +0900</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>001.jpg</t>
-        </is>
+      <c r="E2">
+        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -4466,10 +4149,9 @@
           <t>Mon, 20 Apr 2026 14:12:00 +0900</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>002.jpg</t>
-        </is>
+      <c r="E3">
+        <f>IMAGE("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -4491,10 +4173,9 @@
           <t>Mon, 30 Mar 2026 15:52:00 +0900</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>003.jpg</t>
-        </is>
+      <c r="E4">
+        <f>IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -4516,10 +4197,9 @@
           <t>Mon, 09 Mar 2026 15:56:00 +0900</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
+      <c r="E5">
+        <f>IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260310/thumb1/BBS_202603100847055860.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -4541,10 +4221,9 @@
           <t>Sun, 08 Mar 2026 17:19:00 +0900</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>005.jpg</t>
-        </is>
+      <c r="E6">
+        <f>IMAGE("https://imgnews.pstatic.net/image/009/2026/03/08/0005646852_001_20260308175312269.jpg?type=w800")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -4566,10 +4245,9 @@
           <t>Fri, 06 Mar 2026 10:46:00 +0900</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>006.jpg</t>
-        </is>
+      <c r="E7">
+        <f>IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/06/2026030610261598884_00_643.jpg")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -4591,10 +4269,9 @@
           <t>Tue, 27 Jan 2026 18:56:00 +0900</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>007.jpg</t>
-        </is>
+      <c r="E8">
+        <f>IMAGE("https://imgnews.pstatic.net/image/021/2026/01/27/0002766903_001_20260127185614662.png?type=w800")</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -2504,12 +2504,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="E87">
-        <f>IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg")</f>
+        <f>IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg")</f>
         <v/>
       </c>
     </row>
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="E88">
-        <f>IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg")</f>
+        <f>IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg")</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="E2">
-        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="E3">
-        <f>IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg")</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E4">
-        <f>IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="E5">
-        <f>IMAGE("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg")</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="E6">
-        <f>IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="E7">
-        <f>IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="E8">
-        <f>IMAGE("https://www.jeonmae.co.kr/news/thumbnail/202605/1256767_976877_187_v150.jpg")</f>
+        <f>HYPERLINK("https://www.jeonmae.co.kr/news/thumbnail/202605/1256767_976877_187_v150.jpg", IMAGE("https://www.jeonmae.co.kr/news/thumbnail/202605/1256767_976877_187_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="E9">
-        <f>IMAGE("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="E10">
-        <f>IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="E11">
-        <f>IMAGE("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="E12">
-        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="E13">
-        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -750,21 +750,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[뉴공 아카이브]강은호 전 방위사업청장·전북대 첨단방위산업학과 교수...</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>http://www.ddanzi.com/879846987</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 11:42:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E14">
-        <f>IMAGE("https://www.ddanzi.com/./files/attach/images/1176663/987/846/879/e3d94bdf26e8a3de4247826410f25b3e.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -774,21 +774,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E15">
-        <f>IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800")</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -798,21 +798,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E16">
-        <f>IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg")</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -846,21 +846,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E18">
-        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800")</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -870,21 +870,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E19">
-        <f>IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -894,21 +894,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[뉴공 아카이브]강은호 전 방위사업청장·전북대 첨단방위산업학과 교수...</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>http://www.ddanzi.com/879301743</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 11:46:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>IMAGE("https://www.ddanzi.com/./files/attach/images/1176663/743/301/879/1c5e3c5a58fddbcdf694eb20a336a880.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -918,21 +918,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -942,21 +942,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800")</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -966,21 +966,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg")</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -990,21 +990,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg")</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1014,21 +1014,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1038,21 +1038,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1062,21 +1062,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1086,21 +1086,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[뉴공 아카이브]강은호 전 방위사업청장·전북대 첨단방위산업학과 교수...</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>http://www.ddanzi.com/878494144</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 12:30:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E28">
-        <f>IMAGE("https://www.ddanzi.com/./files/attach/images/1176663/144/494/878/b2ada78cb3b317b58717884e9ae1e6e1.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1110,21 +1110,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800")</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1134,21 +1134,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[뉴공 아카이브]강은호 전 방위사업청장·전북대 첨단방위산업학과 교수...</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>http://www.ddanzi.com/877818479</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 12:46:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>IMAGE("https://www.ddanzi.com/./files/attach/images/1176663/479/818/877/c16820231793e69cba35df2fa3e117c4.jpg")</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1158,21 +1158,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E31">
-        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1182,21 +1182,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800")</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1206,21 +1206,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>“AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1230,21 +1230,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>IMAGE("https://static.naeil.com/img/rect_logo.jpg")</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1254,21 +1254,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>전북대 71억 규모 '첨단인재양성 부트캠프 사업' 선정</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>http://www.veritas-a.com/news/articleView.html?idxno=600409</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Wed, 04 Mar 2026 14:34:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800")</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1278,21 +1278,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
+          <t>전북대, 첨단산업 인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001010129?sid=102</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
+          <t>Wed, 04 Mar 2026 12:37:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1302,21 +1302,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>“AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
+          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
+          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800")</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1326,21 +1326,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
+          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
+          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1350,21 +1350,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>전북대 71억 규모 '첨단인재양성 부트캠프 사업' 선정</t>
+          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>http://www.veritas-a.com/news/articleView.html?idxno=600409</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 14:34:00 +0900</t>
+          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>IMAGE("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1374,21 +1374,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>전북대, 첨단산업 인재양성 부트캠프 사업 선정</t>
+          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001010129?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 12:37:00 +0900</t>
+          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>IMAGE("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1398,21 +1398,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
+          <t>전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
+          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg")</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1422,21 +1422,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
+          <t>전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
+          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
+          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800")</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1446,21 +1446,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
+          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
+          <t>http://www.kyosu.net/news/articleView.html?idxno=155230</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
+          <t>Thu, 15 Jan 2026 21:16:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800")</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png", IMAGE("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png"))</f>
         <v/>
       </c>
     </row>
@@ -1470,21 +1470,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
+          <t>전북대, 방산 AI 유니콘 '쉴드 AI'와 협력 추진</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=432185</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
+          <t>Thu, 15 Jan 2026 20:08:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800")</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1494,21 +1494,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, 글로벌 방산 AI 유니콘 쉴드 AI와 피지컬 AI 협력 추진</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
+          <t>https://www.betanews.net/article/view/beta202601150086</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
+          <t>Thu, 15 Jan 2026 19:26:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg")</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1518,21 +1518,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 체계 구축한다</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
+          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542514</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
+          <t>Thu, 15 Jan 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>IMAGE("https://static.naeil.com/img/rect_logo.jpg")</f>
+        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1542,21 +1542,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진...피지컬...</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>http://www.kyosu.net/news/articleView.html?idxno=155230</t>
+          <t>http://www.jbsori.com/news/articleView.html?idxno=16762</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 21:16:00 +0900</t>
+          <t>Thu, 15 Jan 2026 15:50:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>IMAGE("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png")</f>
+        <f>HYPERLINK("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg", IMAGE("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1566,21 +1566,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>전북대, 방산 AI 유니콘 '쉴드 AI'와 협력 추진</t>
+          <t>전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=432185</t>
+          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 20:08:00 +0900</t>
+          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png", IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png"))</f>
         <v/>
       </c>
     </row>
@@ -1590,21 +1590,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>전북대, 글로벌 방산 AI 유니콘 쉴드 AI와 피지컬 AI 협력 추진</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202601150086</t>
+          <t>https://www.gukjenews.com/news/articleView.html?idxno=3481565</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 19:26:00 +0900</t>
+          <t>Thu, 15 Jan 2026 14:06:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>IMAGE("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg")</f>
+        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1614,21 +1614,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 체계 구축한다</t>
+          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542514</t>
+          <t>http://www.veritas-a.com/news/articleView.html?idxno=594342</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 18:24:00 +0900</t>
+          <t>Thu, 15 Jan 2026 12:22:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1638,21 +1638,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진...피지컬...</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>http://www.jbsori.com/news/articleView.html?idxno=16762</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003390311?sid=102</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:50:00 +0900</t>
+          <t>Thu, 15 Jan 2026 12:12:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>IMAGE("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1662,21 +1662,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
+          <t>전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
+          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1686,21 +1686,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.gukjenews.com/news/articleView.html?idxno=3481565</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=588811</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 14:06:00 +0900</t>
+          <t>Thu, 15 Jan 2026 10:36:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>IMAGE("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1710,21 +1710,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>http://www.veritas-a.com/news/articleView.html?idxno=594342</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:22:00 +0900</t>
+          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>IMAGE("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1734,21 +1734,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003390311?sid=102</t>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:12:00 +0900</t>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>IMAGE("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800")</f>
+        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1758,21 +1758,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800")</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1782,21 +1782,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력</t>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=588811</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:36:00 +0900</t>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>IMAGE("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1806,21 +1806,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800")</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
         <v/>
       </c>
     </row>
@@ -1830,21 +1830,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 10:00:00 +0900</t>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1854,21 +1854,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1878,21 +1878,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1902,21 +1902,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556")</f>
+        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1926,22 +1926,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:54:00 +0900</t>
-        </is>
-      </c>
-      <c r="E63">
-        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800")</f>
-        <v/>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -1950,21 +1951,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800")</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1974,21 +1975,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800")</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1998,21 +1999,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2022,23 +2023,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E67">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -2047,21 +2047,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 15:02:00 +0900</t>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg")</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2071,21 +2071,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 11:30:00 +0900</t>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2095,21 +2095,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 06:00:00 +0900</t>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2119,21 +2119,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800")</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2143,21 +2143,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>“한·일 함정 분야 경쟁 가능성”</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2167,21 +2167,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2191,21 +2191,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800")</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2215,21 +2215,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2239,21 +2239,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800")</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2263,21 +2263,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2287,22 +2287,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E78">
-        <f>IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg")</f>
-        <v/>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -2311,21 +2312,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800")</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
         <v/>
       </c>
     </row>
@@ -2335,21 +2336,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2359,21 +2360,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2383,23 +2384,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E82">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -2408,21 +2408,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549")</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2432,21 +2432,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800")</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2456,21 +2456,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2480,22 +2480,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2575581</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E86">
-        <f>IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg")</f>
-        <v/>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -2504,21 +2505,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg")</f>
+        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2528,21 +2529,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2552,21 +2553,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800")</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2576,23 +2577,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E90">
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="91">
@@ -2601,21 +2601,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>http://amenews.kr/news/view.php?idx=66331</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg")</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2625,21 +2625,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2649,22 +2649,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
-        </is>
-      </c>
-      <c r="E93">
-        <f>IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg")</f>
-        <v/>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -2673,21 +2674,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg")</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2697,21 +2698,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
         </is>
       </c>
       <c r="E95">
-        <f>IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2721,22 +2722,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
-        </is>
-      </c>
-      <c r="E96">
-        <f>IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800")</f>
-        <v/>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -2745,21 +2747,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>IMAGE("https://www.businesspost.co.kr/news/photo/202603/20260325115129_24184.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2769,21 +2771,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2573034</t>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg")</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2793,21 +2795,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2817,23 +2819,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+          <t>https://www.etoday.co.kr/news/view/2571395</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E100">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="101">
@@ -2842,21 +2843,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2866,21 +2867,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260401154708093</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
+          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg")</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2890,21 +2891,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
+          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800")</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2914,21 +2915,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
+          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2571395</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
+          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2938,21 +2939,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
+          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
+          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
+          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800")</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2962,21 +2963,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
+          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
+          <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
+          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
         <v/>
       </c>
     </row>
@@ -2986,21 +2987,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
+          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
+          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg")</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3010,21 +3011,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
+          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3034,21 +3035,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
+          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
+          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg")</f>
+        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3058,21 +3059,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260326500334</t>
+          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
+          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png")</f>
+        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3082,22 +3083,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
+          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
-        </is>
-      </c>
-      <c r="E111">
-        <f>IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg")</f>
-        <v/>
+          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -3106,22 +3108,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
+          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
+          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
-        </is>
-      </c>
-      <c r="E112">
-        <f>IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800")</f>
-        <v/>
+          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -3130,21 +3133,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
+          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E113">
-        <f>IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg")</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3154,21 +3157,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
+          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3178,23 +3181,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
+          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E115">
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="116">
@@ -3203,23 +3205,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
+          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
+          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+        </is>
+      </c>
+      <c r="E116">
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="117">
@@ -3228,21 +3229,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
+          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
+          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3252,22 +3253,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
+          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
+          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E118">
-        <f>IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800")</f>
-        <v/>
+          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -3276,21 +3278,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
+          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
+          <t>https://www.ajunews.com/view/20260310153628801</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
+          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg")</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3300,21 +3302,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
+          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E120">
-        <f>IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg")</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3324,21 +3326,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
+          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
+          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3348,23 +3350,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E122">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="123">
@@ -3373,21 +3374,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260310153628801</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
+          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3397,21 +3398,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
+          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
         </is>
       </c>
       <c r="E124">
-        <f>IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3421,21 +3422,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
+          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
+          <t>https://www.ajunews.com/view/20260227150934536</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
+          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800")</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3445,21 +3446,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
+          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
+          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800")</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3469,21 +3470,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
+          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E127">
-        <f>IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800")</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3493,22 +3494,23 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E128">
-        <f>IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800")</f>
-        <v/>
+          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -3517,21 +3519,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
+          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260227150934536</t>
+          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg")</f>
+        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3541,21 +3543,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
+          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E130">
-        <f>IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg")</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3565,21 +3567,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
+          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
+          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg")</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3589,23 +3591,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
+          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
+          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E132">
+        <f>HYPERLINK("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg", IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="133">
@@ -3614,21 +3615,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
+          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
+          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg")</f>
+        <f>HYPERLINK("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg", IMAGE("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3638,23 +3639,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
+          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
+        </is>
+      </c>
+      <c r="E134">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="135">
@@ -3663,21 +3663,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
+          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
+          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3687,21 +3687,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
+          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
+          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3711,21 +3711,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
+          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
+          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>IMAGE("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3735,21 +3735,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
+          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
+          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
+          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>IMAGE("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800")</f>
+        <f>HYPERLINK("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png", IMAGE("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png"))</f>
         <v/>
       </c>
     </row>
@@ -3759,21 +3759,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
+          <t>'60조 잠수함' 끌어올 현대차 떴다… 韓-獨 벼랑끝 '국가 대항전'</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003499499?sid=101</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
+          <t>Wed, 28 Jan 2026 05:00:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>IMAGE("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3783,21 +3783,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
+          <t>[로드픽] 핵잠 논의, 기술 아닌 '국가 통제의 문제'로 옮겨갔다</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
+          <t>http://www.newsroad.co.kr/news/articleView.html?idxno=53361</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
+          <t>Tue, 27 Jan 2026 23:06:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800")</f>
+        <f>HYPERLINK("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg", IMAGE("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3807,21 +3807,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
+          <t>[단독]방사청, 방산기업들에 ‘생성형 AI 해킹’ 주의 공문 발송</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002591811?sid=101</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
+          <t>Tue, 27 Jan 2026 17:06:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/27/0002591811_001_20260128090813263.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/27/0002591811_001_20260128090813263.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3831,21 +3831,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
+          <t>외교 경쟁 넘은 방산 수주전… 韓 '민관협력' 패키지로 차별화</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260127010012312</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
+          <t>Mon, 26 Jan 2026 18:06:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>IMAGE("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png")</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/01m/27d/20260127010012312_1769482157_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/01m/27d/20260127010012312_1769482157_1.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3855,21 +3855,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>'60조 잠수함' 끌어올 현대차 떴다… 韓-獨 벼랑끝 '국가 대항전'</t>
+          <t>&amp;quot;무기입찰인줄 알았는데&amp;quot;···60조 캐나다 잠수함 '국가 산업 총력전'</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003499499?sid=101</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2384464</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 05:00:00 +0900</t>
+          <t>Thu, 22 Jan 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>IMAGE("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800")</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202601/2384464_1213799_3517_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202601/2384464_1213799_3517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3879,21 +3879,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[로드픽] 핵잠 논의, 기술 아닌 '국가 통제의 문제'로 옮겨갔다</t>
+          <t>전북대 학생들, 무기체계 자립도 평가 입체적 지표 제시 '학계 주목'</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>http://www.newsroad.co.kr/news/articleView.html?idxno=53361</t>
+          <t>https://www.ajunews.com/view/20260119082719729</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 23:06:00 +0900</t>
+          <t>Mon, 19 Jan 2026 08:32:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>IMAGE("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg")</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/01/19/20260119082811702593.jpg", IMAGE("https://image.ajunews.com/content/image/2026/01/19/20260119082811702593.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3903,21 +3903,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[단독]방사청, 방산기업들에 ‘생성형 AI 해킹’ 주의 공문 발송</t>
+          <t>전북대 학생들, '무기체계 자립도' 새로운 지표 제시 '주목'</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002591811?sid=101</t>
+          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542654</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 17:06:00 +0900</t>
+          <t>Sun, 18 Jan 2026 14:52:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>IMAGE("https://imgnews.pstatic.net/image/016/2026/01/27/0002591811_001_20260128090813263.png?type=w800")</f>
+        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202601/1542654_744874_597_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542654_744874_597_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3927,21 +3927,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>외교 경쟁 넘은 방산 수주전… 韓 '민관협력' 패키지로 차별화</t>
+          <t>전북대 학생들 ‘무기체계 자립도’ 새 지표 제시 눈길</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260127010012312</t>
+          <t>https://n.news.naver.com/mnews/article/022/0004098361?sid=102</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 18:06:00 +0900</t>
+          <t>Sun, 18 Jan 2026 06:35:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>IMAGE("https://img.asiatoday.co.kr/file/2026y/01m/27d/20260127010012312_1769482157_1.jpg")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/022/2026/01/18/20260116511422_20260118063511077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/022/2026/01/18/20260116511422_20260118063511077.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3951,117 +3951,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>&amp;quot;무기입찰인줄 알았는데&amp;quot;···60조 캐나다 잠수함 '국가 산업 총력전'</t>
+          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2384464</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Thu, 22 Jan 2026 08:00:00 +0900</t>
+          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202601/2384464_1213799_3517_v150.jpg")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>전북대 학생들, 무기체계 자립도 평가 입체적 지표 제시 '학계 주목'</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>https://www.ajunews.com/view/20260119082719729</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Mon, 19 Jan 2026 08:32:00 +0900</t>
-        </is>
-      </c>
-      <c r="E148">
-        <f>IMAGE("https://image.ajunews.com/content/image/2026/01/19/20260119082811702593.jpg")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>전북대 학생들, '무기체계 자립도' 새로운 지표 제시 '주목'</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542654</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Sun, 18 Jan 2026 14:52:00 +0900</t>
-        </is>
-      </c>
-      <c r="E149">
-        <f>IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542654_744874_597_v150.jpg")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>전북대 학생들 ‘무기체계 자립도’ 새 지표 제시 눈길</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/022/0004098361?sid=102</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Sun, 18 Jan 2026 06:35:00 +0900</t>
-        </is>
-      </c>
-      <c r="E150">
-        <f>IMAGE("https://imgnews.pstatic.net/image/022/2026/01/18/20260116511422_20260118063511077.jpg?type=w800")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E151">
-        <f>IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4126,7 +4030,7 @@
         </is>
       </c>
       <c r="E2">
-        <f>IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4150,7 +4054,7 @@
         </is>
       </c>
       <c r="E3">
-        <f>IMAGE("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg")</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4174,7 +4078,7 @@
         </is>
       </c>
       <c r="E4">
-        <f>IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg")</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4198,7 +4102,7 @@
         </is>
       </c>
       <c r="E5">
-        <f>IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260310/thumb1/BBS_202603100847055860.jpg")</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260310/thumb1/BBS_202603100847055860.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260310/thumb1/BBS_202603100847055860.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4222,7 +4126,7 @@
         </is>
       </c>
       <c r="E6">
-        <f>IMAGE("https://imgnews.pstatic.net/image/009/2026/03/08/0005646852_001_20260308175312269.jpg?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/009/2026/03/08/0005646852_001_20260308175312269.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/009/2026/03/08/0005646852_001_20260308175312269.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4246,7 +4150,7 @@
         </is>
       </c>
       <c r="E7">
-        <f>IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/06/2026030610261598884_00_643.jpg")</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/06/2026030610261598884_00_643.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/06/2026030610261598884_00_643.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4270,7 +4174,7 @@
         </is>
       </c>
       <c r="E8">
-        <f>IMAGE("https://imgnews.pstatic.net/image/021/2026/01/27/0002766903_001_20260127185614662.png?type=w800")</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/01/27/0002766903_001_20260127185614662.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/01/27/0002766903_001_20260127185614662.png?type=w800"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -2408,12 +2408,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -2408,12 +2408,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2518,9 +2518,10 @@
           <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
         </is>
       </c>
-      <c r="E87">
-        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
-        <v/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -3556,9 +3557,10 @@
           <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
         </is>
       </c>
-      <c r="E130">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
-        <v/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="131">

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E147"/>
+  <dimension ref="A1:E148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1734,21 +1734,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
+          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 10:00:00 +0900</t>
+          <t>Tue, 26 May 2026 18:21:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1758,21 +1758,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+          <t>Tue, 26 May 2026 14:57:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1782,21 +1782,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1806,21 +1806,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1830,21 +1830,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:54:00 +0900</t>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1854,21 +1854,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
         <v/>
       </c>
     </row>
@@ -1878,21 +1878,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1902,21 +1902,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1926,23 +1926,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E63">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -1951,21 +1950,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 15:02:00 +0900</t>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1975,22 +1974,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 11:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E65">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -1999,21 +1999,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 06:00:00 +0900</t>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2023,21 +2023,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2047,21 +2047,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>“한·일 함정 분야 경쟁 가능성”</t>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2071,21 +2071,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2095,21 +2095,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2119,21 +2119,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2143,21 +2143,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2167,21 +2167,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2191,21 +2191,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2215,21 +2215,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2239,21 +2239,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2263,21 +2263,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2287,23 +2287,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E78">
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -2312,21 +2311,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2336,22 +2335,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E80">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -2360,21 +2360,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
         <v/>
       </c>
     </row>
@@ -2384,21 +2384,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2575581</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2408,21 +2408,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2432,21 +2432,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2456,21 +2456,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2480,23 +2480,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E86">
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -2505,23 +2504,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>http://amenews.kr/news/view.php?idx=66331</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+        </is>
+      </c>
+      <c r="E87">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="88">
@@ -2530,22 +2528,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
-        </is>
-      </c>
-      <c r="E88">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -2554,22 +2553,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
-        </is>
-      </c>
-      <c r="E89">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
-        <v/>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -2578,21 +2578,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2602,21 +2602,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2626,21 +2626,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2650,23 +2650,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E93">
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="94">
@@ -2675,21 +2674,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2573034</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2699,22 +2698,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E95">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
-        <v/>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -2723,23 +2723,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E96">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -2748,21 +2747,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2772,22 +2771,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260401154708093</t>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E98">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
-        <v/>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -2796,21 +2796,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2820,21 +2820,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2571395</t>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2844,21 +2844,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
+          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2868,21 +2868,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
+          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
+          <t>https://www.etoday.co.kr/news/view/2571395</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2892,21 +2892,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
+          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2916,21 +2916,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
+          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2940,21 +2940,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
+          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2964,21 +2964,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260326500334</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
+          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2988,21 +2988,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
+          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
+          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
+          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3012,21 +3012,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
+          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
+          <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
         <v/>
       </c>
     </row>
@@ -3036,21 +3036,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
+          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3060,21 +3060,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
+          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3084,23 +3084,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
+          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
+          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E111">
+        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="112">
@@ -3109,23 +3108,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
+          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
+          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E112">
+        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="113">
@@ -3134,22 +3132,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
+          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
-        </is>
-      </c>
-      <c r="E113">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
-        <v/>
+          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -3158,22 +3157,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
+          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
+          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E114">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
-        <v/>
+          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -3182,21 +3182,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
+          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
+          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3206,21 +3206,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
+          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3230,21 +3230,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
+          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
+          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3254,23 +3254,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
+          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
+          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+        </is>
+      </c>
+      <c r="E118">
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="119">
@@ -3279,21 +3278,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
+          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260310153628801</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
+          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3303,22 +3302,23 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
+          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
+          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E120">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -3327,21 +3327,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
+          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
+          <t>https://www.ajunews.com/view/20260310153628801</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
+          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3351,21 +3351,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
+          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3375,21 +3375,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
+          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3404,16 +3404,16 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
+          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
         </is>
       </c>
       <c r="E124">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3423,21 +3423,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260227150934536</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3447,21 +3447,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3471,21 +3471,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
+          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
+          <t>https://www.ajunews.com/view/20260227150934536</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
+          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3495,23 +3495,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
+          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
+          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E128">
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="129">
@@ -3520,21 +3519,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
+          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3544,17 +3543,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
+          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
+          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -3569,21 +3568,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
+          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
+          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
+          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3593,21 +3592,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
+          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
+          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg", IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3617,21 +3616,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
+          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
+          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg", IMAGE("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3641,21 +3640,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
+          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
+          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
+          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg", IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3665,21 +3664,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
+          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
+          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
+          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg", IMAGE("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3689,21 +3688,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
+          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
+          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3713,21 +3712,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
+          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
+          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3737,21 +3736,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
+          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
+          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png", IMAGE("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3761,21 +3760,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>'60조 잠수함' 끌어올 현대차 떴다… 韓-獨 벼랑끝 '국가 대항전'</t>
+          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003499499?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 05:00:00 +0900</t>
+          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3785,21 +3784,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>[로드픽] 핵잠 논의, 기술 아닌 '국가 통제의 문제'로 옮겨갔다</t>
+          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>http://www.newsroad.co.kr/news/articleView.html?idxno=53361</t>
+          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 23:06:00 +0900</t>
+          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg", IMAGE("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png", IMAGE("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png"))</f>
         <v/>
       </c>
     </row>
@@ -3809,21 +3808,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>[단독]방사청, 방산기업들에 ‘생성형 AI 해킹’ 주의 공문 발송</t>
+          <t>'60조 잠수함' 끌어올 현대차 떴다… 韓-獨 벼랑끝 '국가 대항전'</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002591811?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003499499?sid=101</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 17:06:00 +0900</t>
+          <t>Wed, 28 Jan 2026 05:00:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/27/0002591811_001_20260128090813263.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/27/0002591811_001_20260128090813263.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3833,21 +3832,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>외교 경쟁 넘은 방산 수주전… 韓 '민관협력' 패키지로 차별화</t>
+          <t>[로드픽] 핵잠 논의, 기술 아닌 '국가 통제의 문제'로 옮겨갔다</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260127010012312</t>
+          <t>http://www.newsroad.co.kr/news/articleView.html?idxno=53361</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 18:06:00 +0900</t>
+          <t>Tue, 27 Jan 2026 23:06:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/01m/27d/20260127010012312_1769482157_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/01m/27d/20260127010012312_1769482157_1.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg", IMAGE("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3857,21 +3856,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>&amp;quot;무기입찰인줄 알았는데&amp;quot;···60조 캐나다 잠수함 '국가 산업 총력전'</t>
+          <t>[단독]방사청, 방산기업들에 ‘생성형 AI 해킹’ 주의 공문 발송</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2384464</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002591811?sid=101</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Thu, 22 Jan 2026 08:00:00 +0900</t>
+          <t>Tue, 27 Jan 2026 17:06:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202601/2384464_1213799_3517_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202601/2384464_1213799_3517_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/27/0002591811_001_20260128090813263.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/27/0002591811_001_20260128090813263.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3881,21 +3880,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>전북대 학생들, 무기체계 자립도 평가 입체적 지표 제시 '학계 주목'</t>
+          <t>외교 경쟁 넘은 방산 수주전… 韓 '민관협력' 패키지로 차별화</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260119082719729</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260127010012312</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:32:00 +0900</t>
+          <t>Mon, 26 Jan 2026 18:06:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/01/19/20260119082811702593.jpg", IMAGE("https://image.ajunews.com/content/image/2026/01/19/20260119082811702593.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/01m/27d/20260127010012312_1769482157_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/01m/27d/20260127010012312_1769482157_1.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3905,21 +3904,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>전북대 학생들, '무기체계 자립도' 새로운 지표 제시 '주목'</t>
+          <t>&amp;quot;무기입찰인줄 알았는데&amp;quot;···60조 캐나다 잠수함 '국가 산업 총력전'</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542654</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2384464</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 14:52:00 +0900</t>
+          <t>Thu, 22 Jan 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202601/1542654_744874_597_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542654_744874_597_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202601/2384464_1213799_3517_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202601/2384464_1213799_3517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3929,21 +3928,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>전북대 학생들 ‘무기체계 자립도’ 새 지표 제시 눈길</t>
+          <t>전북대 학생들, 무기체계 자립도 평가 입체적 지표 제시 '학계 주목'</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/022/0004098361?sid=102</t>
+          <t>https://www.ajunews.com/view/20260119082719729</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 06:35:00 +0900</t>
+          <t>Mon, 19 Jan 2026 08:32:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/022/2026/01/18/20260116511422_20260118063511077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/022/2026/01/18/20260116511422_20260118063511077.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/01/19/20260119082811702593.jpg", IMAGE("https://image.ajunews.com/content/image/2026/01/19/20260119082811702593.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3953,20 +3952,44 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
+          <t>전북대 학생들, '무기체계 자립도' 새로운 지표 제시 '주목'</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542654</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 14:52:00 +0900</t>
+        </is>
+      </c>
+      <c r="E147">
+        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202601/1542654_744874_597_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542654_744874_597_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
           <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
-      <c r="E147">
+      <c r="E148">
         <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
         <v/>
       </c>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1734,21 +1734,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
+          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 18:21:00 +0900</t>
+          <t>Wed, 27 May 2026 17:23:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260527172309602.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260527172309602.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1758,22 +1758,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
+          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 14:57:00 +0900</t>
-        </is>
-      </c>
-      <c r="E56">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
-        <v/>
+          <t>Wed, 27 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -1782,21 +1783,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
+          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 10:00:00 +0900</t>
+          <t>Tue, 26 May 2026 18:21:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1806,21 +1807,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+          <t>Tue, 26 May 2026 14:57:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1830,21 +1831,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1854,21 +1855,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1878,21 +1879,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:54:00 +0900</t>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1902,21 +1903,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
         <v/>
       </c>
     </row>
@@ -1926,21 +1927,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1950,21 +1951,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1974,23 +1975,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E65">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -1999,21 +1999,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 15:02:00 +0900</t>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2023,22 +2023,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 11:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E67">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -2047,21 +2048,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 06:00:00 +0900</t>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2071,21 +2072,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2095,21 +2096,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>“한·일 함정 분야 경쟁 가능성”</t>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2119,21 +2120,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2143,21 +2144,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2167,21 +2168,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2191,21 +2192,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2215,21 +2216,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2239,21 +2240,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2263,21 +2264,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2287,21 +2288,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2311,21 +2312,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2335,23 +2336,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E80">
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -2360,21 +2360,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2384,22 +2384,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E82">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -2408,21 +2409,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
         <v/>
       </c>
     </row>
@@ -2432,21 +2433,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2575581</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2456,21 +2457,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2480,21 +2481,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2504,21 +2505,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2528,23 +2529,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E88">
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="89">
@@ -2553,23 +2553,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>http://amenews.kr/news/view.php?idx=66331</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+        </is>
+      </c>
+      <c r="E89">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -2578,22 +2577,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
-        </is>
-      </c>
-      <c r="E90">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -2602,21 +2602,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
+        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2626,21 +2626,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2650,21 +2650,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2674,21 +2674,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2698,23 +2698,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E95">
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="96">
@@ -2723,21 +2722,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2573034</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2747,22 +2746,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E97">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
-        <v/>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -2771,23 +2771,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E98">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="99">
@@ -2796,21 +2795,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2820,22 +2819,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260401154708093</t>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E100">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
-        <v/>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -2844,21 +2844,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2868,21 +2868,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2571395</t>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2892,21 +2892,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
+          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2916,21 +2916,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
+          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
+          <t>https://www.etoday.co.kr/news/view/2571395</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2940,21 +2940,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
+          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2964,21 +2964,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
+          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2988,21 +2988,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
+          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3012,21 +3012,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260326500334</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
+          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3036,21 +3036,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
+          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
+          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
+          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3060,21 +3060,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
+          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
+          <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
         <v/>
       </c>
     </row>
@@ -3084,21 +3084,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
+          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3108,21 +3108,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
+          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E112">
-        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3132,23 +3132,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
+          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
+          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E113">
+        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="114">
@@ -3157,23 +3156,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
+          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
+          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E114">
+        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="115">
@@ -3182,22 +3180,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
+          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
-        </is>
-      </c>
-      <c r="E115">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
-        <v/>
+          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -3206,22 +3205,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
+          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
+          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E116">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
-        <v/>
+          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -3230,21 +3230,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
+          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
+          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3254,21 +3254,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
+          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3278,21 +3278,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
+          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
+          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3302,23 +3302,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
+          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
+          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+        </is>
+      </c>
+      <c r="E120">
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="121">
@@ -3327,21 +3326,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
+          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260310153628801</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
+          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3351,22 +3350,23 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
+          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
+          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E122">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -3375,21 +3375,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
+          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
+          <t>https://www.ajunews.com/view/20260310153628801</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
+          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3399,21 +3399,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
+          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E124">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3423,21 +3423,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
+          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3452,16 +3452,16 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
+          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3471,21 +3471,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260227150934536</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3495,21 +3495,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
         </is>
       </c>
       <c r="E128">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3519,21 +3519,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
+          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
+          <t>https://www.ajunews.com/view/20260227150934536</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
+          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3543,23 +3543,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
+          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
+          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E130">
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="131">
@@ -3568,21 +3567,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
+          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3592,22 +3591,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
+          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
-        </is>
-      </c>
-      <c r="E132">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
-        <v/>
+          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -3616,21 +3616,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
+          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
+          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
+          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3640,22 +3640,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
+          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E134">
-        <f>HYPERLINK("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg", IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg"))</f>
-        <v/>
+          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -3664,21 +3665,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
+          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
+          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg", IMAGE("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3688,21 +3689,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
+          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
+          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
+          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg", IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3712,21 +3713,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
+          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
+          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
+          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg", IMAGE("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3736,21 +3737,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
+          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
+          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3760,21 +3761,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
+          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
+          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3784,21 +3785,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
+          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
+          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png", IMAGE("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3808,21 +3809,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>'60조 잠수함' 끌어올 현대차 떴다… 韓-獨 벼랑끝 '국가 대항전'</t>
+          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003499499?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 05:00:00 +0900</t>
+          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3832,21 +3833,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>[로드픽] 핵잠 논의, 기술 아닌 '국가 통제의 문제'로 옮겨갔다</t>
+          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>http://www.newsroad.co.kr/news/articleView.html?idxno=53361</t>
+          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 23:06:00 +0900</t>
+          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg", IMAGE("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png", IMAGE("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png"))</f>
         <v/>
       </c>
     </row>
@@ -3856,21 +3857,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>[단독]방사청, 방산기업들에 ‘생성형 AI 해킹’ 주의 공문 발송</t>
+          <t>'60조 잠수함' 끌어올 현대차 떴다… 韓-獨 벼랑끝 '국가 대항전'</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002591811?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003499499?sid=101</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 17:06:00 +0900</t>
+          <t>Wed, 28 Jan 2026 05:00:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/27/0002591811_001_20260128090813263.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/27/0002591811_001_20260128090813263.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3880,21 +3881,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>외교 경쟁 넘은 방산 수주전… 韓 '민관협력' 패키지로 차별화</t>
+          <t>[로드픽] 핵잠 논의, 기술 아닌 '국가 통제의 문제'로 옮겨갔다</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260127010012312</t>
+          <t>http://www.newsroad.co.kr/news/articleView.html?idxno=53361</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 18:06:00 +0900</t>
+          <t>Tue, 27 Jan 2026 23:06:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/01m/27d/20260127010012312_1769482157_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/01m/27d/20260127010012312_1769482157_1.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg", IMAGE("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3904,21 +3905,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>&amp;quot;무기입찰인줄 알았는데&amp;quot;···60조 캐나다 잠수함 '국가 산업 총력전'</t>
+          <t>[단독]방사청, 방산기업들에 ‘생성형 AI 해킹’ 주의 공문 발송</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2384464</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002591811?sid=101</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Thu, 22 Jan 2026 08:00:00 +0900</t>
+          <t>Tue, 27 Jan 2026 17:06:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202601/2384464_1213799_3517_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202601/2384464_1213799_3517_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/27/0002591811_001_20260128090813263.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/27/0002591811_001_20260128090813263.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3928,21 +3929,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>전북대 학생들, 무기체계 자립도 평가 입체적 지표 제시 '학계 주목'</t>
+          <t>외교 경쟁 넘은 방산 수주전… 韓 '민관협력' 패키지로 차별화</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260119082719729</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260127010012312</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:32:00 +0900</t>
+          <t>Mon, 26 Jan 2026 18:06:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/01/19/20260119082811702593.jpg", IMAGE("https://image.ajunews.com/content/image/2026/01/19/20260119082811702593.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/01m/27d/20260127010012312_1769482157_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/01m/27d/20260127010012312_1769482157_1.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3952,44 +3953,20 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>전북대 학생들, '무기체계 자립도' 새로운 지표 제시 '주목'</t>
+          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542654</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 14:52:00 +0900</t>
+          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202601/1542654_744874_597_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542654_744874_597_v150.jpg"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E148">
         <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
         <v/>
       </c>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E147"/>
+  <dimension ref="A1:E148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1734,21 +1734,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
+          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 17:23:00 +0900</t>
+          <t>Thu, 28 May 2026 17:38:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260527172309602.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260527172309602.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1758,23 +1758,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
+          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 28 May 2026 15:29:00 +0900</t>
+        </is>
+      </c>
+      <c r="E56">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -1783,21 +1782,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
+          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 18:21:00 +0900</t>
+          <t>Thu, 28 May 2026 10:35:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1807,21 +1806,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
+          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 14:57:00 +0900</t>
+          <t>Wed, 27 May 2026 17:23:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1831,22 +1830,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
+          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
+          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 10:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E59">
-        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
-        <v/>
+          <t>Wed, 27 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -1855,21 +1855,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+          <t>Tue, 26 May 2026 18:21:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1879,21 +1879,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+          <t>Tue, 26 May 2026 14:57:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1903,21 +1903,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
+        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1927,21 +1927,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:54:00 +0900</t>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1951,21 +1951,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1975,21 +1975,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
         <v/>
       </c>
     </row>
@@ -1999,21 +1999,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2023,23 +2023,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E67">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -2048,21 +2047,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 15:02:00 +0900</t>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2072,21 +2071,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 11:30:00 +0900</t>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2096,22 +2095,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 06:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E70">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
-        <v/>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -2120,21 +2120,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2144,21 +2144,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>“한·일 함정 분야 경쟁 가능성”</t>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2168,21 +2168,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2192,21 +2192,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2216,21 +2216,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2240,21 +2240,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2264,21 +2264,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
+          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2288,21 +2288,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2312,21 +2312,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2336,21 +2336,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2360,21 +2360,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2384,23 +2384,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E82">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -2409,21 +2408,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2433,21 +2432,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2457,22 +2456,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E85">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -2481,21 +2481,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2575581</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
         <v/>
       </c>
     </row>
@@ -2505,21 +2505,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2529,21 +2529,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2553,21 +2553,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2577,23 +2577,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E90">
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="91">
@@ -2602,21 +2601,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>http://amenews.kr/news/view.php?idx=66331</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2626,21 +2625,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2650,22 +2649,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
-        </is>
-      </c>
-      <c r="E93">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
-        <v/>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -2674,21 +2674,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
+        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2698,21 +2698,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
         </is>
       </c>
       <c r="E95">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2722,21 +2722,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2746,23 +2746,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E97">
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="98">
@@ -2771,21 +2770,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2573034</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2795,21 +2794,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2819,17 +2818,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -2844,21 +2843,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2868,21 +2867,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260401154708093</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2892,22 +2891,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E103">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
-        <v/>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -2916,21 +2916,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
+          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2571395</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2940,21 +2940,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2964,21 +2964,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
+          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2988,21 +2988,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
+          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
+          <t>https://www.etoday.co.kr/news/view/2571395</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3012,21 +3012,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
+          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3036,21 +3036,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
+          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3060,21 +3060,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260326500334</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
+          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3084,21 +3084,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
+          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
+          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3108,21 +3108,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
+          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
+          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
         </is>
       </c>
       <c r="E112">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3132,21 +3132,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
+          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
+          <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
         </is>
       </c>
       <c r="E113">
-        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
         <v/>
       </c>
     </row>
@@ -3156,21 +3156,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
+          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3180,23 +3180,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
+          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+        </is>
+      </c>
+      <c r="E115">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="116">
@@ -3205,23 +3204,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
+          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
+          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E116">
+        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="117">
@@ -3230,21 +3228,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
+          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
+          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
+          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3254,22 +3252,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
+          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E118">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -3278,22 +3277,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
+          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
+          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E119">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -3302,21 +3302,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
+          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3326,21 +3326,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
+          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
+          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3350,23 +3350,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
+          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E122">
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="123">
@@ -3375,21 +3374,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
+          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260310153628801</t>
+          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
+          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3399,21 +3398,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
+          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
+          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
         </is>
       </c>
       <c r="E124">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3423,22 +3422,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
+          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E125">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
-        <v/>
+          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -3447,21 +3447,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
+          <t>https://www.ajunews.com/view/20260310153628801</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
+          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3471,21 +3471,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
+          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3495,21 +3495,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
+          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
         </is>
       </c>
       <c r="E128">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3519,21 +3519,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260227150934536</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3543,21 +3543,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
         </is>
       </c>
       <c r="E130">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3567,21 +3567,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
+          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3591,23 +3591,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
+          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
+          <t>https://www.ajunews.com/view/20260227150934536</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+        </is>
+      </c>
+      <c r="E132">
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="133">
@@ -3616,21 +3615,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
+          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
+          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3640,23 +3639,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
+          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E134">
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="135">
@@ -3665,22 +3663,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
+          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E135">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -3689,21 +3688,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
+          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
+          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
+          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg", IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3713,21 +3712,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
+          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
+          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg", IMAGE("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3737,21 +3736,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
+          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
+          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3761,21 +3760,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
+          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
+          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
+          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg", IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3785,21 +3784,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
+          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
+          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
+          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg", IMAGE("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3809,21 +3808,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
+          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
+          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3833,21 +3832,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
+          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
+          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png", IMAGE("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3857,21 +3856,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>'60조 잠수함' 끌어올 현대차 떴다… 韓-獨 벼랑끝 '국가 대항전'</t>
+          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003499499?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 05:00:00 +0900</t>
+          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3881,21 +3880,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[로드픽] 핵잠 논의, 기술 아닌 '국가 통제의 문제'로 옮겨갔다</t>
+          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>http://www.newsroad.co.kr/news/articleView.html?idxno=53361</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 23:06:00 +0900</t>
+          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg", IMAGE("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3905,21 +3904,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[단독]방사청, 방산기업들에 ‘생성형 AI 해킹’ 주의 공문 발송</t>
+          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002591811?sid=101</t>
+          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 17:06:00 +0900</t>
+          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/27/0002591811_001_20260128090813263.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/27/0002591811_001_20260128090813263.png?type=w800"))</f>
+        <f>HYPERLINK("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png", IMAGE("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png"))</f>
         <v/>
       </c>
     </row>
@@ -3929,21 +3928,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>외교 경쟁 넘은 방산 수주전… 韓 '민관협력' 패키지로 차별화</t>
+          <t>'60조 잠수함' 끌어올 현대차 떴다… 韓-獨 벼랑끝 '국가 대항전'</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260127010012312</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003499499?sid=101</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 18:06:00 +0900</t>
+          <t>Wed, 28 Jan 2026 05:00:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/01m/27d/20260127010012312_1769482157_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/01m/27d/20260127010012312_1769482157_1.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3953,20 +3952,44 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
+          <t>[로드픽] 핵잠 논의, 기술 아닌 '국가 통제의 문제'로 옮겨갔다</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>http://www.newsroad.co.kr/news/articleView.html?idxno=53361</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Tue, 27 Jan 2026 23:06:00 +0900</t>
+        </is>
+      </c>
+      <c r="E147">
+        <f>HYPERLINK("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg", IMAGE("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
           <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
-      <c r="E147">
+      <c r="E148">
         <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
         <v/>
       </c>
@@ -3982,7 +4005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4156,30 +4179,6 @@
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>국회 무궁화포럼 ‘한국형 핵잠(K-SSN) 특별법’ 제정 위한 긴급토론회...</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002766903?sid=100</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Tue, 27 Jan 2026 18:56:00 +0900</t>
-        </is>
-      </c>
-      <c r="E8">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/01/27/0002766903_001_20260127185614662.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/01/27/0002766903_001_20260127185614662.png?type=w800"))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -1734,21 +1734,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
+          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 17:38:00 +0900</t>
+          <t>Fri, 29 May 2026 17:40:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1758,21 +1758,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
+          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
+          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 15:29:00 +0900</t>
+          <t>Fri, 29 May 2026 15:14:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1782,21 +1782,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
+          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 10:35:00 +0900</t>
+          <t>Thu, 28 May 2026 17:38:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1806,21 +1806,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
+          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 17:23:00 +0900</t>
+          <t>Thu, 28 May 2026 15:29:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1830,23 +1830,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
+          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 28 May 2026 10:35:00 +0900</t>
+        </is>
+      </c>
+      <c r="E59">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -1855,21 +1854,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
+          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 18:21:00 +0900</t>
+          <t>Wed, 27 May 2026 17:23:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1879,22 +1878,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
+          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 14:57:00 +0900</t>
-        </is>
-      </c>
-      <c r="E61">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
-        <v/>
+          <t>Wed, 27 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -1903,21 +1903,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
+          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 10:00:00 +0900</t>
+          <t>Tue, 26 May 2026 18:21:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1927,21 +1927,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+          <t>Tue, 26 May 2026 14:57:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1951,21 +1951,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1975,21 +1975,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1999,21 +1999,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:54:00 +0900</t>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2023,21 +2023,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
         <v/>
       </c>
     </row>
@@ -2047,21 +2047,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2071,21 +2071,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2095,23 +2095,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E70">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -2120,21 +2119,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 15:02:00 +0900</t>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2144,22 +2143,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 11:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E72">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -2168,21 +2168,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 06:00:00 +0900</t>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2192,21 +2192,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2216,21 +2216,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>“한·일 함정 분야 경쟁 가능성”</t>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2240,21 +2240,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2264,21 +2264,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2288,21 +2288,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2312,21 +2312,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2336,21 +2336,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2360,21 +2360,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2384,21 +2384,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2408,21 +2408,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2432,21 +2432,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2456,23 +2456,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E85">
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -2481,21 +2480,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2505,22 +2504,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E87">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -2529,21 +2529,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
         <v/>
       </c>
     </row>
@@ -2553,21 +2553,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2575581</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2577,21 +2577,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2601,21 +2601,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2625,21 +2625,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2649,23 +2649,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E93">
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="94">
@@ -2674,21 +2673,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>http://amenews.kr/news/view.php?idx=66331</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2698,22 +2697,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
-        </is>
-      </c>
-      <c r="E95">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -2722,21 +2722,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
+        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2746,21 +2746,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2770,21 +2770,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2794,21 +2794,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2818,23 +2818,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E100">
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="101">
@@ -2843,21 +2842,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2573034</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2867,22 +2866,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E102">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
-        <v/>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -2891,23 +2891,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E103">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="104">
@@ -2916,21 +2915,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2940,22 +2939,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260401154708093</t>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E105">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
-        <v/>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -2964,21 +2964,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2988,21 +2988,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2571395</t>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3012,21 +3012,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
+          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3036,21 +3036,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
+          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
+          <t>https://www.etoday.co.kr/news/view/2571395</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3060,21 +3060,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
+          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3084,21 +3084,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
+          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3108,21 +3108,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
+          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E112">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3132,21 +3132,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260326500334</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
+          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E113">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3156,21 +3156,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
+          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
+          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
+          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3180,21 +3180,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
+          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
+          <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
         <v/>
       </c>
     </row>
@@ -3204,21 +3204,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
+          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3228,21 +3228,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
+          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3252,23 +3252,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
+          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
+          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E118">
+        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="119">
@@ -3277,23 +3276,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
+          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
+          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E119">
+        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="120">
@@ -3302,22 +3300,23 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
+          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
-        </is>
-      </c>
-      <c r="E120">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
-        <v/>
+          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -3326,22 +3325,23 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
+          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
+          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E121">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
-        <v/>
+          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -3350,21 +3350,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
+          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
+          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3374,21 +3374,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
+          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3398,21 +3398,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
+          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
+          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E124">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3422,23 +3422,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
+          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
+          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+        </is>
+      </c>
+      <c r="E125">
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="126">
@@ -3447,21 +3446,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
+          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260310153628801</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
+          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3471,22 +3470,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
+          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
+          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E127">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -3495,21 +3495,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
+          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
+          <t>https://www.ajunews.com/view/20260310153628801</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
+          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
         </is>
       </c>
       <c r="E128">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3519,21 +3519,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
+          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3543,21 +3543,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
+          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
         </is>
       </c>
       <c r="E130">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3572,16 +3572,16 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
+          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3591,21 +3591,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260227150934536</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3615,21 +3615,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3639,21 +3639,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
+          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
+          <t>https://www.ajunews.com/view/20260227150934536</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
+          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3663,23 +3663,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
+          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
+          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E135">
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="136">
@@ -3688,21 +3687,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
+          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3712,22 +3711,23 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
+          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
-        </is>
-      </c>
-      <c r="E137">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
-        <v/>
+          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -3736,21 +3736,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
+          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
+          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
+          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3760,21 +3760,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
+          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
+          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg", IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3784,21 +3784,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
+          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
+          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg", IMAGE("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3808,21 +3808,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
+          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
+          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
+          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg", IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3832,21 +3832,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
+          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
+          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
+          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg", IMAGE("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3856,21 +3856,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
+          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
+          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3880,21 +3880,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
+          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
+          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3904,21 +3904,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
+          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
+          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png", IMAGE("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3928,21 +3928,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>'60조 잠수함' 끌어올 현대차 떴다… 韓-獨 벼랑끝 '국가 대항전'</t>
+          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003499499?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 05:00:00 +0900</t>
+          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/01/28/0003499499_001_20260206153413055.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3952,21 +3952,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[로드픽] 핵잠 논의, 기술 아닌 '국가 통제의 문제'로 옮겨갔다</t>
+          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>http://www.newsroad.co.kr/news/articleView.html?idxno=53361</t>
+          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 23:06:00 +0900</t>
+          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg", IMAGE("https://cdn.newsroad.co.kr/news/thumbnail/202601/53361_72109_3222_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png", IMAGE("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -2879,10 +2879,9 @@
           <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+      <c r="E102">
+        <f>HYPERLINK("https://www.businesspost.co.kr/news/photo/202603/20260325115129_24184.jpg", IMAGE("https://www.businesspost.co.kr/news/photo/202603/20260325115129_24184.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="103">

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -1734,21 +1734,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
+          <t>[상생의 힘, 기업가치를 올린다] 김동관의 한화, 방산 넘어 안보 기업으...</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
+          <t>https://www.g-enews.com/view.php?ud=20260601151511969112616b072_1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 17:40:00 +0900</t>
+          <t>Mon, 01 Jun 2026 19:12:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1758,21 +1758,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
+          <t>[상생의 힘, 기업가치를 올린다] 한화, 방산·조선·우주 국가전략산업...</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
+          <t>https://www.g-enews.com/view.php?ud=202606011338107634112616b072_1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 15:14:00 +0900</t>
+          <t>Mon, 01 Jun 2026 19:08:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1782,21 +1782,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
+          <t>‘K-잠수함’ 1만4000km 잠항, 獨 꺾고 60조 잭팟 터뜨릴까</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
+          <t>https://www.viva100.com/article/20260601500751</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 17:38:00 +0900</t>
+          <t>Mon, 01 Jun 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260602045218", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260602045218"))</f>
         <v/>
       </c>
     </row>
@@ -1806,21 +1806,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
+          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 15:29:00 +0900</t>
+          <t>Fri, 29 May 2026 17:40:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1830,21 +1830,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
+          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
+          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 10:35:00 +0900</t>
+          <t>Fri, 29 May 2026 15:14:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1854,21 +1854,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
+          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 17:23:00 +0900</t>
+          <t>Thu, 28 May 2026 17:38:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1878,23 +1878,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
+          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 28 May 2026 15:29:00 +0900</t>
+        </is>
+      </c>
+      <c r="E61">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -1903,21 +1902,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
+          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 18:21:00 +0900</t>
+          <t>Thu, 28 May 2026 10:35:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1927,21 +1926,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
+          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 14:57:00 +0900</t>
+          <t>Wed, 27 May 2026 17:23:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1951,22 +1950,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
+          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
+          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 10:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E64">
-        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
-        <v/>
+          <t>Wed, 27 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -1975,21 +1975,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+          <t>Tue, 26 May 2026 18:21:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1999,21 +1999,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+          <t>Tue, 26 May 2026 14:57:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2023,21 +2023,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
+        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2047,21 +2047,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:54:00 +0900</t>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2071,21 +2071,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2095,21 +2095,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
         <v/>
       </c>
     </row>
@@ -2119,21 +2119,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2143,23 +2143,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E72">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -2168,21 +2167,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 15:02:00 +0900</t>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2192,21 +2191,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 11:30:00 +0900</t>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2216,22 +2215,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 06:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E75">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
-        <v/>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -2240,21 +2240,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2264,21 +2264,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>“한·일 함정 분야 경쟁 가능성”</t>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2288,21 +2288,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2312,21 +2312,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2336,21 +2336,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2360,21 +2360,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2384,21 +2384,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
+          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2408,21 +2408,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2432,21 +2432,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2456,21 +2456,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2480,21 +2480,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2504,23 +2504,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E87">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="88">
@@ -2529,21 +2528,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2553,21 +2552,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2577,22 +2576,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E90">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -2601,21 +2601,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2575581</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
         <v/>
       </c>
     </row>
@@ -2625,21 +2625,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2649,21 +2649,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2673,21 +2673,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2697,23 +2697,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E95">
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="96">
@@ -2722,21 +2721,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>http://amenews.kr/news/view.php?idx=66331</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2746,21 +2745,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2770,22 +2769,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
-        </is>
-      </c>
-      <c r="E98">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
-        <v/>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -2794,21 +2794,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
+        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2818,21 +2818,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2842,21 +2842,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2866,21 +2866,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://www.businesspost.co.kr/news/photo/202603/20260325115129_24184.jpg", IMAGE("https://www.businesspost.co.kr/news/photo/202603/20260325115129_24184.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2890,21 +2890,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2573034</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2914,21 +2914,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2938,17 +2938,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -2963,21 +2963,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2987,21 +2987,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260401154708093</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3011,22 +3011,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E108">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
-        <v/>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -3035,21 +3036,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
+          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2571395</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3059,21 +3060,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3083,21 +3084,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
+          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3107,21 +3108,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
+          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
+          <t>https://www.etoday.co.kr/news/view/2571395</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E112">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3131,21 +3132,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
+          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E113">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3155,21 +3156,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
+          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3179,21 +3180,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260326500334</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
+          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3203,21 +3204,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
+          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
+          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3227,21 +3228,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
+          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
+          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3251,21 +3252,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
+          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
+          <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
         <v/>
       </c>
     </row>
@@ -3275,21 +3276,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
+          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3299,23 +3300,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
+          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+        </is>
+      </c>
+      <c r="E120">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="121">
@@ -3324,23 +3324,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
+          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
+          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E121">
+        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="122">
@@ -3349,21 +3348,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
+          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
+          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
+          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3373,22 +3372,23 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
+          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E123">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -3397,22 +3397,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
+          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
+          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E124">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -3421,21 +3422,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
+          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3445,21 +3446,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
+          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
+          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3469,23 +3470,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
+          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E127">
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -3494,21 +3494,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
+          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260310153628801</t>
+          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
+          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
         </is>
       </c>
       <c r="E128">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3518,21 +3518,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
+          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
+          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3542,22 +3542,23 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
+          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E130">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
-        <v/>
+          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -3566,21 +3567,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
+          <t>https://www.ajunews.com/view/20260310153628801</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
+          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3590,21 +3591,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
+          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3614,21 +3615,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
+          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3638,21 +3639,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260227150934536</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3662,21 +3663,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3686,21 +3687,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
+          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3710,23 +3711,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
+          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
+          <t>https://www.ajunews.com/view/20260227150934536</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+        </is>
+      </c>
+      <c r="E137">
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="138">
@@ -3735,21 +3735,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
+          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
+          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3759,21 +3759,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
+          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
+          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3783,22 +3783,23 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
+          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E140">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -3807,21 +3808,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
+          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
+          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
+          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg", IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3831,21 +3832,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
+          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
+          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg", IMAGE("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3855,21 +3856,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
+          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
+          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3879,21 +3880,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
+          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
+          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
+          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg", IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3903,21 +3904,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>“한국형 핵잠 논의 석달째 공회전…특별법부터 제정해야”</t>
+          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592486?sid=101</t>
+          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 16:33:00 +0900</t>
+          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592486_001_20260130114110680.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg", IMAGE("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3927,21 +3928,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>방사청, 방산기업에 ‘생성형 AI 해킹’ 주의 공문발송</t>
+          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002592280?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:38:00 +0900</t>
+          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/01/28/0002592280_001_20260128113809784.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3951,21 +3952,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>한국형 핵추진잠수함(K-SSN), 선택이 아닌 국가 필수 전략...''제도적 뒷...</t>
+          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://www.pinpointnews.co.kr/news/articleView.html?idxno=422526</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:36:00 +0900</t>
+          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png", IMAGE("https://www.pinpointnews.co.kr/image/logo/snslogo_20221006054135.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,21 +462,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E2">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -486,21 +486,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+          <t>Tue, 19 May 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -510,21 +510,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>전북대, 국방사업관리사 교육기관 2년 연속 선정</t>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=839163</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 07:56:00 +0900</t>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -534,21 +534,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>전북대, 방사청 국방사업관리사 교육 2년 연속 선정</t>
+          <t>전북대, 국방사업관리사 교육기관 2년 연속 선정</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2585001</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=839163</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 16:20:00 +0900</t>
+          <t>Sun, 17 May 2026 07:56:00 +0900</t>
         </is>
       </c>
       <c r="E5">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -558,21 +558,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+          <t>전북대, 방사청 국방사업관리사 교육 2년 연속 선정</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+          <t>https://www.etoday.co.kr/news/view/2585001</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+          <t>Fri, 15 May 2026 16:20:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -582,21 +582,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -606,21 +606,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>안도걸 의원, AI 시대 광반도체 국방 활용 세미나 열어</t>
+          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.jeonmae.co.kr/news/articleView.html?idxno=1256767</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 12:56:00 +0900</t>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
       <c r="E8">
-        <f>HYPERLINK("https://www.jeonmae.co.kr/news/thumbnail/202605/1256767_976877_187_v150.jpg", IMAGE("https://www.jeonmae.co.kr/news/thumbnail/202605/1256767_976877_187_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -630,21 +630,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정…방위산...</t>
+          <t>안도걸 의원, AI 시대 광반도체 국방 활용 세미나 열어</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003427957?sid=102</t>
+          <t>https://www.jeonmae.co.kr/news/articleView.html?idxno=1256767</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 12:01:00 +0900</t>
+          <t>Fri, 15 May 2026 12:56:00 +0900</t>
         </is>
       </c>
       <c r="E9">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.jeonmae.co.kr/news/thumbnail/202605/1256767_976877_187_v150.jpg", IMAGE("https://www.jeonmae.co.kr/news/thumbnail/202605/1256767_976877_187_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -654,21 +654,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정…방위산...</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003427957?sid=102</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+          <t>Fri, 15 May 2026 12:01:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -678,21 +678,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>전북대 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=610278</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:18:00 +0900</t>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E11">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -702,21 +702,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>전북대 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=610278</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+          <t>Fri, 15 May 2026 11:18:00 +0900</t>
         </is>
       </c>
       <c r="E12">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -726,21 +726,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E13">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -750,21 +750,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E14">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -774,21 +774,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E15">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -798,21 +798,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E16">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -846,21 +846,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E18">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -870,21 +870,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E19">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -894,21 +894,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -918,21 +918,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -942,21 +942,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -966,22 +966,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
-        </is>
-      </c>
-      <c r="E23">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
-        <v/>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -990,21 +991,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1014,21 +1015,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1038,21 +1039,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1062,21 +1063,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1086,21 +1087,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E28">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1110,21 +1111,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1134,21 +1135,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1158,21 +1159,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E31">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1182,21 +1183,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1206,21 +1207,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>“AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
+          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
+          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1230,21 +1231,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
+          <t>“AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
+          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1254,21 +1255,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>전북대 71억 규모 '첨단인재양성 부트캠프 사업' 선정</t>
+          <t>전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>http://www.veritas-a.com/news/articleView.html?idxno=600409</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 14:34:00 +0900</t>
+          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1278,21 +1279,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>전북대, 첨단산업 인재양성 부트캠프 사업 선정</t>
+          <t>전북대 71억 규모 '첨단인재양성 부트캠프 사업' 선정</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001010129?sid=102</t>
+          <t>http://www.veritas-a.com/news/articleView.html?idxno=600409</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 12:37:00 +0900</t>
+          <t>Wed, 04 Mar 2026 14:34:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1302,21 +1303,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
+          <t>전북대, 첨단산업 인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001010129?sid=102</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
+          <t>Wed, 04 Mar 2026 12:37:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1326,21 +1327,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
+          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
+          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1350,21 +1351,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
+          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
+          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1374,21 +1375,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
+          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
+          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1398,21 +1399,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
+          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1422,21 +1423,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
+          <t>전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
+          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1446,21 +1447,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>http://www.kyosu.net/news/articleView.html?idxno=155230</t>
+          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 21:16:00 +0900</t>
+          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png", IMAGE("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1470,21 +1471,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>전북대, 방산 AI 유니콘 '쉴드 AI'와 협력 추진</t>
+          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=432185</t>
+          <t>http://www.kyosu.net/news/articleView.html?idxno=155230</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 20:08:00 +0900</t>
+          <t>Thu, 15 Jan 2026 21:16:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png", IMAGE("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png"))</f>
         <v/>
       </c>
     </row>
@@ -1494,21 +1495,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>전북대, 글로벌 방산 AI 유니콘 쉴드 AI와 피지컬 AI 협력 추진</t>
+          <t>전북대, 방산 AI 유니콘 '쉴드 AI'와 협력 추진</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202601150086</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=432185</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 19:26:00 +0900</t>
+          <t>Thu, 15 Jan 2026 20:08:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1518,21 +1519,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 체계 구축한다</t>
+          <t>전북대, 글로벌 방산 AI 유니콘 쉴드 AI와 피지컬 AI 협력 추진</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542514</t>
+          <t>https://www.betanews.net/article/view/beta202601150086</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 18:24:00 +0900</t>
+          <t>Thu, 15 Jan 2026 19:26:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1542,21 +1543,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진...피지컬...</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 체계 구축한다</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>http://www.jbsori.com/news/articleView.html?idxno=16762</t>
+          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542514</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:50:00 +0900</t>
+          <t>Thu, 15 Jan 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg", IMAGE("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1566,21 +1567,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진...피지컬...</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
+          <t>http://www.jbsori.com/news/articleView.html?idxno=16762</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
+          <t>Thu, 15 Jan 2026 15:50:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png", IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png"))</f>
+        <f>HYPERLINK("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg", IMAGE("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1590,21 +1591,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.gukjenews.com/news/articleView.html?idxno=3481565</t>
+          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 14:06:00 +0900</t>
+          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png", IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png"))</f>
         <v/>
       </c>
     </row>
@@ -1614,21 +1615,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>http://www.veritas-a.com/news/articleView.html?idxno=594342</t>
+          <t>https://www.gukjenews.com/news/articleView.html?idxno=3481565</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:22:00 +0900</t>
+          <t>Thu, 15 Jan 2026 14:06:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1638,21 +1639,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003390311?sid=102</t>
+          <t>http://www.veritas-a.com/news/articleView.html?idxno=594342</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:12:00 +0900</t>
+          <t>Thu, 15 Jan 2026 12:22:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1662,21 +1663,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003390311?sid=102</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
+          <t>Thu, 15 Jan 2026 12:12:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1686,21 +1687,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력</t>
+          <t>전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=588811</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:36:00 +0900</t>
+          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1710,21 +1711,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
+          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=588811</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
+          <t>Thu, 15 Jan 2026 10:36:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1734,21 +1735,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[상생의 힘, 기업가치를 올린다] 김동관의 한화, 방산 넘어 안보 기업으...</t>
+          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260601151511969112616b072_1</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 19:12:00 +0900</t>
+          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1758,21 +1759,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[상생의 힘, 기업가치를 올린다] 한화, 방산·조선·우주 국가전략산업...</t>
+          <t>한화에어로 참사, 미국·EU 방산 입찰 발목 잡나...'대전 사고' 도마 위</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202606011338107634112616b072_1</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=247498</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 19:08:00 +0900</t>
+          <t>Tue, 02 Jun 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1782,21 +1783,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>‘K-잠수함’ 1만4000km 잠항, 獨 꺾고 60조 잭팟 터뜨릴까</t>
+          <t>반복된 폭발사고…K방산 신뢰도 ‘악영향’</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260601500751</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1302742&amp;inflow=N</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 15:32:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:48:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260602045218", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260602045218"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606021446", IMAGE("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606021446"))</f>
         <v/>
       </c>
     </row>
@@ -1806,22 +1807,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
+          <t>KDDX 보안 감점 공방이 던진 질문…방산 조달 사업의 大원칙은</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/108042</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 17:40:00 +0900</t>
-        </is>
-      </c>
-      <c r="E58">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
-        <v/>
+          <t>Tue, 02 Jun 2026 13:04:00 +0900</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -1830,21 +1832,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
+          <t>[상생의 힘, 기업가치를 올린다] 김동관의 한화, 방산 넘어 안보 기업으...</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
+          <t>https://www.g-enews.com/view.php?ud=20260601151511969112616b072_1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 15:14:00 +0900</t>
+          <t>Mon, 01 Jun 2026 19:12:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1854,21 +1856,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
+          <t>[상생의 힘, 기업가치를 올린다] 한화, 방산·조선·우주 국가전략산업...</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
+          <t>https://www.g-enews.com/view.php?ud=202606011338107634112616b072_1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 17:38:00 +0900</t>
+          <t>Mon, 01 Jun 2026 19:08:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1878,21 +1880,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
+          <t>‘K-잠수함’ 1만4000km 잠항, 獨 꺾고 60조 잭팟 터뜨릴까</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
+          <t>https://www.viva100.com/article/20260601500751</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 15:29:00 +0900</t>
+          <t>Mon, 01 Jun 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260603033214", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260603033214"))</f>
         <v/>
       </c>
     </row>
@@ -1902,21 +1904,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
+          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 10:35:00 +0900</t>
+          <t>Fri, 29 May 2026 17:40:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1926,21 +1928,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
+          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
+          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 17:23:00 +0900</t>
+          <t>Fri, 29 May 2026 15:14:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1950,23 +1952,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
+          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 28 May 2026 17:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E64">
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -1975,21 +1976,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
+          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 18:21:00 +0900</t>
+          <t>Thu, 28 May 2026 15:29:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1999,21 +2000,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
+          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 14:57:00 +0900</t>
+          <t>Thu, 28 May 2026 10:35:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2023,21 +2024,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
+          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
+          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 10:00:00 +0900</t>
+          <t>Wed, 27 May 2026 17:23:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2047,22 +2048,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:56:00 +0900</t>
-        </is>
-      </c>
-      <c r="E68">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
-        <v/>
+          <t>Wed, 27 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -2071,21 +2073,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+          <t>Tue, 26 May 2026 18:21:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2095,21 +2097,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+          <t>Tue, 26 May 2026 14:57:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2119,21 +2121,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:54:00 +0900</t>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2143,21 +2145,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2167,21 +2169,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2191,21 +2193,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
         <v/>
       </c>
     </row>
@@ -2215,23 +2217,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E75">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="76">
@@ -2240,21 +2241,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 15:02:00 +0900</t>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2264,21 +2265,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 11:30:00 +0900</t>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2288,21 +2289,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 06:00:00 +0900</t>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2312,22 +2313,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
-        </is>
-      </c>
-      <c r="E79">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
-        <v/>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -2336,21 +2338,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>“한·일 함정 분야 경쟁 가능성”</t>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2360,21 +2362,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2384,21 +2386,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2408,21 +2410,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2432,21 +2434,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2456,21 +2458,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
+          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2480,21 +2482,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2504,21 +2506,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2528,21 +2530,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2552,21 +2554,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2576,23 +2578,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E90">
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="91">
@@ -2601,21 +2602,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2625,21 +2626,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2649,21 +2650,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2673,22 +2674,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2575581</t>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E94">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
-        <v/>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -2697,21 +2699,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E95">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
         <v/>
       </c>
     </row>
@@ -2721,21 +2723,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2745,21 +2747,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2769,23 +2771,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E98">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="99">
@@ -2794,21 +2795,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>http://amenews.kr/news/view.php?idx=66331</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2818,21 +2819,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2842,21 +2843,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2866,22 +2867,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E102">
-        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
-        <v/>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -2890,21 +2892,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2914,21 +2916,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2938,23 +2940,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
+        </is>
+      </c>
+      <c r="E105">
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="106">
@@ -2963,21 +2964,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2573034</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2987,21 +2988,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3011,23 +3012,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+        </is>
+      </c>
+      <c r="E108">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="109">
@@ -3036,22 +3036,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E109">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
-        <v/>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -3060,21 +3061,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260401154708093</t>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3084,21 +3085,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3108,22 +3109,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2571395</t>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E112">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
-        <v/>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -3132,21 +3134,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
+          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E113">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3156,21 +3158,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3180,21 +3182,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
+          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3204,21 +3206,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
+          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
+          <t>https://www.etoday.co.kr/news/view/2571395</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3228,21 +3230,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
+          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3252,21 +3254,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260326500334</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
+          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3276,21 +3278,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
+          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
+          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260327/thumb1/2026032701000262800025071.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3300,21 +3302,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
+          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3324,21 +3326,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
+          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
+          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3348,21 +3350,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
+          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
+          <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
         <v/>
       </c>
     </row>
@@ -3372,17 +3374,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
+          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
+          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3397,23 +3399,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
+          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+        </is>
+      </c>
+      <c r="E124">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -3422,21 +3423,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
+          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
+          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
+          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
+        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3446,21 +3447,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
+          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
+          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
+          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3470,22 +3471,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
+          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E127">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
-        <v/>
+          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -3494,22 +3496,23 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
+          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
+          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
-        </is>
-      </c>
-      <c r="E128">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
-        <v/>
+          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -3518,21 +3521,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
+          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
+          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3542,23 +3545,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
+          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E130">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="131">
@@ -3567,21 +3569,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
+          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260310153628801</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
+          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3591,21 +3593,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
+          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
+          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
+          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3615,21 +3617,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
+          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
+          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3639,22 +3641,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
+          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E134">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
-        <v/>
+          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -3663,21 +3666,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
+          <t>https://www.ajunews.com/view/20260310153628801</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
+          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3687,21 +3690,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
+          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3711,21 +3714,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
+          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260227150934536</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3735,21 +3738,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3759,21 +3762,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
+          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3783,23 +3786,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E140">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="141">
@@ -3808,21 +3810,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
+          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
+          <t>https://www.ajunews.com/view/20260227150934536</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3832,21 +3834,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
+          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
+          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
+          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3856,21 +3858,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
+          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
+          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3880,22 +3882,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
+          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E144">
-        <f>HYPERLINK("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg", IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -3904,21 +3907,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>&amp;quot;한국형 핵추진잠수함, 단순 무기 아닌 '국가통합관리체계'&amp;quot;</t>
+          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://www.econovill.com/news/articleView.html?idxno=727438</t>
+          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 19:00:00 +0900</t>
+          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg", IMAGE("https://cdn.econovill.com/news/thumbnail/202601/727438_695182_5642_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3928,22 +3931,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>&amp;quot;美핵잠수함 도입, 제독이 32년 총괄… 韓, 특별법 만들어 독립성 줘야...</t>
+          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001126989?sid=100</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:51:00 +0900</t>
-        </is>
-      </c>
-      <c r="E146">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/01/28/0001126989_001_20260128181010337.jpg?type=w800"))</f>
-        <v/>
+          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -3952,21 +3956,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>빗장 풀린 한국형 핵잠수함…&amp;quot;중대 전환점, 특별법 제정 시급&amp;quot;</t>
+          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003053350?sid=101</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 17:45:00 +0900</t>
+          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/01/28/0003053350_001_20260128174511074.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3976,20 +3980,44 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
+          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E148">
+        <f>HYPERLINK("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg", IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
           <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
-      <c r="E148">
+      <c r="E149">
         <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
         <v/>
       </c>
@@ -4126,9 +4154,10 @@
           <t>Mon, 09 Mar 2026 15:56:00 +0900</t>
         </is>
       </c>
-      <c r="E5">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260310/thumb1/BBS_202603100847055860.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/tmplat/upload/20260310/thumb1/BBS_202603100847055860.jpg"))</f>
-        <v/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="6">

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -1759,21 +1759,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>한화에어로 참사, 미국·EU 방산 입찰 발목 잡나...'대전 사고' 도마 위</t>
+          <t>[단독] 4월에 국방과학연구소 합동 안전검사도 못 막은 한화에어로 참사</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=247498</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934274?sid=102</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 16:02:00 +0900</t>
+          <t>Wed, 03 Jun 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260603210510080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260603210510080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1783,21 +1783,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>반복된 폭발사고…K방산 신뢰도 ‘악영향’</t>
+          <t>한화에어로 참사, 미국·EU 방산 입찰 발목 잡나...'대전 사고' 도마 위</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1302742&amp;inflow=N</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=247498</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:48:00 +0900</t>
+          <t>Tue, 02 Jun 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606021446", IMAGE("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606021446"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1807,23 +1807,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KDDX 보안 감점 공방이 던진 질문…방산 조달 사업의 大원칙은</t>
+          <t>반복된 폭발사고…K방산 신뢰도 ‘악영향’</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/108042</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1302742&amp;inflow=N</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 13:04:00 +0900</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 02 Jun 2026 14:48:00 +0900</t>
+        </is>
+      </c>
+      <c r="E58">
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231", IMAGE("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231"))</f>
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -1832,22 +1831,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[상생의 힘, 기업가치를 올린다] 김동관의 한화, 방산 넘어 안보 기업으...</t>
+          <t>KDDX 보안 감점 공방이 던진 질문…방산 조달 사업의 大원칙은</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260601151511969112616b072_1</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/108042</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 19:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E59">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg"))</f>
-        <v/>
+          <t>Tue, 02 Jun 2026 13:04:00 +0900</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -1856,21 +1856,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[상생의 힘, 기업가치를 올린다] 한화, 방산·조선·우주 국가전략산업...</t>
+          <t>[상생의 힘, 기업가치를 올린다] 김동관의 한화, 방산 넘어 안보 기업으...</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202606011338107634112616b072_1</t>
+          <t>https://www.g-enews.com/view.php?ud=20260601151511969112616b072_1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 19:08:00 +0900</t>
+          <t>Mon, 01 Jun 2026 19:12:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1880,21 +1880,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>‘K-잠수함’ 1만4000km 잠항, 獨 꺾고 60조 잭팟 터뜨릴까</t>
+          <t>[상생의 힘, 기업가치를 올린다] 한화, 방산·조선·우주 국가전략산업...</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260601500751</t>
+          <t>https://www.g-enews.com/view.php?ud=202606011338107634112616b072_1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 15:32:00 +0900</t>
+          <t>Mon, 01 Jun 2026 19:08:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260603033214", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260603033214"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1904,21 +1904,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
+          <t>‘K-잠수함’ 1만4000km 잠항, 獨 꺾고 60조 잭팟 터뜨릴까</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
+          <t>https://www.viva100.com/article/20260601500751</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 17:40:00 +0900</t>
+          <t>Mon, 01 Jun 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604034154", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604034154"))</f>
         <v/>
       </c>
     </row>
@@ -1928,21 +1928,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
+          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 15:14:00 +0900</t>
+          <t>Fri, 29 May 2026 17:40:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1952,21 +1952,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
+          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
+          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 17:38:00 +0900</t>
+          <t>Fri, 29 May 2026 15:14:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
+        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1976,21 +1976,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
+          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 15:29:00 +0900</t>
+          <t>Thu, 28 May 2026 17:38:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2000,21 +2000,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
+          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 10:35:00 +0900</t>
+          <t>Thu, 28 May 2026 15:29:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2024,21 +2024,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
+          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 17:23:00 +0900</t>
+          <t>Thu, 28 May 2026 10:35:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2048,23 +2048,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
+          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
+          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 27 May 2026 17:23:00 +0900</t>
+        </is>
+      </c>
+      <c r="E68">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -2073,22 +2072,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
+          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 18:21:00 +0900</t>
-        </is>
-      </c>
-      <c r="E69">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
-        <v/>
+          <t>Wed, 27 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -2097,21 +2097,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
+          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 14:57:00 +0900</t>
+          <t>Tue, 26 May 2026 18:21:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2121,21 +2121,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
+          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 10:00:00 +0900</t>
+          <t>Tue, 26 May 2026 14:57:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2145,21 +2145,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
+        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2169,21 +2169,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2193,21 +2193,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2217,21 +2217,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:54:00 +0900</t>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
         <v/>
       </c>
     </row>
@@ -2241,21 +2241,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2265,21 +2265,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2289,21 +2289,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2313,23 +2313,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+        </is>
+      </c>
+      <c r="E79">
+        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -2338,22 +2337,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 15:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E80">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
-        <v/>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -2362,21 +2362,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 11:30:00 +0900</t>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2386,21 +2386,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 06:00:00 +0900</t>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2410,21 +2410,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2434,21 +2434,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>“한·일 함정 분야 경쟁 가능성”</t>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2458,21 +2458,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2482,21 +2482,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2506,21 +2506,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2530,21 +2530,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2554,21 +2554,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2578,21 +2578,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2602,21 +2602,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2626,21 +2626,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2650,21 +2650,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2674,23 +2674,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E94">
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -2699,22 +2698,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E95">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
-        <v/>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -2723,21 +2723,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
         <v/>
       </c>
     </row>
@@ -2747,21 +2747,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2771,21 +2771,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2575581</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2795,21 +2795,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2843,21 +2843,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2867,23 +2867,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+        </is>
+      </c>
+      <c r="E102">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="103">
@@ -2892,22 +2891,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>http://amenews.kr/news/view.php?idx=66331</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
-        </is>
-      </c>
-      <c r="E103">
-        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
-        <v/>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -2916,21 +2916,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2940,21 +2940,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2964,21 +2964,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2988,21 +2988,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3012,21 +3012,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3036,23 +3036,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+        </is>
+      </c>
+      <c r="E109">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="110">
@@ -3061,21 +3060,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2573034</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <f>HYPERLINK("https://www.businesspost.co.kr/news/photo/202603/20260325115129_24184.jpg", IMAGE("https://www.businesspost.co.kr/news/photo/202603/20260325115129_24184.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3085,21 +3084,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3109,23 +3108,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E112">
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="113">
@@ -3134,22 +3132,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E113">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
-        <v/>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -3158,21 +3157,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260401154708093</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3182,21 +3181,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3206,21 +3205,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
+          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2571395</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3230,21 +3229,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
+          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
+          <t>https://www.etoday.co.kr/news/view/2571395</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3254,21 +3253,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
+          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3278,21 +3277,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
+          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
+          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3302,21 +3301,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
+          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3326,21 +3325,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
+          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3350,21 +3349,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260326500334</t>
+          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
+          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3374,23 +3373,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
+          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
+          <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E123">
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
+        <v/>
       </c>
     </row>
     <row r="124">
@@ -3399,22 +3397,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
+          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
-        </is>
-      </c>
-      <c r="E124">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
-        <v/>
+          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -3423,21 +3422,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
+          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3447,21 +3446,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
+          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
+          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3471,23 +3470,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
+          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
+          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E127">
+        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -3496,17 +3494,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
+          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
+          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -3521,22 +3519,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
+          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
+          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
-        </is>
-      </c>
-      <c r="E129">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
-        <v/>
+          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -3545,21 +3544,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
+          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
+          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E130">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3569,21 +3568,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
+          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
+          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3593,21 +3592,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
+          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3617,21 +3616,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
+          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
+          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
+          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3641,23 +3640,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
+          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E134">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="135">
@@ -3666,22 +3664,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
+          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260310153628801</t>
+          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
-        </is>
-      </c>
-      <c r="E135">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
-        <v/>
+          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -3690,21 +3689,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
+          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
+          <t>https://www.ajunews.com/view/20260310153628801</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
+          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3714,21 +3713,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
+          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
+          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3738,21 +3737,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
+          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3767,16 +3766,16 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
+          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3791,16 +3790,16 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
+          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3810,21 +3809,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260227150934536</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3834,21 +3833,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
+          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
+          <t>https://www.ajunews.com/view/20260227150934536</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3858,21 +3857,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
+          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
+          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
+          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3882,23 +3881,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
+          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E144">
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="145">
@@ -3907,22 +3905,23 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
+          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
-        </is>
-      </c>
-      <c r="E145">
-        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -3931,23 +3930,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
+          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
+          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E146">
+        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="147">
@@ -3956,21 +3954,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
+          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
+          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3980,21 +3978,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>캐나다로 간 정의선·김동관…불붙은 잠수함 수주 경쟁에 마침표 찍을까</t>
+          <t>60조 캐나다 잠수함 수주전···'나토 동맹' 변수되나</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://www.financialpost.co.kr/news/articleView.html?idxno=245902</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2389503</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 05:00:00 +0900</t>
+          <t>Tue, 03 Feb 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E148">
-        <f>HYPERLINK("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg", IMAGE("https://cdn.financialpost.co.kr/news/thumbnail/202601/245902_293444_3931_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202602/2389503_1219270_4041_v150.jpg"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,21 +462,3563 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>** AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E2">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E3">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E4">
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>전북대, 국방사업관리사 교육기관 2년 연속 선정</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=839163</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sun, 17 May 2026 07:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E5">
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>전북대, 방사청 국방사업관리사 교육 2년 연속 선정</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.etoday.co.kr/news/view/2585001</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 16:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E6">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E7">
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+        </is>
+      </c>
+      <c r="E8">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>안도걸 의원, AI 시대 광반도체 국방 활용 세미나 열어</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.jeonmae.co.kr/news/articleView.html?idxno=1256767</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 12:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E9">
+        <f>HYPERLINK("https://www.jeonmae.co.kr/news/thumbnail/202605/1256767_976877_187_v150.jpg", IMAGE("https://www.jeonmae.co.kr/news/thumbnail/202605/1256767_976877_187_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정…방위산...</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/030/0003427957?sid=102</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 12:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E10">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E11">
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>전북대 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=610278</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 11:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E12">
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E14">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+        </is>
+      </c>
+      <c r="E15">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E16">
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+        </is>
+      </c>
+      <c r="E17">
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E18">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+        </is>
+      </c>
+      <c r="E19">
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E20">
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+        </is>
+      </c>
+      <c r="E21">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+        </is>
+      </c>
+      <c r="E22">
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+        </is>
+      </c>
+      <c r="E24">
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E25">
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E26">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E27">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E28">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E29">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E30">
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E31">
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+        </is>
+      </c>
+      <c r="E32">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
+        </is>
+      </c>
+      <c r="E33">
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>“AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
+        </is>
+      </c>
+      <c r="E34">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E35">
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>전북대 71억 규모 '첨단인재양성 부트캠프 사업' 선정</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>http://www.veritas-a.com/news/articleView.html?idxno=600409</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Wed, 04 Mar 2026 14:34:00 +0900</t>
+        </is>
+      </c>
+      <c r="E36">
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>전북대, 첨단산업 인재양성 부트캠프 사업 선정</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/031/0001010129?sid=102</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Wed, 04 Mar 2026 12:37:00 +0900</t>
+        </is>
+      </c>
+      <c r="E37">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E38">
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E39">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E40">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E41">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E42">
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
+        </is>
+      </c>
+      <c r="E43">
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>http://www.kyosu.net/news/articleView.html?idxno=155230</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 21:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E44">
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png", IMAGE("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>전북대, 방산 AI 유니콘 '쉴드 AI'와 협력 추진</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=432185</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 20:08:00 +0900</t>
+        </is>
+      </c>
+      <c r="E45">
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>전북대, 글로벌 방산 AI 유니콘 쉴드 AI와 피지컬 AI 협력 추진</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.betanews.net/article/view/beta202601150086</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 19:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E46">
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 체계 구축한다</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542514</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 18:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E47">
+        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진...피지컬...</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>http://www.jbsori.com/news/articleView.html?idxno=16762</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 15:50:00 +0900</t>
+        </is>
+      </c>
+      <c r="E48">
+        <f>HYPERLINK("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg", IMAGE("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
+        </is>
+      </c>
+      <c r="E49">
+        <f>HYPERLINK("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png", IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.gukjenews.com/news/articleView.html?idxno=3481565</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 14:06:00 +0900</t>
+        </is>
+      </c>
+      <c r="E50">
+        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>http://www.veritas-a.com/news/articleView.html?idxno=594342</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 12:22:00 +0900</t>
+        </is>
+      </c>
+      <c r="E51">
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/030/0003390311?sid=102</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 12:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E52">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
+        </is>
+      </c>
+      <c r="E53">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://news.unn.net/news/articleView.html?idxno=588811</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 10:36:00 +0900</t>
+        </is>
+      </c>
+      <c r="E54">
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E55">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>배틀그라운드 기술이 전장으로...K-방산, 게임사와 'AI 전쟁' 준비한다</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.newsquest.co.kr/news/articleView.html?idxno=267287</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 15:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E56">
+        <f>HYPERLINK("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg", IMAGE("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>[단독] 4월에 국방과학연구소 합동 안전검사도 못 막은 한화에어로 참사</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/469/0000934274?sid=102</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 17:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E57">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>한화에어로 참사, 미국·EU 방산 입찰 발목 잡나...'대전 사고' 도마 위</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=247498</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Tue, 02 Jun 2026 16:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E58">
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>반복된 폭발사고…K방산 신뢰도 ‘악영향’</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1302742&amp;inflow=N</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Tue, 02 Jun 2026 14:48:00 +0900</t>
+        </is>
+      </c>
+      <c r="E59">
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231", IMAGE("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>KDDX 보안 감점 공방이 던진 질문…방산 조달 사업의 大원칙은</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/108042</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Tue, 02 Jun 2026 13:04:00 +0900</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>[상생의 힘, 기업가치를 올린다] 김동관의 한화, 방산 넘어 안보 기업으...</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.g-enews.com/view.php?ud=20260601151511969112616b072_1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 19:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E61">
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>[상생의 힘, 기업가치를 올린다] 한화, 방산·조선·우주 국가전략산업...</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.g-enews.com/view.php?ud=202606011338107634112616b072_1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 19:08:00 +0900</t>
+        </is>
+      </c>
+      <c r="E62">
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>‘K-잠수함’ 1만4000km 잠항, 獨 꺾고 60조 잭팟 터뜨릴까</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.viva100.com/article/20260601500751</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 15:32:00 +0900</t>
+        </is>
+      </c>
+      <c r="E63">
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604154701", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604154701"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 17:40:00 +0900</t>
+        </is>
+      </c>
+      <c r="E64">
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 15:14:00 +0900</t>
+        </is>
+      </c>
+      <c r="E65">
+        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 17:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E66">
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 15:29:00 +0900</t>
+        </is>
+      </c>
+      <c r="E67">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 10:35:00 +0900</t>
+        </is>
+      </c>
+      <c r="E68">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 17:23:00 +0900</t>
+        </is>
+      </c>
+      <c r="E69">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Tue, 26 May 2026 18:21:00 +0900</t>
+        </is>
+      </c>
+      <c r="E71">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Tue, 26 May 2026 14:57:00 +0900</t>
+        </is>
+      </c>
+      <c r="E72">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E73">
+        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E74">
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E75">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E76">
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E77">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E78">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E79">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+        </is>
+      </c>
+      <c r="E80">
+        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E82">
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E83">
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E84">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E85">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+        </is>
+      </c>
+      <c r="E86">
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+        </is>
+      </c>
+      <c r="E87">
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E88">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+        </is>
+      </c>
+      <c r="E89">
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E90">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E91">
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E92">
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E93">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E94">
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E95">
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E97">
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E98">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E99">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E100">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E101">
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E102">
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+        </is>
+      </c>
+      <c r="E103">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E105">
+        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
+        </is>
+      </c>
+      <c r="E106">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
+        </is>
+      </c>
+      <c r="E107">
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E108">
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E109">
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+        </is>
+      </c>
+      <c r="E110">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E112">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E113">
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E115">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E116">
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E117">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://www.etoday.co.kr/news/view/2571395</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E118">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E119">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
+        </is>
+      </c>
+      <c r="E120">
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E121">
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E122">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+        </is>
+      </c>
+      <c r="E123">
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
           <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="E124">
         <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+        </is>
+      </c>
+      <c r="E126">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E127">
+        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E128">
+        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
+        </is>
+      </c>
+      <c r="E131">
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E132">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E133">
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+        </is>
+      </c>
+      <c r="E134">
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E135">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://www.ajunews.com/view/20260310153628801</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
+        </is>
+      </c>
+      <c r="E137">
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E138">
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E139">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E140">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
+        </is>
+      </c>
+      <c r="E141">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E142">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://www.ajunews.com/view/20260227150934536</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+        </is>
+      </c>
+      <c r="E143">
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E144">
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E145">
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E147">
+        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E149">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -491,7 +4033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,23 +4069,143 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>** [특별기고·전북대 장원준 교수] AI·첨단기술 기반 ‘스마트 강군’ 육...</t>
+          <t>K방산 수출, 이제는 정보다 [기고]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>https://n.news.naver.com/mnews/article/469/0000927039?sid=110</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Thu, 23 Apr 2026 04:31:00 +0900</t>
+        </is>
+      </c>
+      <c r="E2">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>전쟁은 '생산능력'이다 : 미국의 무기 부족이 던지는 경고[기고]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://news.mtn.co.kr/news-detail/2026042014032324372</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mon, 20 Apr 2026 14:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E3">
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>첨단항공엔진, 지금 시작하지 않으면 골든타임 놓친다 [기고]</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://news.mtn.co.kr/news-detail/2026033015455091764</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 15:52:00 +0900</t>
+        </is>
+      </c>
+      <c r="E4">
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[특별기고·전북대 장원준 교수] AI·첨단기술 기반 ‘스마트 강군’ 육...</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>https://kookbang.dema.mil.kr/newsWeb/20260309/3/ATCE_CTGR_0020040016/view.do</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Mon, 09 Mar 2026 15:56:00 +0900</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>이미지 없음</t>
         </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[기고] K방산 롱런의 조건 '현지 생산'</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/009/0005646852?sid=110</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sun, 08 Mar 2026 17:19:00 +0900</t>
+        </is>
+      </c>
+      <c r="E6">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/009/2026/03/08/0005646852_001_20260308175312269.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/009/2026/03/08/0005646852_001_20260308175312269.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>가성비 전쟁 시대, 한국은 준비됐나 [기고]</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://news.mtn.co.kr/news-detail/2026030610261598884</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fri, 06 Mar 2026 10:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E7">
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/06/2026030610261598884_00_643.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/06/2026030610261598884_00_643.jpg"))</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,21 +630,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>안도걸 의원, AI 시대 광반도체 국방 활용 세미나 열어</t>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정…방위산...</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.jeonmae.co.kr/news/articleView.html?idxno=1256767</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003427957?sid=102</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 12:56:00 +0900</t>
+          <t>Fri, 15 May 2026 12:01:00 +0900</t>
         </is>
       </c>
       <c r="E9">
-        <f>HYPERLINK("https://www.jeonmae.co.kr/news/thumbnail/202605/1256767_976877_187_v150.jpg", IMAGE("https://www.jeonmae.co.kr/news/thumbnail/202605/1256767_976877_187_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -654,21 +654,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정…방위산...</t>
+          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003427957?sid=102</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 12:01:00 +0900</t>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -678,21 +678,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>전북대 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=610278</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+          <t>Fri, 15 May 2026 11:18:00 +0900</t>
         </is>
       </c>
       <c r="E11">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -702,21 +702,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>전북대 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=610278</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:18:00 +0900</t>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E12">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -726,21 +726,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E13">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -750,21 +750,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E14">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -774,21 +774,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E15">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -798,21 +798,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E16">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -846,21 +846,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E18">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -870,21 +870,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E19">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -894,21 +894,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -918,21 +918,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -942,22 +942,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
-        </is>
-      </c>
-      <c r="E22">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
-        <v/>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -966,23 +967,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+        </is>
+      </c>
+      <c r="E23">
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -991,21 +991,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1015,21 +1015,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1039,21 +1039,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1063,21 +1063,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1087,21 +1087,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E28">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1111,21 +1111,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1135,21 +1135,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1159,21 +1159,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E31">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1183,21 +1183,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1207,21 +1207,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
+          <t>“AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
+          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1231,21 +1231,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>“AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
+          <t>전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
+          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1255,21 +1255,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
+          <t>전북대 71억 규모 '첨단인재양성 부트캠프 사업' 선정</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
+          <t>http://www.veritas-a.com/news/articleView.html?idxno=600409</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
+          <t>Wed, 04 Mar 2026 14:34:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1279,21 +1279,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>전북대 71억 규모 '첨단인재양성 부트캠프 사업' 선정</t>
+          <t>전북대, 첨단산업 인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>http://www.veritas-a.com/news/articleView.html?idxno=600409</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001010129?sid=102</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 14:34:00 +0900</t>
+          <t>Wed, 04 Mar 2026 12:37:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1303,21 +1303,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>전북대, 첨단산업 인재양성 부트캠프 사업 선정</t>
+          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001010129?sid=102</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 12:37:00 +0900</t>
+          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1327,21 +1327,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
+          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
+          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1351,21 +1351,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
+          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
+          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1375,21 +1375,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
+          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
+          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1399,21 +1399,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
+          <t>전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
+          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1423,21 +1423,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
+          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
+          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1447,21 +1447,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
+          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
+          <t>http://www.kyosu.net/news/articleView.html?idxno=155230</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
+          <t>Thu, 15 Jan 2026 21:16:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png", IMAGE("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png"))</f>
         <v/>
       </c>
     </row>
@@ -1471,21 +1471,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, 방산 AI 유니콘 '쉴드 AI'와 협력 추진</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>http://www.kyosu.net/news/articleView.html?idxno=155230</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=432185</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 21:16:00 +0900</t>
+          <t>Thu, 15 Jan 2026 20:08:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png", IMAGE("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1495,21 +1495,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>전북대, 방산 AI 유니콘 '쉴드 AI'와 협력 추진</t>
+          <t>전북대, 글로벌 방산 AI 유니콘 쉴드 AI와 피지컬 AI 협력 추진</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=432185</t>
+          <t>https://www.betanews.net/article/view/beta202601150086</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 20:08:00 +0900</t>
+          <t>Thu, 15 Jan 2026 19:26:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1519,21 +1519,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>전북대, 글로벌 방산 AI 유니콘 쉴드 AI와 피지컬 AI 협력 추진</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 체계 구축한다</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202601150086</t>
+          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542514</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 19:26:00 +0900</t>
+          <t>Thu, 15 Jan 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg"))</f>
+        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1543,21 +1543,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 체계 구축한다</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진...피지컬...</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542514</t>
+          <t>http://www.jbsori.com/news/articleView.html?idxno=16762</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 18:24:00 +0900</t>
+          <t>Thu, 15 Jan 2026 15:50:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg", IMAGE("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1567,21 +1567,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진...피지컬...</t>
+          <t>전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>http://www.jbsori.com/news/articleView.html?idxno=16762</t>
+          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:50:00 +0900</t>
+          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg", IMAGE("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png", IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png"))</f>
         <v/>
       </c>
     </row>
@@ -1591,21 +1591,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
+          <t>https://www.gukjenews.com/news/articleView.html?idxno=3481565</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
+          <t>Thu, 15 Jan 2026 14:06:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png", IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png"))</f>
+        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1615,21 +1615,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.gukjenews.com/news/articleView.html?idxno=3481565</t>
+          <t>http://www.veritas-a.com/news/articleView.html?idxno=594342</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 14:06:00 +0900</t>
+          <t>Thu, 15 Jan 2026 12:22:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1639,21 +1639,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>http://www.veritas-a.com/news/articleView.html?idxno=594342</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003390311?sid=102</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:22:00 +0900</t>
+          <t>Thu, 15 Jan 2026 12:12:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1663,21 +1663,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003390311?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:12:00 +0900</t>
+          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1687,21 +1687,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
+          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=588811</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
+          <t>Thu, 15 Jan 2026 10:36:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1711,21 +1711,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력</t>
+          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=588811</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:36:00 +0900</t>
+          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1735,21 +1735,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
+          <t>배틀그라운드 기술이 전장으로...K-방산, 게임사와 'AI 전쟁' 준비한다</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
+          <t>https://www.newsquest.co.kr/news/articleView.html?idxno=267287</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
+          <t>Thu, 04 Jun 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg", IMAGE("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1759,21 +1759,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>배틀그라운드 기술이 전장으로...K-방산, 게임사와 'AI 전쟁' 준비한다</t>
+          <t>[단독] 4월에 국방과학연구소 합동 안전검사도 못 막은 한화에어로 참사</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.newsquest.co.kr/news/articleView.html?idxno=267287</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934274?sid=102</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Thu, 04 Jun 2026 15:00:00 +0900</t>
+          <t>Wed, 03 Jun 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg", IMAGE("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1783,21 +1783,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[단독] 4월에 국방과학연구소 합동 안전검사도 못 막은 한화에어로 참사</t>
+          <t>한화에어로 참사, 미국·EU 방산 입찰 발목 잡나...'대전 사고' 도마 위</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934274?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=247498</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 03 Jun 2026 17:01:00 +0900</t>
+          <t>Tue, 02 Jun 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1807,21 +1807,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>한화에어로 참사, 미국·EU 방산 입찰 발목 잡나...'대전 사고' 도마 위</t>
+          <t>반복된 폭발사고…K방산 신뢰도 ‘악영향’</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=247498</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1302742&amp;inflow=N</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 16:02:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:48:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231", IMAGE("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231"))</f>
         <v/>
       </c>
     </row>
@@ -1831,22 +1831,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>반복된 폭발사고…K방산 신뢰도 ‘악영향’</t>
+          <t>KDDX 보안 감점 공방이 던진 질문…방산 조달 사업의 大원칙은</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1302742&amp;inflow=N</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/108042</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:48:00 +0900</t>
-        </is>
-      </c>
-      <c r="E59">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231", IMAGE("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231"))</f>
-        <v/>
+          <t>Tue, 02 Jun 2026 13:04:00 +0900</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -1855,23 +1856,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KDDX 보안 감점 공방이 던진 질문…방산 조달 사업의 大원칙은</t>
+          <t>[상생의 힘, 기업가치를 올린다] 김동관의 한화, 방산 넘어 안보 기업으...</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/108042</t>
+          <t>https://www.g-enews.com/view.php?ud=20260601151511969112616b072_1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 13:04:00 +0900</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 01 Jun 2026 19:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E60">
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -1880,21 +1880,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[상생의 힘, 기업가치를 올린다] 김동관의 한화, 방산 넘어 안보 기업으...</t>
+          <t>[상생의 힘, 기업가치를 올린다] 한화, 방산·조선·우주 국가전략산업...</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260601151511969112616b072_1</t>
+          <t>https://www.g-enews.com/view.php?ud=202606011338107634112616b072_1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 19:12:00 +0900</t>
+          <t>Mon, 01 Jun 2026 19:08:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1904,21 +1904,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[상생의 힘, 기업가치를 올린다] 한화, 방산·조선·우주 국가전략산업...</t>
+          <t>‘K-잠수함’ 1만4000km 잠항, 獨 꺾고 60조 잭팟 터뜨릴까</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202606011338107634112616b072_1</t>
+          <t>https://www.viva100.com/article/20260601500751</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 19:08:00 +0900</t>
+          <t>Mon, 01 Jun 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604160127", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604160127"))</f>
         <v/>
       </c>
     </row>
@@ -1928,21 +1928,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>‘K-잠수함’ 1만4000km 잠항, 獨 꺾고 60조 잭팟 터뜨릴까</t>
+          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260601500751</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 15:32:00 +0900</t>
+          <t>Fri, 29 May 2026 17:40:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604154701", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604154701"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1952,21 +1952,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
+          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
+          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 17:40:00 +0900</t>
+          <t>Fri, 29 May 2026 15:14:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
+        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1976,21 +1976,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
+          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 15:14:00 +0900</t>
+          <t>Thu, 28 May 2026 17:38:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2000,21 +2000,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
+          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 17:38:00 +0900</t>
+          <t>Thu, 28 May 2026 15:29:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2024,21 +2024,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
+          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 15:29:00 +0900</t>
+          <t>Thu, 28 May 2026 10:35:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2048,21 +2048,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
+          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 10:35:00 +0900</t>
+          <t>Wed, 27 May 2026 17:23:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2072,22 +2072,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
+          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
+          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 17:23:00 +0900</t>
-        </is>
-      </c>
-      <c r="E69">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
-        <v/>
+          <t>Wed, 27 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -2096,23 +2097,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
+          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 26 May 2026 18:21:00 +0900</t>
+        </is>
+      </c>
+      <c r="E70">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -2121,21 +2121,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
+          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 18:21:00 +0900</t>
+          <t>Tue, 26 May 2026 14:57:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2145,21 +2145,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 14:57:00 +0900</t>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2169,21 +2169,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 10:00:00 +0900</t>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2193,21 +2193,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2217,21 +2217,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
         <v/>
       </c>
     </row>
@@ -2241,21 +2241,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2265,21 +2265,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:54:00 +0900</t>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2289,21 +2289,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2313,21 +2313,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2337,22 +2337,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 16:58:00 +0900</t>
-        </is>
-      </c>
-      <c r="E80">
-        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -2361,23 +2362,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E81">
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="82">
@@ -2386,21 +2386,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 15:02:00 +0900</t>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2410,21 +2410,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 11:30:00 +0900</t>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2434,21 +2434,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 06:00:00 +0900</t>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2458,21 +2458,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2482,21 +2482,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>“한·일 함정 분야 경쟁 가능성”</t>
+          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2506,21 +2506,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2530,21 +2530,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2554,21 +2554,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2578,21 +2578,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2602,21 +2602,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2626,21 +2626,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2650,21 +2650,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2674,21 +2674,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2698,22 +2698,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E95">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
-        <v/>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -2722,23 +2723,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E96">
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -2747,21 +2747,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2771,21 +2771,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2795,21 +2795,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2819,21 +2819,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2575581</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2867,21 +2867,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2891,22 +2891,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
-        </is>
-      </c>
-      <c r="E103">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -2915,17 +2916,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -2940,21 +2941,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>http://amenews.kr/news/view.php?idx=66331</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2964,21 +2965,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2988,21 +2989,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3012,21 +3013,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3036,21 +3037,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3060,22 +3061,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
-        </is>
-      </c>
-      <c r="E110">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
-        <v/>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -3084,23 +3086,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E111">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="112">
@@ -3109,21 +3110,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2573034</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
         </is>
       </c>
       <c r="E112">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3133,22 +3134,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E113">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
-        <v/>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -3157,23 +3159,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E114">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="115">
@@ -3182,21 +3183,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3206,21 +3207,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260401154708093</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3230,21 +3231,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+          <t>https://www.etoday.co.kr/news/view/2571395</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3254,21 +3255,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
+          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2571395</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3278,21 +3279,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
+          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
+          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3302,21 +3303,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
+          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
+          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3326,21 +3327,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
+          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
+          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3350,21 +3351,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
+          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3374,21 +3375,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
+          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
+          <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
         <v/>
       </c>
     </row>
@@ -3398,22 +3399,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260326500334</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
-        </is>
-      </c>
-      <c r="E124">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
-        <v/>
+          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -3422,23 +3424,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
+          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+        </is>
+      </c>
+      <c r="E125">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="126">
@@ -3447,21 +3448,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
+          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
+          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3471,21 +3472,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
+          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
+          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3495,22 +3496,23 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
+          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E128">
-        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
-        <v/>
+          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -3519,17 +3521,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
+          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
+          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
+          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -3544,23 +3546,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
+          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
+        </is>
+      </c>
+      <c r="E130">
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="131">
@@ -3569,21 +3570,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
+          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
+          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3593,21 +3594,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
+          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
+          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3617,21 +3618,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
+          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
+          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
+          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3641,21 +3642,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
+          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3665,22 +3666,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
+          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
+          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E135">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
-        <v/>
+          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -3689,23 +3691,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
+          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
+          <t>https://www.ajunews.com/view/20260310153628801</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
+        </is>
+      </c>
+      <c r="E136">
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="137">
@@ -3714,21 +3715,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
+          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260310153628801</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
+          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3738,21 +3739,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
+          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
+          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3762,21 +3763,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
+          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3791,16 +3792,16 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
+          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3815,16 +3816,16 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
+          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3834,21 +3835,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
+          <t>https://www.ajunews.com/view/20260227150934536</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
+          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3858,21 +3859,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
+          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260227150934536</t>
+          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3882,21 +3883,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
+          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3906,22 +3907,23 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
+          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E145">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
-        <v/>
+          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -3930,23 +3932,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
+          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
+          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E146">
+        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="147">
@@ -3955,21 +3956,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
+          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3979,45 +3980,20 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
+          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
           <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
-      <c r="E149">
+      <c r="E148">
         <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
         <v/>
       </c>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604160127", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604160127"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604161552", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604161552"))</f>
         <v/>
       </c>
     </row>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2843,12 +2843,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[특별기고·전북대 장원준 교수] AI·첨단기술 기반 ‘스마트 강군’ 육...</t>
+          <t>** [특별기고·전북대 장원준 교수] AI·첨단기술 기반 ‘스마트 강군’ 육...</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -462,21 +462,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
+          <t>** 전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
         </is>
       </c>
       <c r="E2">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -486,21 +486,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+          <t>** 전북대, 국방사업관리사 교육기관 2년 연속 선정</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=839163</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+          <t>Sun, 17 May 2026 07:56:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -510,21 +510,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>** 전북대, 방사청 국방사업관리사 교육 2년 연속 선정</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+          <t>https://www.etoday.co.kr/news/view/2585001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+          <t>Fri, 15 May 2026 16:20:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -534,21 +534,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>전북대, 국방사업관리사 교육기관 2년 연속 선정</t>
+          <t>** '방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=839163</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 07:56:00 +0900</t>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
         </is>
       </c>
       <c r="E5">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -558,21 +558,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전북대, 방사청 국방사업관리사 교육 2년 연속 선정</t>
+          <t>** “방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2585001</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 16:20:00 +0900</t>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -582,21 +582,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+          <t>** 전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정…방위산...</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003427957?sid=102</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+          <t>Fri, 15 May 2026 12:01:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -606,21 +606,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+          <t>** 전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E8">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -630,21 +630,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정…방위산...</t>
+          <t>** 전북대 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003427957?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=610278</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 12:01:00 +0900</t>
+          <t>Fri, 15 May 2026 11:18:00 +0900</t>
         </is>
       </c>
       <c r="E9">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -654,21 +654,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>** 전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -678,21 +678,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>전북대 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>** 전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=610278</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:18:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E11">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -702,21 +702,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>** 피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E12">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -726,21 +726,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>** 전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E13">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -750,21 +750,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>** 전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E14">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -774,21 +774,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>** 전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E15">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -798,21 +798,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>** 전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
         </is>
       </c>
       <c r="E16">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>** “AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -846,21 +846,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>** 전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E18">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -870,21 +870,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>** 전북대 71억 규모 '첨단인재양성 부트캠프 사업' 선정</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>http://www.veritas-a.com/news/articleView.html?idxno=600409</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Wed, 04 Mar 2026 14:34:00 +0900</t>
         </is>
       </c>
       <c r="E19">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -894,21 +894,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>** 전북대, 첨단산업 인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001010129?sid=102</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Wed, 04 Mar 2026 12:37:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -918,21 +918,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>** 전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -942,23 +942,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>** 전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
+        </is>
+      </c>
+      <c r="E22">
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -967,21 +966,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>** 전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>http://www.kyosu.net/news/articleView.html?idxno=155230</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+          <t>Thu, 15 Jan 2026 21:16:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png", IMAGE("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png"))</f>
         <v/>
       </c>
     </row>
@@ -991,21 +990,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>** 전북대, 방산 AI 유니콘 '쉴드 AI'와 협력 추진</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=432185</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Thu, 15 Jan 2026 20:08:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1015,21 +1014,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>** 전북대, 글로벌 방산 AI 유니콘 쉴드 AI와 피지컬 AI 협력 추진</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>https://www.betanews.net/article/view/beta202601150086</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 15 Jan 2026 19:26:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1039,21 +1038,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>** 전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 체계 구축한다</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542514</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Thu, 15 Jan 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1063,21 +1062,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>** 전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진...피지컬...</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>http://www.jbsori.com/news/articleView.html?idxno=16762</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Thu, 15 Jan 2026 15:50:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg", IMAGE("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1087,21 +1086,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>** 전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
         </is>
       </c>
       <c r="E28">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png", IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png"))</f>
         <v/>
       </c>
     </row>
@@ -1111,21 +1110,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>** 전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://www.gukjenews.com/news/articleView.html?idxno=3481565</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Thu, 15 Jan 2026 14:06:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1135,21 +1134,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>** 전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>http://www.veritas-a.com/news/articleView.html?idxno=594342</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Thu, 15 Jan 2026 12:22:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1159,21 +1158,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>** 전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003390311?sid=102</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Thu, 15 Jan 2026 12:12:00 +0900</t>
         </is>
       </c>
       <c r="E31">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1183,21 +1182,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
+          <t>** 전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
+          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1207,21 +1206,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>“AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
+          <t>** 전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=588811</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
+          <t>Thu, 15 Jan 2026 10:36:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1231,21 +1230,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
+          <t>** 'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1255,21 +1254,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>전북대 71억 규모 '첨단인재양성 부트캠프 사업' 선정</t>
+          <t>** 전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>http://www.veritas-a.com/news/articleView.html?idxno=600409</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 14:34:00 +0900</t>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1279,21 +1278,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>전북대, 첨단산업 인재양성 부트캠프 사업 선정</t>
+          <t>** 전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001010129?sid=102</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 12:37:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1303,21 +1302,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
+          <t>** 전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1327,21 +1326,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
+          <t>** 전북대-한화시스템 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1351,21 +1350,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
+          <t>** 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1375,21 +1374,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
+          <t>** [단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1399,21 +1398,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1423,21 +1422,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
+          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
+          <t>Tue, 19 May 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1447,21 +1446,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>http://www.kyosu.net/news/articleView.html?idxno=155230</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 21:16:00 +0900</t>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png", IMAGE("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1471,21 +1470,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>전북대, 방산 AI 유니콘 '쉴드 AI'와 협력 추진</t>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=432185</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 20:08:00 +0900</t>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1495,21 +1494,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>전북대, 글로벌 방산 AI 유니콘 쉴드 AI와 피지컬 AI 협력 추진</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202601150086</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 19:26:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1519,21 +1518,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 체계 구축한다</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542514</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 18:24:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1543,21 +1542,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진...피지컬...</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>http://www.jbsori.com/news/articleView.html?idxno=16762</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:50:00 +0900</t>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg", IMAGE("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1567,21 +1566,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png", IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1591,21 +1590,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.gukjenews.com/news/articleView.html?idxno=3481565</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 14:06:00 +0900</t>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1615,22 +1614,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>http://www.veritas-a.com/news/articleView.html?idxno=594342</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:22:00 +0900</t>
-        </is>
-      </c>
-      <c r="E50">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg"))</f>
-        <v/>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -1639,21 +1639,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003390311?sid=102</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:12:00 +0900</t>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1663,21 +1663,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1687,21 +1687,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=588811</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:36:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1711,21 +1711,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1735,21 +1735,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>배틀그라운드 기술이 전장으로...K-방산, 게임사와 'AI 전쟁' 준비한다</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.newsquest.co.kr/news/articleView.html?idxno=267287</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Thu, 04 Jun 2026 15:00:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg", IMAGE("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1759,21 +1759,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[단독] 4월에 국방과학연구소 합동 안전검사도 못 막은 한화에어로 참사</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934274?sid=102</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 03 Jun 2026 17:01:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1783,21 +1783,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>한화에어로 참사, 미국·EU 방산 입찰 발목 잡나...'대전 사고' 도마 위</t>
+          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=247498</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 16:02:00 +0900</t>
+          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1807,21 +1807,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>반복된 폭발사고…K방산 신뢰도 ‘악영향’</t>
+          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1302742&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:48:00 +0900</t>
+          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231", IMAGE("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1831,23 +1831,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KDDX 보안 감점 공방이 던진 질문…방산 조달 사업의 大원칙은</t>
+          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/108042</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 13:04:00 +0900</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E59">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -1856,21 +1855,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[상생의 힘, 기업가치를 올린다] 김동관의 한화, 방산 넘어 안보 기업으...</t>
+          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260601151511969112616b072_1</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 19:12:00 +0900</t>
+          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1880,21 +1879,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[상생의 힘, 기업가치를 올린다] 한화, 방산·조선·우주 국가전략산업...</t>
+          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202606011338107634112616b072_1</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 19:08:00 +0900</t>
+          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1904,21 +1903,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>‘K-잠수함’ 1만4000km 잠항, 獨 꺾고 60조 잭팟 터뜨릴까</t>
+          <t>배틀그라운드 기술이 전장으로...K-방산, 게임사와 'AI 전쟁' 준비한다</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260601500751</t>
+          <t>https://www.newsquest.co.kr/news/articleView.html?idxno=267287</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 15:32:00 +0900</t>
+          <t>Thu, 04 Jun 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604161552", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604161552"))</f>
+        <f>HYPERLINK("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg", IMAGE("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1928,21 +1927,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
+          <t>[단독] 4월에 국방과학연구소 합동 안전검사도 못 막은 한화에어로 참사</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934274?sid=102</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 17:40:00 +0900</t>
+          <t>Wed, 03 Jun 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1952,21 +1951,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
+          <t>한화에어로 참사, 미국·EU 방산 입찰 발목 잡나...'대전 사고' 도마 위</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=247498</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 15:14:00 +0900</t>
+          <t>Tue, 02 Jun 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1976,21 +1975,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
+          <t>반복된 폭발사고…K방산 신뢰도 ‘악영향’</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1302742&amp;inflow=N</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 17:38:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:48:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231", IMAGE("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231"))</f>
         <v/>
       </c>
     </row>
@@ -2000,22 +1999,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
+          <t>KDDX 보안 감점 공방이 던진 질문…방산 조달 사업의 大원칙은</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/108042</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 15:29:00 +0900</t>
-        </is>
-      </c>
-      <c r="E66">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 02 Jun 2026 13:04:00 +0900</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -2024,21 +2024,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
+          <t>[상생의 힘, 기업가치를 올린다] 김동관의 한화, 방산 넘어 안보 기업으...</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=20260601151511969112616b072_1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 10:35:00 +0900</t>
+          <t>Mon, 01 Jun 2026 19:12:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2048,21 +2048,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
+          <t>[상생의 힘, 기업가치를 올린다] 한화, 방산·조선·우주 국가전략산업...</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
+          <t>https://www.g-enews.com/view.php?ud=202606011338107634112616b072_1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 17:23:00 +0900</t>
+          <t>Mon, 01 Jun 2026 19:08:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2072,23 +2072,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
+          <t>‘K-잠수함’ 1만4000km 잠항, 獨 꺾고 60조 잭팟 터뜨릴까</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
+          <t>https://www.viva100.com/article/20260601500751</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 01 Jun 2026 15:32:00 +0900</t>
+        </is>
+      </c>
+      <c r="E69">
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604162610", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604162610"))</f>
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -2097,21 +2096,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
+          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 18:21:00 +0900</t>
+          <t>Fri, 29 May 2026 17:40:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2121,21 +2120,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
+          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
+          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 14:57:00 +0900</t>
+          <t>Fri, 29 May 2026 15:14:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2145,21 +2144,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
+          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 10:00:00 +0900</t>
+          <t>Thu, 28 May 2026 17:38:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2169,21 +2168,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+          <t>Thu, 28 May 2026 15:29:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2193,21 +2192,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+          <t>Thu, 28 May 2026 10:35:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2217,21 +2216,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+          <t>Wed, 27 May 2026 17:23:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2241,22 +2240,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:54:00 +0900</t>
-        </is>
-      </c>
-      <c r="E76">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
-        <v/>
+          <t>Wed, 27 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -2265,21 +2265,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+          <t>Tue, 26 May 2026 18:21:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2289,21 +2289,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+          <t>Tue, 26 May 2026 14:57:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2313,21 +2313,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2337,23 +2337,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E80">
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -2362,21 +2361,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 15:02:00 +0900</t>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2386,21 +2385,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 11:30:00 +0900</t>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
         <v/>
       </c>
     </row>
@@ -2410,21 +2409,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 06:00:00 +0900</t>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2434,21 +2433,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2458,21 +2457,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>“한·일 함정 분야 경쟁 가능성”</t>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2482,21 +2481,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2506,22 +2505,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E87">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
-        <v/>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -2530,21 +2530,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2554,21 +2554,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2578,21 +2578,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>전북대-한화시스템 첨단 방산기술 협력 본격화</t>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2602,21 +2602,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2626,21 +2626,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2650,21 +2650,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2674,21 +2674,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2698,23 +2698,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E95">
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="96">
@@ -2723,21 +2722,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2747,22 +2746,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E97">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -2771,21 +2771,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
         <v/>
       </c>
     </row>
@@ -2795,21 +2795,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2575581</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2819,21 +2819,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2843,21 +2843,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2867,21 +2867,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2891,23 +2891,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E103">
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="104">
@@ -2916,23 +2915,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>http://amenews.kr/news/view.php?idx=66331</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+        </is>
+      </c>
+      <c r="E104">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="105">
@@ -2941,22 +2939,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
-        </is>
-      </c>
-      <c r="E105">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -2965,22 +2964,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
-        </is>
-      </c>
-      <c r="E106">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
-        <v/>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -2989,21 +2989,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3013,21 +3013,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3037,21 +3037,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3061,23 +3061,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E110">
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="111">
@@ -3086,21 +3085,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2573034</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3110,22 +3109,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E112">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
-        <v/>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -3134,23 +3134,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E113">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="114">
@@ -3159,21 +3158,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3183,22 +3182,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260401154708093</t>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E115">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
-        <v/>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -3207,21 +3207,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4045,22 +4045,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>K방산 수출, 이제는 정보다 [기고]</t>
+          <t>** [특별기고·전북대 장원준 교수] AI·첨단기술 기반 ‘스마트 강군’ 육...</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000927039?sid=110</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260309/3/ATCE_CTGR_0020040016/view.do</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 04:31:00 +0900</t>
-        </is>
-      </c>
-      <c r="E2">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800"))</f>
-        <v/>
+          <t>Mon, 09 Mar 2026 15:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -4069,21 +4070,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>전쟁은 '생산능력'이다 : 미국의 무기 부족이 던지는 경고[기고]</t>
+          <t>K방산 수출, 이제는 정보다 [기고]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026042014032324372</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000927039?sid=110</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 14:12:00 +0900</t>
+          <t>Thu, 23 Apr 2026 04:31:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4093,21 +4094,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>첨단항공엔진, 지금 시작하지 않으면 골든타임 놓친다 [기고]</t>
+          <t>전쟁은 '생산능력'이다 : 미국의 무기 부족이 던지는 경고[기고]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026033015455091764</t>
+          <t>https://news.mtn.co.kr/news-detail/2026042014032324372</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 15:52:00 +0900</t>
+          <t>Mon, 20 Apr 2026 14:12:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4117,23 +4118,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>** [특별기고·전북대 장원준 교수] AI·첨단기술 기반 ‘스마트 강군’ 육...</t>
+          <t>첨단항공엔진, 지금 시작하지 않으면 골든타임 놓친다 [기고]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260309/3/ATCE_CTGR_0020040016/view.do</t>
+          <t>https://news.mtn.co.kr/news-detail/2026033015455091764</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 15:56:00 +0900</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 30 Mar 2026 15:52:00 +0900</t>
+        </is>
+      </c>
+      <c r="E5">
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="6">

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,21 +462,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>** 전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E2">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -486,21 +486,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>** 전북대, 국방사업관리사 교육기관 2년 연속 선정</t>
+          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=839163</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 07:56:00 +0900</t>
+          <t>Tue, 19 May 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -510,21 +510,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>** 전북대, 방사청 국방사업관리사 교육 2년 연속 선정</t>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2585001</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 16:20:00 +0900</t>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/05/20260515161317_2334155_700_466.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -534,21 +534,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>** '방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+          <t>전북대, 국방사업관리사 교육기관 2년 연속 선정</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=839163</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+          <t>Sun, 17 May 2026 07:56:00 +0900</t>
         </is>
       </c>
       <c r="E5">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -558,21 +558,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>** “방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -582,21 +582,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>** 전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정…방위산...</t>
+          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003427957?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 12:01:00 +0900</t>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/15/0003427957_001_20260515120114089.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>** 전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -630,21 +630,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>** 전북대 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=610278</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:18:00 +0900</t>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E9">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202605/610278_523484_1622_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -654,21 +654,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>** 전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -678,21 +678,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>** 전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E11">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -702,21 +702,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>** 피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E12">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -726,21 +726,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>** 전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E13">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -750,21 +750,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>** 전북대, 방산 인공지능 인재양성 선정</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E14">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -774,21 +774,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>** 전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E15">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -798,21 +798,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>** 전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E16">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>** “AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -846,21 +846,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>** 전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E18">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -870,22 +870,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>** 전북대 71억 규모 '첨단인재양성 부트캠프 사업' 선정</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>http://www.veritas-a.com/news/articleView.html?idxno=600409</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 14:34:00 +0900</t>
-        </is>
-      </c>
-      <c r="E19">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202603/600409_514021_3155_v150.jpg"))</f>
-        <v/>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -894,21 +895,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>** 전북대, 첨단산업 인재양성 부트캠프 사업 선정</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001010129?sid=102</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 12:37:00 +0900</t>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/03/04/0001010129_001_20260304123710175.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -918,21 +919,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>** 전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -942,21 +943,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>** 전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -966,21 +967,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>** 전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>http://www.kyosu.net/news/articleView.html?idxno=155230</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 21:16:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png", IMAGE("https://cdn.kyosu.net/news/photo/202601/155230_150748_1015.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -990,21 +991,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>** 전북대, 방산 AI 유니콘 '쉴드 AI'와 협력 추진</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=432185</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 20:08:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202601/432185_142198_718_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1014,21 +1015,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>** 전북대, 글로벌 방산 AI 유니콘 쉴드 AI와 피지컬 AI 협력 추진</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202601150086</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 19:26:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/01/15/beta20260115000099.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1038,21 +1039,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>** 전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 체계 구축한다</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>http://www.domin.co.kr/news/articleView.html?idxno=1542514</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 18:24:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202601/1542514_744671_2955_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1062,21 +1063,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>** 전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진...피지컬...</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>http://www.jbsori.com/news/articleView.html?idxno=16762</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:50:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>HYPERLINK("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg", IMAGE("https://cdn.jbsori.com/news/thumbnail/202601/16762_37404_4735_v150.jpg"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1086,21 +1087,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>** 전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E28">
-        <f>HYPERLINK("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png", IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1110,21 +1111,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>** 전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.gukjenews.com/news/articleView.html?idxno=3481565</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 14:06:00 +0900</t>
+          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202601/3481565_3625055_228_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1134,21 +1135,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>** 전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>“AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>http://www.veritas-a.com/news/articleView.html?idxno=594342</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:22:00 +0900</t>
+          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202601/594342_508142_2029_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1158,21 +1159,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>** 전북대, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003390311?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:12:00 +0900</t>
+          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E31">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/01/15/0003390311_001_20260115121217425.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1182,21 +1183,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>** 전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
+          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
+          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1206,21 +1207,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>** 전북대, 세계 3대 방산유니콘 '쉴드 AI'와 전략적 협력</t>
+          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=588811</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:36:00 +0900</t>
+          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202601/588811_410518_3418_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1230,21 +1231,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>** 'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1254,21 +1255,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>** 전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
+          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1278,21 +1279,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>** 전북대-한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=204918</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:58:00 +0900</t>
+          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202604/204918_205281_5653.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1302,21 +1303,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>** 전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+          <t>전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1326,21 +1327,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>** 전북대-한화시스템 첨단 방산기술 협력 본격화</t>
+          <t>전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607576</t>
+          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:18:00 +0900</t>
+          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607576_520922_1639_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png", IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png"))</f>
         <v/>
       </c>
     </row>
@@ -1350,21 +1351,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>** 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+          <t>전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
+          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1374,21 +1375,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>** [단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
+          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1398,21 +1399,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
+          <t>배틀그라운드 기술이 전장으로...K-방산, 게임사와 'AI 전쟁' 준비한다</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
+          <t>https://www.newsquest.co.kr/news/articleView.html?idxno=267287</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
+          <t>Thu, 04 Jun 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg", IMAGE("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1422,21 +1423,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+          <t>[단독] 4월에 국방과학연구소 합동 안전검사도 못 막은 한화에어로 참사</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934274?sid=102</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+          <t>Wed, 03 Jun 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1446,21 +1447,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>한화에어로 참사, 미국·EU 방산 입찰 발목 잡나...'대전 사고' 도마 위</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=247498</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+          <t>Tue, 02 Jun 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1470,21 +1471,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>반복된 폭발사고…K방산 신뢰도 ‘악영향’</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1302742&amp;inflow=N</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:48:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231", IMAGE("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231"))</f>
         <v/>
       </c>
     </row>
@@ -1494,22 +1495,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>KDDX 보안 감점 공방이 던진 질문…방산 조달 사업의 大원칙은</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/108042</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E45">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 02 Jun 2026 13:04:00 +0900</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1518,21 +1520,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>[상생의 힘, 기업가치를 올린다] 김동관의 한화, 방산 넘어 안보 기업으...</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>https://www.g-enews.com/view.php?ud=20260601151511969112616b072_1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Mon, 01 Jun 2026 19:12:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1542,21 +1544,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>[상생의 힘, 기업가치를 올린다] 한화, 방산·조선·우주 국가전략산업...</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>https://www.g-enews.com/view.php?ud=202606011338107634112616b072_1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Mon, 01 Jun 2026 19:08:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1566,21 +1568,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>‘K-잠수함’ 1만4000km 잠항, 獨 꺾고 60조 잭팟 터뜨릴까</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>https://www.viva100.com/article/20260601500751</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Mon, 01 Jun 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604174643", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604174643"))</f>
         <v/>
       </c>
     </row>
@@ -1590,21 +1592,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Fri, 29 May 2026 17:40:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1614,23 +1616,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Fri, 29 May 2026 15:14:00 +0900</t>
+        </is>
+      </c>
+      <c r="E50">
+        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -1639,21 +1640,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+          <t>Thu, 28 May 2026 17:38:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1663,21 +1664,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 28 May 2026 15:29:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1687,21 +1688,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Thu, 28 May 2026 10:35:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1711,21 +1712,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Wed, 27 May 2026 17:23:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1735,22 +1736,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E55">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
-        <v/>
+          <t>Wed, 27 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -1759,21 +1761,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Tue, 26 May 2026 18:21:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1783,21 +1785,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
+          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
+          <t>Tue, 26 May 2026 14:57:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1807,21 +1809,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1831,21 +1833,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1855,21 +1857,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1879,21 +1881,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
         <v/>
       </c>
     </row>
@@ -1903,21 +1905,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>배틀그라운드 기술이 전장으로...K-방산, 게임사와 'AI 전쟁' 준비한다</t>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.newsquest.co.kr/news/articleView.html?idxno=267287</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Thu, 04 Jun 2026 15:00:00 +0900</t>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg", IMAGE("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1927,21 +1929,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[단독] 4월에 국방과학연구소 합동 안전검사도 못 막은 한화에어로 참사</t>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934274?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Wed, 03 Jun 2026 17:01:00 +0900</t>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1951,21 +1953,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>한화에어로 참사, 미국·EU 방산 입찰 발목 잡나...'대전 사고' 도마 위</t>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=247498</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 16:02:00 +0900</t>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1975,21 +1977,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>반복된 폭발사고…K방산 신뢰도 ‘악영향’</t>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1302742&amp;inflow=N</t>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:48:00 +0900</t>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231", IMAGE("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231"))</f>
+        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1999,17 +2001,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KDDX 보안 감점 공방이 던진 질문…방산 조달 사업의 大원칙은</t>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/108042</t>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 13:04:00 +0900</t>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2024,21 +2026,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[상생의 힘, 기업가치를 올린다] 김동관의 한화, 방산 넘어 안보 기업으...</t>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260601151511969112616b072_1</t>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 19:12:00 +0900</t>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2048,21 +2050,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[상생의 힘, 기업가치를 올린다] 한화, 방산·조선·우주 국가전략산업...</t>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202606011338107634112616b072_1</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 19:08:00 +0900</t>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2072,21 +2074,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>‘K-잠수함’ 1만4000km 잠항, 獨 꺾고 60조 잭팟 터뜨릴까</t>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260601500751</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 15:32:00 +0900</t>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604162610", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604162610"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2096,21 +2098,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 17:40:00 +0900</t>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2120,21 +2122,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 15:14:00 +0900</t>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2144,21 +2146,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
+          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 17:38:00 +0900</t>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2168,21 +2170,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
+          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 15:29:00 +0900</t>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2192,21 +2194,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 10:35:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2216,21 +2218,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 17:23:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2240,23 +2242,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E76">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -2265,21 +2266,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 18:21:00 +0900</t>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2289,21 +2290,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 14:57:00 +0900</t>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2313,22 +2314,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 10:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E79">
-        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
-        <v/>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -2337,21 +2339,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
         <v/>
       </c>
     </row>
@@ -2361,21 +2363,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2385,21 +2387,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2409,21 +2411,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:54:00 +0900</t>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2433,21 +2435,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2457,21 +2459,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2481,21 +2483,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2505,17 +2507,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 06:02:00 +0900</t>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2530,21 +2532,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 15:02:00 +0900</t>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
+        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2554,21 +2556,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 11:30:00 +0900</t>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2578,21 +2580,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 06:00:00 +0900</t>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2602,21 +2604,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2626,21 +2628,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>“한·일 함정 분야 경쟁 가능성”</t>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2650,21 +2652,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2674,22 +2676,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
-        </is>
-      </c>
-      <c r="E94">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
-        <v/>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -2698,21 +2701,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E95">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2722,21 +2725,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2746,17 +2749,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2771,21 +2774,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2795,21 +2798,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2819,21 +2822,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2843,21 +2846,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2575581</t>
+          <t>https://www.etoday.co.kr/news/view/2571395</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2867,21 +2870,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>K-방산 강국으로의 도약, &amp;quot;첨단 복합소재 공급망 자립 최우선 과제&amp;quot;</t>
+          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1038170</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1038170_263476_2948_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2891,21 +2894,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2915,21 +2918,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2939,23 +2942,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E105">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="106">
@@ -2964,23 +2966,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>http://amenews.kr/news/view.php?idx=66331</t>
+          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+        </is>
+      </c>
+      <c r="E106">
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="107">
@@ -2989,21 +2990,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+          <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
+          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
         <v/>
       </c>
     </row>
@@ -3013,22 +3014,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
-        </is>
-      </c>
-      <c r="E108">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -3037,21 +3039,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3061,21 +3063,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3085,21 +3087,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3109,17 +3111,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3134,22 +3136,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2573034</t>
+          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
-        </is>
-      </c>
-      <c r="E113">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
-        <v/>
+          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -3158,21 +3161,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
+          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3182,23 +3185,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E115">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="116">
@@ -3207,21 +3209,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260401154708093</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
+          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3231,21 +3233,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
+          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2571395</t>
+          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
+          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3255,21 +3257,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
+          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
+          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3279,22 +3281,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
+          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
+          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
-        </is>
-      </c>
-      <c r="E119">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -3303,21 +3306,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
+          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
+          <t>https://www.ajunews.com/view/20260310153628801</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
+          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3327,21 +3330,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
+          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3351,21 +3354,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
+          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3375,21 +3378,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>한국형 차기 구축함 사업자 7월에 선정</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260326500334</t>
+          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
+          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3399,23 +3402,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>임무 중심·민간 참여·성능 향상 가속화 등 논의</t>
+          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260327/5/ATCE_CTGR_0010010000/view.do</t>
+          <t>https://www.ajunews.com/view/20260227150934536</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:24:00 +0900</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+        </is>
+      </c>
+      <c r="E124">
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -3424,21 +3426,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>부승찬·강선영 의원 공동주최 'K-방산 지속성장 전략' 세미나 성료</t>
+          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002433611?sid=102</t>
+          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 17:07:00 +0900</t>
+          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/25/0002433611_001_20260325170711793.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3448,21 +3450,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>&amp;quot;K-방산, 규제혁신 없인 지속성장 어렵다&amp;quot;…국회 세미나서 제도 개선 한...</t>
+          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://www.straightnews.co.kr/news/articleView.html?idxno=298422</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 09:26:00 +0900</t>
+          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg", IMAGE("https://cdn.straightnews.co.kr/news/thumbnail/202603/298422_207325_235_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3472,22 +3474,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>[현장] K-방산 지속 성장, '글로벌 규제 대응'에 달렸다…&amp;quot;정부 원팀 지...</t>
+          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>http://www.newsian.co.kr/news/articleView.html?idxno=87644</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 19:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E127">
-        <f>HYPERLINK("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg", IMAGE("https://cdn.newsian.co.kr/news/thumbnail/202603/87644_79544_1228_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -3496,23 +3499,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>마스가 참여하려면 ‘보안 인증’ 필수…“협력업체까지 대비해야”</t>
+          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1295369&amp;inflow=N</t>
+          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 16:50:00 +0900</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E128">
+        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="129">
@@ -3521,23 +3523,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>‘100년 성역’ 깬 트럼프의 존스법 유예… K-조선 기회인가 신기루인가</t>
+          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603190170</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 17:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E129">
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="130">
@@ -3546,21 +3547,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>김종출號 KAI 출범…'경영 안정·수주 확대' 드라이브 건다</t>
+          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260319010005913</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 15:58:00 +0900</t>
+          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E130">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/03m/20d/2026031901001078600059131.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3570,21 +3571,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>[2026어젠다] 화력보다 '속도'…22년 조달 장벽 깬 미국</t>
+          <t>경남정보대, 간호학과 취업박람회·국방산업학과 특강 잇달아...'지역 맞...</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001134633?sid=104</t>
+          <t>https://www.ajunews.com/view/20260604140251194</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar 2026 06:00:00 +0900</t>
+          <t>Thu, 04 Jun 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/18/0001134633_001_20260401151811141.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/06/04/20260604140756601033.jpg", IMAGE("https://image.ajunews.com/content/image/2026/06/04/20260604140756601033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3594,21 +3595,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>K-방산, 'NATO 무기 공급 세계 2위' 공식 등극…서방 군수 공급망 편입</t>
+          <t>[부산ㆍ경남 대학 브리핑 모음(6월4일)] 국립창원대, ‘TUG Campus 유·무인...</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1351596</t>
+          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202606031021265380946</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 15:00:00 +0900</t>
+          <t>Thu, 04 Jun 2026 10:02:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1351596_1136361_472_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/06/03/202606031021265380946-2-669126.JPG", IMAGE("https://image.dnews.co.kr/photo/photo/2026/06/03/202606031021265380946-2-669126.JPG"))</f>
         <v/>
       </c>
     </row>
@@ -3618,21 +3619,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 7년 만에 재매입…&amp;quot;방산·우주항공 협력 강화&amp;quot;</t>
+          <t>“AI 판 뒤집히면 민주주의 붕괴”…中에 쫓기는 美 ‘섬뜩 경고’ [팩...</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026031609273027275</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003527926?sid=105</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mon, 16 Mar 2026 10:14:00 +0900</t>
+          <t>Thu, 04 Jun 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/16/2026031609273027275_00_819.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/06/04/0003527926_001_20260604060112525.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/06/04/0003527926_001_20260604060112525.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3642,21 +3643,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>‘첩첩산중’ 무주가 우주 기지로… “거대 산봉우리들이 자연 방호벽”</t>
+          <t>[6·3지선] 권익현, 부안군수 3선 성공…&amp;quot;하나된 대통합의 부안 만들겠다...</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003964275?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008983941?sid=162</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Fri, 13 Mar 2026 00:46:00 +0900</t>
+          <t>Thu, 04 Jun 2026 03:00:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/03/13/0003964275_001_20260313095810822.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/04/0008983941_001_20260604030132821.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/04/0008983941_001_20260604030132821.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3666,23 +3667,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>개청 20년 방사청…‘K-방산 르네상스’ 넘어 글로벌 톱4 안착하려면</t>
+          <t>“K-방산 미래 인재 키운다”… 경남정보대, 방산 전문가 초청 특강</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202603120062</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005771069?sid=102</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 14:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 02 Jun 2026 15:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E135">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/06/02/0005771069_001_20260602150313293.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/06/02/0005771069_001_20260602150313293.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="136">
@@ -3691,21 +3691,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>천궁 다음은 한국형 사드? 중동에 팔 신무기 '착착' 나온다</t>
+          <t>[부산교육종합] 동의과학대·경남정보대, 각종 수상 및 특강 개최 눈길</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260310153628801</t>
+          <t>https://www.g-enews.com/view.php?ud=20260602144105335537f21df127_1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 18:06:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:52:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg", IMAGE("https://image.ajunews.com/content/image/2026/03/10/20260310160412635766.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202606021442280788837f21df12711222312362.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202606021442280788837f21df12711222312362.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3715,21 +3715,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>K-방산, 올해 수출 승부처 점검…대형 사업 향방</t>
+          <t>부울경 방산 인재 육성 본격화.. 경남정보대, 특강 화제</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1344768</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=842079</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 15:46:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:44:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1344768_1129699_124_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202606/842079_855400_2824_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202606/842079_855400_2824_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3739,21 +3739,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>[미국·이란 전쟁] 드론 군단에 최첨단 방공망 '무용지물'</t>
+          <t>15개월 시정공백 끝낼 창원특례시 시장후보 4인 공약</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001132298?sid=101</t>
+          <t>https://www.newsgn.com/news/articleView.html?idxno=554981</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 14:44:00 +0900</t>
+          <t>Mon, 01 Jun 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/03/03/0001132298_001_20260303153308420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsgn.com/news/thumbnail/202606/554981_361763_2345_v150.jpg", IMAGE("https://cdn.newsgn.com/news/thumbnail/202606/554981_361763_2345_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3763,21 +3763,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>[부산ㆍ경남 대학 브리핑 모음(6월1일)] 동의대 K-뷰티학과, 베트남 인트...</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133540?sid=100</t>
+          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202605310842445790568</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 08:12:00 +0900</t>
+          <t>Mon, 01 Jun 2026 08:02:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133540_001_20260302085827922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/05/31/202605310842445790568-2-668491.jpg", IMAGE("https://image.dnews.co.kr/photo/photo/2026/05/31/202605310842445790568-2-668491.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3787,21 +3787,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>동양대, Yes-UP DYU 취창업전문가 특강 운영</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133530?sid=100</t>
+          <t>https://www.kgnews.co.kr/news/article.html?no=898019</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Mon, 02 Mar 2026 07:35:00 +0900</t>
+          <t>Sun, 31 May 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/02/0012133530_001_20260302085427536.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.kgnews.co.kr/data/photos/20260522/art_17801971535159_6edc3a.jpg", IMAGE("https://www.kgnews.co.kr/data/photos/20260522/art_17801971535159_6edc3a.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3811,21 +3811,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>한국형 차기 구축함 사업자 7월에 선정</t>
+          <t>동양대 군사학과, 방위산업·국방 R&amp;amp;D 진로 특강 개최</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012133398?sid=100</t>
+          <t>https://www.gukjenews.com/news/articleView.html?idxno=3595705</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar 2026 22:11:00 +0900</t>
+          <t>Fri, 29 May 2026 18:48:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/03/01/0012133398_001_20260301223017493.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202605/3595705_3753692_4549_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202605/3595705_3753692_4549_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3835,21 +3835,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>[오주석의 이심戰심] 드론 시대에도 헬기는 죽지 않는다</t>
+          <t>K-핵잠이 던진 새판…HD현대·한화 '협력과 경쟁' 딜레마</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260227150934536</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=127309</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 16:42:00 +0900</t>
+          <t>Fri, 29 May 2026 14:26:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg", IMAGE("https://image.ajunews.com/content/image/2026/02/27/20260227162415390430.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202605/127309_112204_2951_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202605/127309_112204_2951_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3859,21 +3859,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>노조 반발에 KAI 사장 인선 불발…리더십 공백 장기화</t>
+          <t>Creating a business-friendly policy ecosystem is key to Korea’s manufac...</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026022611002311032</t>
+          <t>https://n.news.naver.com/mnews/article/640/0000089168?sid=110</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Thu, 26 Feb 2026 11:20:00 +0900</t>
+          <t>Fri, 29 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/02/26/2026022611002311032_00_737.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/640/2026/05/29/0000089168_001_20260529100110885.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/640/2026/05/29/0000089168_001_20260529100110885.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3883,21 +3883,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>'수장 공백’ 장기화 불가피…KAI, 조직 안정·사업 재정비 ‘차질’</t>
+          <t>[김동원의 이코노믹스] 기업 친화적 정책 생태계 만들어야 한국 제조업...</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007559</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003526556?sid=110</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 16:44:00 +0900</t>
+          <t>Fri, 29 May 2026 00:14:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/26d/2026022501001382200075591.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/05/29/0003526556_001_20260529053237448.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/05/29/0003526556_001_20260529053237448.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3907,23 +3907,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>방산 ‘빅4’ 영업익 ‘4조 시대’ 개막… 올해도 성장 기대↑</t>
+          <t>[부산ㆍ경남 대학 브리핑 모음(5월28일)] 동서대 디자인대학, 미국 패션...</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/103440</t>
+          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202605271640520080204</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 28 May 2026 08:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E145">
+        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/05/27/202605271640520080204-2-667920.jpg", IMAGE("https://image.dnews.co.kr/photo/photo/2026/05/27/202605271640520080204-2-667920.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="146">
@@ -3932,21 +3931,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>수출이 실적 견인… K-방산 4사, 내수→글로벌로 체질 전환</t>
+          <t>기업이 캠퍼스로 왔다···전북대·탈레스코리아 '산학협력'에 속도</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>http://www.newsdream.kr/news/articleView.html?idxno=107410</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2433457</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:38:00 +0900</t>
+          <t>Wed, 27 May 2026 15:54:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg", IMAGE("https://cdn.newsdream.kr/news/thumbnail/202602/107410_79602_318_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2433457_1268751_5344_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2433457_1268751_5344_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3956,21 +3955,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>韓 방산현장 직관한 加장관… &amp;quot;미래 온 듯&amp;quot; 기술력에 '엄지척'</t>
+          <t>[정책의 맥]산업 新르네상스, 기업과 함께 싸워줄 공학교육 전환기</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260205010001719</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005768122?sid=110</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
+          <t>Wed, 27 May 2026 09:27:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/05/27/0005768122_001_20260527151111337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/05/27/0005768122_001_20260527151111337.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3980,22 +3979,1106 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
+          <t>'제2회 우주항공의 날' 기념식 27일 사천서 개최</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
+          <t>http://www.gndomin.com/news/articleView.html?idxno=476754</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
+          <t>Tue, 26 May 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E148">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
-        <v/>
+        <f>HYPERLINK("http://www.gndomin.com/image/logo/snslogo_20240325100844.png", IMAGE("http://www.gndomin.com/image/logo/snslogo_20240325100844.png"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>전북대, ‘학부생부터 글로벌 방산기업과 연결’…K-방산 인재양성 새 ...</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://www.viva100.com/article/20260526500712</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Tue, 26 May 2026 14:42:00 +0900</t>
+        </is>
+      </c>
+      <c r="E149">
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/05/26/.cache/512/20260526500704.jpg?v=20260604175111", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/05/26/.cache/512/20260526500704.jpg?v=20260604175111"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>전북대-탈레스코리아, 글로벌 방산·우주 인재양성 협력 '속도'</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/030/0003431295?sid=102</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Tue, 26 May 2026 14:37:00 +0900</t>
+        </is>
+      </c>
+      <c r="E150">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/26/0003431295_001_20260526143710089.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/26/0003431295_001_20260526143710089.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>전북대·탈레스코리아 &amp;quot;방산·우주 인재 양성 협력 확대&amp;quot;</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/003/0013967151?sid=102</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Tue, 26 May 2026 11:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E151">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/05/26/NISI20260526_0002144874_web_20260526113009_20260526113916721.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/05/26/NISI20260526_0002144874_web_20260526113009_20260526113916721.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>[윤은기의 X경영(80)] 초가속 시대, '시간 압축'이 승패를 가른다</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=203091</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Tue, 26 May 2026 09:50:00 +0900</t>
+        </is>
+      </c>
+      <c r="E152">
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202605/203091_470025_4822_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202605/203091_470025_4822_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>“증시만 호황인 건 비정상, 실물경제도 같이 살아야 선진국형”</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/262/0000019395?sid=101</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Mon, 25 May 2026 07:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E153">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/05/25/0000019395_001_20260525070110630.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/05/25/0000019395_001_20260525070110630.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>“한국 2000억 달러 흑자, 미국이 그냥 둘까”</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/353/0000055533?sid=102</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Sat, 23 May 2026 00:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E154">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/353/2026/05/23/0000055533_001_20260523013423648.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/353/2026/05/23/0000055533_001_20260523013423648.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>주가 신기루와 반도체 착시 걷어내야 하는 이유</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/036/0000053637?sid=101</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Thu, 21 May 2026 18:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E155">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/036/2026/05/21/0000053637_001_20260601094213980.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/036/2026/05/21/0000053637_001_20260601094213980.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>'방산 불모지' 전북, 탄소 입고 다시 뛴다...첨단소재로 판 바꾼 전북 방...</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=440278</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Thu, 21 May 2026 16:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E156">
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/440278_149320_1654_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/440278_149320_1654_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>사천서 우주 체험하고, 김해서 별 보고</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/020/0003721222?sid=102</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Thu, 21 May 2026 04:33:00 +0900</t>
+        </is>
+      </c>
+      <c r="E157">
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>제2회 우주항공의 날, 경남 곳곳서 우주항공 체험 행사 풍성</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/020/0003720980?sid=102</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 10:19:00 +0900</t>
+        </is>
+      </c>
+      <c r="E158">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/05/20/0003720980_001_20260520101916617.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/05/20/0003720980_001_20260520101916617.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>경남도, 우주항공의 날·주간 맞아 도내 전역서 기념행사 다채</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>https://www.cnbnews.com/news/articleView.html?idxno=1002192</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 10:04:00 +0900</t>
+        </is>
+      </c>
+      <c r="E159">
+        <f>HYPERLINK("https://cdn.cnbnews.com/news/photo/202605/1002192_502105_1779237915.jpg", IMAGE("https://cdn.cnbnews.com/news/photo/202605/1002192_502105_1779237915.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>'우주항공 주간' 경남 곳곳서 정책·산업·문화 아우르는 연계행사 풍성</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/030/0003429368?sid=102</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 08:59:00 +0900</t>
+        </is>
+      </c>
+      <c r="E160">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/20/0003429368_001_20260520085910062.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/20/0003429368_001_20260520085910062.png?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>[Who Is ?] 박재석 SNT다이내믹스 대표이사 사장</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=438134</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 07:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>'우주항공의 날' 경남 곳곳 행사 다채</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>http://www.gndomin.com/news/articleView.html?idxno=476080</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 18:22:00 +0900</t>
+        </is>
+      </c>
+      <c r="E162">
+        <f>HYPERLINK("http://www.gndomin.com/image/logo/snslogo_20240325100844.png", IMAGE("http://www.gndomin.com/image/logo/snslogo_20240325100844.png"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>국립창원대 과학기술원 공약, '신설' 아닌 '전환'이 문제 [6.3 쟁점 점검...</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://www.idomin.com/news/articleView.html?idxno=2006078</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 17:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E163">
+        <f>HYPERLINK("https://cdn.idomin.com/news/photo/202605/2006078_709045_2504.jpg", IMAGE("https://cdn.idomin.com/news/photo/202605/2006078_709045_2504.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>경남도 '제2회 우주항공의 날' 주간 연계 행사 추진</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://www.ulsanpress.net/news/articleView.html?idxno=575488</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 17:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E164">
+        <f>HYPERLINK("https://cdn.ulsanpress.net/news/thumbnail/202605/575488_273004_2441_v150.jpg", IMAGE("https://cdn.ulsanpress.net/news/thumbnail/202605/575488_273004_2441_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>경남도, '제2회 우주항공의 날' 맞아 정책·산업·문화 아우르는 '우주항...</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>https://www.newsgn.com/news/articleView.html?idxno=552950</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 16:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E165">
+        <f>HYPERLINK("https://cdn.newsgn.com/news/thumbnail/202605/552950_359588_3749_v150.jpg", IMAGE("https://cdn.newsgn.com/news/thumbnail/202605/552950_359588_3749_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>경남 전역서 ‘우주항공 주간’ 연계 행사 풍성</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260519010005201</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 14:22:00 +0900</t>
+        </is>
+      </c>
+      <c r="E166">
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/05m/20d/2026052001001022300056201.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/05m/20d/2026052001001022300056201.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>(박창식의 K-국방)한국 방위 역량, 이제 자기 비하를 멈출 때다</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1301220&amp;inflow=N</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E167">
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/19/1301220/attach.jpg?v=202605181605", IMAGE("https://image.newstomato.com/newsimg/2026/5/19/1301220/attach.jpg?v=202605181605"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>방위사업청, 美 국방획득대학교와 공동 워크숍 개최… &amp;quot;첨단 획득역량 ...</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>https://www.gukjenews.com/news/articleView.html?idxno=3585775</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 03:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E168">
+        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202605/3585775_3741735_5024_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202605/3585775_3741735_5024_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>강원대 첨단군사과학기술연구소 ‘국방사업관리사 자격증 과정 운영대...</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/002/0002441873?sid=102</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 18:36:00 +0900</t>
+        </is>
+      </c>
+      <c r="E169">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/18/0002441873_001_20260518183616443.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/18/0002441873_001_20260518183616443.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>방사청, 미 국방획득대학교와 실무급 워크숍</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260519/1/ATCE_CTGR_0010020000/view.do</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 16:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>인·태 시대의 '평화 거점' 한국, 갈등의 파고를 넘는 가교가 될 것인가...</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>http://www.tongilnews.com/news/articleView.html?idxno=216521</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 14:06:00 +0900</t>
+        </is>
+      </c>
+      <c r="E171">
+        <f>HYPERLINK("https://cdn.tongilnews.com/news/thumbnail/202605/216521_115974_247_v150.jpg", IMAGE("https://cdn.tongilnews.com/news/thumbnail/202605/216521_115974_247_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>전북대학교, 방사청 '국방사업관리사' 교육기관 2년 연속 선정…방산 전...</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=202591</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 12:36:00 +0900</t>
+        </is>
+      </c>
+      <c r="E172">
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202605/202591_469341_365_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202605/202591_469341_365_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>방사청, 美 국방획득대학과 '애자일 무기획득' 5일 합숙 토론</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>https://www.newspim.com/news/view/20260518000484</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 10:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E173">
+        <f>HYPERLINK("https://img.newspim.com/news/2026/05/18/2605181053393780_t1.jpg", IMAGE("https://img.newspim.com/news/2026/05/18/2605181053393780_t1.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>방사청, 美 국방획득대와 공동 워크숍…획득인력 양성체계 공유</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/008/0005359123?sid=100</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 10:27:00 +0900</t>
+        </is>
+      </c>
+      <c r="E174">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/05/18/0005359123_001_20260518102817596.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/05/18/0005359123_001_20260518102817596.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>방사청·美 국방획득대, 韓美 국방획득인력 양성체계 및 첨단 획득제도...</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/021/0002791828?sid=100</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 09:03:00 +0900</t>
+        </is>
+      </c>
+      <c r="E175">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/05/18/0002791828_001_20260518090308259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/05/18/0002791828_001_20260518090308259.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>[기술간첩] ⑤ '23조 원' 소는 잃었어도 외양간은 계속 고쳐야…</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://www.bizhankook.com/bk/article/32273</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 16:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E176">
+        <f>HYPERLINK("https://www.bizhankook.com/upload/bk/article/202605/thumb/32273-78198-sample.jpg", IMAGE("https://www.bizhankook.com/upload/bk/article/202605/thumb/32273-78198-sample.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>글로벌 AI-방산-반도체 인재 양성… 매머드급 국가거점국립대로 새 도약</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/020/0003719813?sid=102</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 04:34:00 +0900</t>
+        </is>
+      </c>
+      <c r="E177">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/05/15/0003719813_001_20260515043415656.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/05/15/0003719813_001_20260515043415656.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>대진대학교, 개교 34주년 기념식 개최… ‘K-방산·AI 선도대학’ 도약...</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202605141437242740775</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 20:22:00 +0900</t>
+        </is>
+      </c>
+      <c r="E178">
+        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/05/14/202605141437242740775-2-665578.jpg", IMAGE("https://image.dnews.co.kr/photo/photo/2026/05/14/202605141437242740775-2-665578.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>대진대, 개교 34주년…&amp;quot;K-방산·AI 선도대학 도약&amp;quot; 선언</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/666/0000107051?sid=102</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 18:49:00 +0900</t>
+        </is>
+      </c>
+      <c r="E179">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/666/2026/05/14/0000107051_001_20260514184921026.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/666/2026/05/14/0000107051_001_20260514184921026.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>폴리텍대-한화에어로스페이스, 우주항공·방산 인재 양성 협약 체결</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>http://www.lawissue.co.kr/view.php?ud=202605141722574466f4ab64559d_12</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 17:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E180">
+        <f>HYPERLINK("https://cliimage.commutil.kr/lawissue_www/nimg/default_bimg.png?p=003", IMAGE("https://cliimage.commutil.kr/lawissue_www/nimg/default_bimg.png?p=003"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>한화에어로-폴리텍대, 항공우주·방산 기술인재 양성 '맞손'</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/079/0004147018?sid=102</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 17:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E181">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/079/2026/05/14/0004147018_001_20260514171216898.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/079/2026/05/14/0004147018_001_20260514171216898.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>대진대 개교 34주년 기념식 개최...  'K-방산/AI 선도대학' 도약 선포</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=610088</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 14:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E182">
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202605/610088_523297_2359_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202605/610088_523297_2359_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5월 14일 베이징 회담은 결승전이 아니다</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/047/0002515553?sid=104</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 17:31:00 +0900</t>
+        </is>
+      </c>
+      <c r="E183">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/047/2026/05/13/0002515553_001_20260513173110461.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/047/2026/05/13/0002515553_001_20260513173110461.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>[Who Is ?] 손경석 퍼스텍 대표이사 사장</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=437052</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 07:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>경북도 ‘앵커’ 대학 지원 사업..청년 지역 정착 견인</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/009/0005679052?sid=102</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 18:59:00 +0900</t>
+        </is>
+      </c>
+      <c r="E185">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/009/2026/05/12/0005679052_001_20260512185909544.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/009/2026/05/12/0005679052_001_20260512185909544.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>[부산ㆍ경남 대학 브리핑 모음(5월12일)] 국립창원대 “인도 고위급 대...</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202605111705002220305</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 08:40:00 +0900</t>
+        </is>
+      </c>
+      <c r="E186">
+        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/05/11/202605111705002220305-2-664832.jpg", IMAGE("https://image.dnews.co.kr/photo/photo/2026/05/11/202605111705002220305-2-664832.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>[인터뷰]김태흠 &amp;quot;대전-충남 통합, 9조원 국세·권한 이양되면 추진&amp;quot;</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/417/0001142666?sid=162</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 05:21:00 +0900</t>
+        </is>
+      </c>
+      <c r="E187">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/05/12/0001142666_001_20260512072307509.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/05/12/0001142666_001_20260512072307509.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>국립창원대, 인도 조선해양 고위급 대표단 방문</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>http://www.breaknews.com/1206310</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 16:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E188">
+        <f>HYPERLINK("https://www.breaknewsgn.com/imgdata/breaknewsgn_com/202605/2026051150412533.jpg", IMAGE("https://www.breaknewsgn.com/imgdata/breaknewsgn_com/202605/2026051150412533.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>물가·청년일자리로 쏠린 민심…경기지사 후보들 해법 경쟁</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>https://www.kgnews.co.kr/news/article.html?no=894943</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Sun, 10 May 2026 20:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E189">
+        <f>HYPERLINK("https://www.kgnews.co.kr/data/photos/20260519/art_17784002216015_6d0c30.png", IMAGE("https://www.kgnews.co.kr/data/photos/20260519/art_17784002216015_6d0c30.png"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>경북도 ‘앵커 사업’ 성과 가시화… 지역대학·기업 상생 모델 주목</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>http://www.breaknews.com/1205573</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 17:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E190">
+        <f>HYPERLINK("https://dk.breaknews.com/imgdata/dk_breaknews_com/202605/2026050745561906.jpg", IMAGE("https://dk.breaknews.com/imgdata/dk_breaknews_com/202605/2026050745561906.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>지역대학서 키운 인재, 지역기업 취업으로…경북형 청년 정주모델 성과</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>https://www.kyongbuk.co.kr/news/articleView.html?idxno=4072122</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 16:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E191">
+        <f>HYPERLINK("https://cdn.kyongbuk.co.kr/news/photo/202605/4072122_803539_2151.jpg", IMAGE("https://cdn.kyongbuk.co.kr/news/photo/202605/4072122_803539_2151.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>'라이즈' 재구조화 '앵커' 체계…진학·취업·정주 선순환</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>https://www.hidomin.com/news/articleView.html?idxno=704332</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 14:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E192">
+        <f>HYPERLINK("https://cdn.hidomin.com/news/photo/202605/704332_404734_0928.jpg", IMAGE("https://cdn.hidomin.com/news/photo/202605/704332_404734_0928.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>경북도 ‘앵커’ 사업 성과…청년 정착·기업 경쟁력 동시 강화</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>https://www.kukinews.com/article/view/kuk202605070060</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 11:58:00 +0900</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4009,7 +5092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4070,21 +5153,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>K방산 수출, 이제는 정보다 [기고]</t>
+          <t>** [장원준 칼럼] 차기 한미 정상회담 의제로 ‘방산 공동생산 동맹’ 제안...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000927039?sid=110</t>
+          <t>https://www.news2day.co.kr/article/20260527500120</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 04:31:00 +0900</t>
+          <t>Wed, 27 May 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/05/27/.cache/512/20260527500119.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/05/27/.cache/512/20260527500119.png"))</f>
         <v/>
       </c>
     </row>
@@ -4094,21 +5177,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>전쟁은 '생산능력'이다 : 미국의 무기 부족이 던지는 경고[기고]</t>
+          <t>K방산 수출, 이제는 정보다 [기고]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026042014032324372</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000927039?sid=110</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 14:12:00 +0900</t>
+          <t>Thu, 23 Apr 2026 04:31:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4118,21 +5201,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>첨단항공엔진, 지금 시작하지 않으면 골든타임 놓친다 [기고]</t>
+          <t>전쟁은 '생산능력'이다 : 미국의 무기 부족이 던지는 경고[기고]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026033015455091764</t>
+          <t>https://news.mtn.co.kr/news-detail/2026042014032324372</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 15:52:00 +0900</t>
+          <t>Mon, 20 Apr 2026 14:12:00 +0900</t>
         </is>
       </c>
       <c r="E5">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4142,21 +5225,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[기고] K방산 롱런의 조건 '현지 생산'</t>
+          <t>첨단항공엔진, 지금 시작하지 않으면 골든타임 놓친다 [기고]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/009/0005646852?sid=110</t>
+          <t>https://news.mtn.co.kr/news-detail/2026033015455091764</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:19:00 +0900</t>
+          <t>Mon, 30 Mar 2026 15:52:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/009/2026/03/08/0005646852_001_20260308175312269.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/009/2026/03/08/0005646852_001_20260308175312269.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4166,21 +5249,141 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>[기고] K방산 롱런의 조건 '현지 생산'</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/009/0005646852?sid=110</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sun, 08 Mar 2026 17:19:00 +0900</t>
+        </is>
+      </c>
+      <c r="E7">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/009/2026/03/08/0005646852_001_20260308175312269.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/009/2026/03/08/0005646852_001_20260308175312269.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>가성비 전쟁 시대, 한국은 준비됐나 [기고]</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>https://news.mtn.co.kr/news-detail/2026030610261598884</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Fri, 06 Mar 2026 10:46:00 +0900</t>
         </is>
       </c>
-      <c r="E7">
+      <c r="E8">
         <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/06/2026030610261598884_00_643.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/06/2026030610261598884_00_643.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>반복되는 방산 폭발사고…위험공정 자동화·원가제도 개혁해야[기고]</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://news.mtn.co.kr/news-detail/2026060416345488076</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 17:06:00 +0900</t>
+        </is>
+      </c>
+      <c r="E9">
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/06/04/2026060416345488076_00_159.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/06/04/2026060416345488076_00_159.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[기고]교육부 최초 승인 '첨단방위산업학과', 지역 방산혁신의 새 희망</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/018/0006292697?sid=110</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 06:01:00 +0900</t>
+        </is>
+      </c>
+      <c r="E10">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/018/2026/05/29/0006292697_001_20260529060107244.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/018/2026/05/29/0006292697_001_20260529060107244.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[최기일 칼럼] 軍 방독면 입찰 계약 구조 개선해야</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.news2day.co.kr/article/20260518500244</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 20:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E11">
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/05/18/.cache/512/20260518500243.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/05/18/.cache/512/20260518500243.png"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>미국도 중국도 원하지 않는 최악의 시나리오 [김영근 교수 칼럼]</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.mediafine.co.kr/news/articleView.html?idxno=78947</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 17:58:00 +0900</t>
+        </is>
+      </c>
+      <c r="E12">
+        <f>HYPERLINK("https://cdn.mediafine.co.kr/news/photo/202605/78947_115306_5142.jpg", IMAGE("https://cdn.mediafine.co.kr/news/photo/202605/78947_115306_5142.jpg"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604174643", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604174643"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604180245", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604180245"))</f>
         <v/>
       </c>
     </row>
@@ -2545,9 +2545,10 @@
           <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
         </is>
       </c>
-      <c r="E88">
-        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
-        <v/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -3536,9 +3537,10 @@
           <t>Wed, 04 Feb 2026 17:56:00 +0900</t>
         </is>
       </c>
-      <c r="E129">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/05d/20260205010001719_1770200387_1.jpg"))</f>
-        <v/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -3571,21 +3573,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>경남정보대, 간호학과 취업박람회·국방산업학과 특강 잇달아...'지역 맞...</t>
+          <t>“AI 판 뒤집히면 민주주의 붕괴”…中에 쫓기는 美 ‘섬뜩 경고’ [팩...</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260604140251194</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003527926?sid=105</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Thu, 04 Jun 2026 14:16:00 +0900</t>
+          <t>Thu, 04 Jun 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/06/04/20260604140756601033.jpg", IMAGE("https://image.ajunews.com/content/image/2026/06/04/20260604140756601033.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/06/04/0003527926_001_20260604060112525.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/06/04/0003527926_001_20260604060112525.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3595,21 +3597,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[부산ㆍ경남 대학 브리핑 모음(6월4일)] 국립창원대, ‘TUG Campus 유·무인...</t>
+          <t>[6·3지선] 권익현, 부안군수 3선 성공…&amp;quot;하나된 대통합의 부안 만들겠다...</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202606031021265380946</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008983941?sid=162</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Thu, 04 Jun 2026 10:02:00 +0900</t>
+          <t>Thu, 04 Jun 2026 03:00:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/06/03/202606031021265380946-2-669126.JPG", IMAGE("https://image.dnews.co.kr/photo/photo/2026/06/03/202606031021265380946-2-669126.JPG"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/04/0008983941_001_20260604030132821.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/04/0008983941_001_20260604030132821.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3619,21 +3621,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>“AI 판 뒤집히면 민주주의 붕괴”…中에 쫓기는 美 ‘섬뜩 경고’ [팩...</t>
+          <t>15개월 시정공백 끝낼 창원특례시 시장후보 4인 공약</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003527926?sid=105</t>
+          <t>https://www.newsgn.com/news/articleView.html?idxno=554981</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Thu, 04 Jun 2026 06:00:00 +0900</t>
+          <t>Mon, 01 Jun 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/06/04/0003527926_001_20260604060112525.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/06/04/0003527926_001_20260604060112525.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsgn.com/news/thumbnail/202606/554981_361763_2345_v150.jpg", IMAGE("https://cdn.newsgn.com/news/thumbnail/202606/554981_361763_2345_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3643,21 +3645,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>[6·3지선] 권익현, 부안군수 3선 성공…&amp;quot;하나된 대통합의 부안 만들겠다...</t>
+          <t>동양대, Yes-UP DYU 취창업전문가 특강 운영</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008983941?sid=162</t>
+          <t>https://www.kgnews.co.kr/news/article.html?no=898019</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Thu, 04 Jun 2026 03:00:00 +0900</t>
+          <t>Sun, 31 May 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/04/0008983941_001_20260604030132821.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/04/0008983941_001_20260604030132821.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.kgnews.co.kr/data/photos/20260522/art_17801971535159_6edc3a.jpg", IMAGE("https://www.kgnews.co.kr/data/photos/20260522/art_17801971535159_6edc3a.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3667,21 +3669,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>“K-방산 미래 인재 키운다”… 경남정보대, 방산 전문가 초청 특강</t>
+          <t>동양대 군사학과, 방위산업·국방 R&amp;amp;D 진로 특강 개최</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005771069?sid=102</t>
+          <t>https://www.gukjenews.com/news/articleView.html?idxno=3595705</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 15:02:00 +0900</t>
+          <t>Fri, 29 May 2026 18:48:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/06/02/0005771069_001_20260602150313293.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/06/02/0005771069_001_20260602150313293.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202605/3595705_3753692_4549_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202605/3595705_3753692_4549_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3691,21 +3693,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>[부산교육종합] 동의과학대·경남정보대, 각종 수상 및 특강 개최 눈길</t>
+          <t>K-핵잠이 던진 새판…HD현대·한화 '협력과 경쟁' 딜레마</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260602144105335537f21df127_1</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=127309</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:52:00 +0900</t>
+          <t>Fri, 29 May 2026 14:26:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202606021442280788837f21df12711222312362.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202606021442280788837f21df12711222312362.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202605/127309_112204_2951_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202605/127309_112204_2951_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3715,21 +3717,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>부울경 방산 인재 육성 본격화.. 경남정보대, 특강 화제</t>
+          <t>Creating a business-friendly policy ecosystem is key to Korea’s manufac...</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=842079</t>
+          <t>https://n.news.naver.com/mnews/article/640/0000089168?sid=110</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:44:00 +0900</t>
+          <t>Fri, 29 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202606/842079_855400_2824_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202606/842079_855400_2824_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/640/2026/05/29/0000089168_001_20260529100110885.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/640/2026/05/29/0000089168_001_20260529100110885.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3739,21 +3741,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>15개월 시정공백 끝낼 창원특례시 시장후보 4인 공약</t>
+          <t>[김동원의 이코노믹스] 기업 친화적 정책 생태계 만들어야 한국 제조업...</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://www.newsgn.com/news/articleView.html?idxno=554981</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003526556?sid=110</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 18:24:00 +0900</t>
+          <t>Fri, 29 May 2026 00:14:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://cdn.newsgn.com/news/thumbnail/202606/554981_361763_2345_v150.jpg", IMAGE("https://cdn.newsgn.com/news/thumbnail/202606/554981_361763_2345_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/05/29/0003526556_001_20260529053237448.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/05/29/0003526556_001_20260529053237448.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3763,21 +3765,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>[부산ㆍ경남 대학 브리핑 모음(6월1일)] 동의대 K-뷰티학과, 베트남 인트...</t>
+          <t>기업이 캠퍼스로 왔다···전북대·탈레스코리아 '산학협력'에 속도</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202605310842445790568</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2433457</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 08:02:00 +0900</t>
+          <t>Wed, 27 May 2026 15:54:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/05/31/202605310842445790568-2-668491.jpg", IMAGE("https://image.dnews.co.kr/photo/photo/2026/05/31/202605310842445790568-2-668491.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2433457_1268751_5344_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2433457_1268751_5344_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3787,21 +3789,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>동양대, Yes-UP DYU 취창업전문가 특강 운영</t>
+          <t>[정책의 맥]산업 新르네상스, 기업과 함께 싸워줄 공학교육 전환기</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://www.kgnews.co.kr/news/article.html?no=898019</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005768122?sid=110</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Sun, 31 May 2026 13:42:00 +0900</t>
+          <t>Wed, 27 May 2026 09:27:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://www.kgnews.co.kr/data/photos/20260522/art_17801971535159_6edc3a.jpg", IMAGE("https://www.kgnews.co.kr/data/photos/20260522/art_17801971535159_6edc3a.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/05/27/0005768122_001_20260527151111337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/05/27/0005768122_001_20260527151111337.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3811,21 +3813,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>동양대 군사학과, 방위산업·국방 R&amp;amp;D 진로 특강 개최</t>
+          <t>전북대, ‘학부생부터 글로벌 방산기업과 연결’…K-방산 인재양성 새 ...</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://www.gukjenews.com/news/articleView.html?idxno=3595705</t>
+          <t>https://www.viva100.com/article/20260526500712</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 18:48:00 +0900</t>
+          <t>Tue, 26 May 2026 14:42:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202605/3595705_3753692_4549_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202605/3595705_3753692_4549_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/05/26/.cache/512/20260526500704.jpg?v=20260604180646", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/05/26/.cache/512/20260526500704.jpg?v=20260604180646"))</f>
         <v/>
       </c>
     </row>
@@ -3835,21 +3837,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>K-핵잠이 던진 새판…HD현대·한화 '협력과 경쟁' 딜레마</t>
+          <t>전북대-탈레스코리아, 글로벌 방산·우주 인재양성 협력 '속도'</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=127309</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003431295?sid=102</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 14:26:00 +0900</t>
+          <t>Tue, 26 May 2026 14:37:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202605/127309_112204_2951_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202605/127309_112204_2951_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/26/0003431295_001_20260526143710089.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/26/0003431295_001_20260526143710089.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3859,21 +3861,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Creating a business-friendly policy ecosystem is key to Korea’s manufac...</t>
+          <t>전북대·탈레스코리아 &amp;quot;방산·우주 인재 양성 협력 확대&amp;quot;</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/640/0000089168?sid=110</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013967151?sid=102</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 10:00:00 +0900</t>
+          <t>Tue, 26 May 2026 11:38:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/640/2026/05/29/0000089168_001_20260529100110885.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/640/2026/05/29/0000089168_001_20260529100110885.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/05/26/NISI20260526_0002144874_web_20260526113009_20260526113916721.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/05/26/NISI20260526_0002144874_web_20260526113009_20260526113916721.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3883,21 +3885,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[김동원의 이코노믹스] 기업 친화적 정책 생태계 만들어야 한국 제조업...</t>
+          <t>[윤은기의 X경영(80)] 초가속 시대, '시간 압축'이 승패를 가른다</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003526556?sid=110</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=203091</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 00:14:00 +0900</t>
+          <t>Tue, 26 May 2026 09:50:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/05/29/0003526556_001_20260529053237448.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/05/29/0003526556_001_20260529053237448.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202605/203091_470025_4822_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202605/203091_470025_4822_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3907,21 +3909,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[부산ㆍ경남 대학 브리핑 모음(5월28일)] 동서대 디자인대학, 미국 패션...</t>
+          <t>“증시만 호황인 건 비정상, 실물경제도 같이 살아야 선진국형”</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202605271640520080204</t>
+          <t>https://n.news.naver.com/mnews/article/262/0000019395?sid=101</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 08:02:00 +0900</t>
+          <t>Mon, 25 May 2026 07:01:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/05/27/202605271640520080204-2-667920.jpg", IMAGE("https://image.dnews.co.kr/photo/photo/2026/05/27/202605271640520080204-2-667920.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/05/25/0000019395_001_20260525070110630.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/05/25/0000019395_001_20260525070110630.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3931,21 +3933,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>기업이 캠퍼스로 왔다···전북대·탈레스코리아 '산학협력'에 속도</t>
+          <t>“한국 2000억 달러 흑자, 미국이 그냥 둘까”</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2433457</t>
+          <t>https://n.news.naver.com/mnews/article/353/0000055533?sid=102</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 15:54:00 +0900</t>
+          <t>Sat, 23 May 2026 00:54:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2433457_1268751_5344_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2433457_1268751_5344_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/353/2026/05/23/0000055533_001_20260523013423648.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/353/2026/05/23/0000055533_001_20260523013423648.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3955,21 +3957,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[정책의 맥]산업 新르네상스, 기업과 함께 싸워줄 공학교육 전환기</t>
+          <t>주가 신기루와 반도체 착시 걷어내야 하는 이유</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005768122?sid=110</t>
+          <t>https://n.news.naver.com/mnews/article/036/0000053637?sid=101</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 09:27:00 +0900</t>
+          <t>Thu, 21 May 2026 18:54:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/05/27/0005768122_001_20260527151111337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/05/27/0005768122_001_20260527151111337.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/036/2026/05/21/0000053637_001_20260601094213980.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/036/2026/05/21/0000053637_001_20260601094213980.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3979,21 +3981,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>'제2회 우주항공의 날' 기념식 27일 사천서 개최</t>
+          <t>'방산 불모지' 전북, 탄소 입고 다시 뛴다...첨단소재로 판 바꾼 전북 방...</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>http://www.gndomin.com/news/articleView.html?idxno=476754</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=440278</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 18:28:00 +0900</t>
+          <t>Thu, 21 May 2026 16:20:00 +0900</t>
         </is>
       </c>
       <c r="E148">
-        <f>HYPERLINK("http://www.gndomin.com/image/logo/snslogo_20240325100844.png", IMAGE("http://www.gndomin.com/image/logo/snslogo_20240325100844.png"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/440278_149320_1654_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/440278_149320_1654_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4003,22 +4005,23 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>전북대, ‘학부생부터 글로벌 방산기업과 연결’…K-방산 인재양성 새 ...</t>
+          <t>[Who Is ?] 박재석 SNT다이내믹스 대표이사 사장</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260526500712</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=438134</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 14:42:00 +0900</t>
-        </is>
-      </c>
-      <c r="E149">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/05/26/.cache/512/20260526500704.jpg?v=20260604175111", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/05/26/.cache/512/20260526500704.jpg?v=20260604175111"))</f>
-        <v/>
+          <t>Wed, 20 May 2026 07:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -4027,21 +4030,21 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>전북대-탈레스코리아, 글로벌 방산·우주 인재양성 협력 '속도'</t>
+          <t>국립창원대 과학기술원 공약, '신설' 아닌 '전환'이 문제 [6.3 쟁점 점검...</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003431295?sid=102</t>
+          <t>https://www.idomin.com/news/articleView.html?idxno=2006078</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 14:37:00 +0900</t>
+          <t>Tue, 19 May 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E150">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/26/0003431295_001_20260526143710089.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/26/0003431295_001_20260526143710089.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.idomin.com/news/photo/202605/2006078_709045_2504.jpg", IMAGE("https://cdn.idomin.com/news/photo/202605/2006078_709045_2504.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4051,21 +4054,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>전북대·탈레스코리아 &amp;quot;방산·우주 인재 양성 협력 확대&amp;quot;</t>
+          <t>(박창식의 K-국방)한국 방위 역량, 이제 자기 비하를 멈출 때다</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013967151?sid=102</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1301220&amp;inflow=N</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 11:38:00 +0900</t>
+          <t>Tue, 19 May 2026 06:02:00 +0900</t>
         </is>
       </c>
       <c r="E151">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/05/26/NISI20260526_0002144874_web_20260526113009_20260526113916721.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/05/26/NISI20260526_0002144874_web_20260526113009_20260526113916721.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/19/1301220/attach.jpg?v=202605181605", IMAGE("https://image.newstomato.com/newsimg/2026/5/19/1301220/attach.jpg?v=202605181605"))</f>
         <v/>
       </c>
     </row>
@@ -4075,21 +4078,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>[윤은기의 X경영(80)] 초가속 시대, '시간 압축'이 승패를 가른다</t>
+          <t>방위사업청, 美 국방획득대학교와 공동 워크숍 개최… &amp;quot;첨단 획득역량 ...</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=203091</t>
+          <t>https://www.gukjenews.com/news/articleView.html?idxno=3585775</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 09:50:00 +0900</t>
+          <t>Tue, 19 May 2026 03:38:00 +0900</t>
         </is>
       </c>
       <c r="E152">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202605/203091_470025_4822_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202605/203091_470025_4822_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202605/3585775_3741735_5024_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202605/3585775_3741735_5024_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4099,21 +4102,21 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>“증시만 호황인 건 비정상, 실물경제도 같이 살아야 선진국형”</t>
+          <t>강원대 첨단군사과학기술연구소 ‘국방사업관리사 자격증 과정 운영대...</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/262/0000019395?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441873?sid=102</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Mon, 25 May 2026 07:01:00 +0900</t>
+          <t>Mon, 18 May 2026 18:36:00 +0900</t>
         </is>
       </c>
       <c r="E153">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/05/25/0000019395_001_20260525070110630.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/05/25/0000019395_001_20260525070110630.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/18/0002441873_001_20260518183616443.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/18/0002441873_001_20260518183616443.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4123,22 +4126,23 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>“한국 2000억 달러 흑자, 미국이 그냥 둘까”</t>
+          <t>방사청, 미 국방획득대학교와 실무급 워크숍</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/353/0000055533?sid=102</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260519/1/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 00:54:00 +0900</t>
-        </is>
-      </c>
-      <c r="E154">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/353/2026/05/23/0000055533_001_20260523013423648.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/353/2026/05/23/0000055533_001_20260523013423648.jpg?type=w800"))</f>
-        <v/>
+          <t>Mon, 18 May 2026 16:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -4147,21 +4151,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>주가 신기루와 반도체 착시 걷어내야 하는 이유</t>
+          <t>인·태 시대의 '평화 거점' 한국, 갈등의 파고를 넘는 가교가 될 것인가...</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/036/0000053637?sid=101</t>
+          <t>http://www.tongilnews.com/news/articleView.html?idxno=216521</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Thu, 21 May 2026 18:54:00 +0900</t>
+          <t>Mon, 18 May 2026 14:06:00 +0900</t>
         </is>
       </c>
       <c r="E155">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/036/2026/05/21/0000053637_001_20260601094213980.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/036/2026/05/21/0000053637_001_20260601094213980.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.tongilnews.com/news/thumbnail/202605/216521_115974_247_v150.jpg", IMAGE("https://cdn.tongilnews.com/news/thumbnail/202605/216521_115974_247_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4171,21 +4175,21 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>'방산 불모지' 전북, 탄소 입고 다시 뛴다...첨단소재로 판 바꾼 전북 방...</t>
+          <t>전북대학교, 방사청 '국방사업관리사' 교육기관 2년 연속 선정…방산 전...</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=440278</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=202591</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Thu, 21 May 2026 16:20:00 +0900</t>
+          <t>Mon, 18 May 2026 12:36:00 +0900</t>
         </is>
       </c>
       <c r="E156">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/440278_149320_1654_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/440278_149320_1654_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202605/202591_469341_365_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202605/202591_469341_365_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4195,21 +4199,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>사천서 우주 체험하고, 김해서 별 보고</t>
+          <t>방사청, 美 국방획득대학과 '애자일 무기획득' 5일 합숙 토론</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003721222?sid=102</t>
+          <t>https://www.newspim.com/news/view/20260518000484</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Thu, 21 May 2026 04:33:00 +0900</t>
+          <t>Mon, 18 May 2026 10:56:00 +0900</t>
         </is>
       </c>
       <c r="E157">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://img.newspim.com/news/2026/05/18/2605181053393780_t1.jpg", IMAGE("https://img.newspim.com/news/2026/05/18/2605181053393780_t1.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4219,21 +4223,21 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>제2회 우주항공의 날, 경남 곳곳서 우주항공 체험 행사 풍성</t>
+          <t>방사청, 美 국방획득대와 공동 워크숍…획득인력 양성체계 공유</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003720980?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005359123?sid=100</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Wed, 20 May 2026 10:19:00 +0900</t>
+          <t>Mon, 18 May 2026 10:27:00 +0900</t>
         </is>
       </c>
       <c r="E158">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/05/20/0003720980_001_20260520101916617.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/05/20/0003720980_001_20260520101916617.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/05/18/0005359123_001_20260518102817596.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/05/18/0005359123_001_20260518102817596.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4243,21 +4247,21 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>경남도, 우주항공의 날·주간 맞아 도내 전역서 기념행사 다채</t>
+          <t>방사청·美 국방획득대, 韓美 국방획득인력 양성체계 및 첨단 획득제도...</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://www.cnbnews.com/news/articleView.html?idxno=1002192</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002791828?sid=100</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Wed, 20 May 2026 10:04:00 +0900</t>
+          <t>Mon, 18 May 2026 09:03:00 +0900</t>
         </is>
       </c>
       <c r="E159">
-        <f>HYPERLINK("https://cdn.cnbnews.com/news/photo/202605/1002192_502105_1779237915.jpg", IMAGE("https://cdn.cnbnews.com/news/photo/202605/1002192_502105_1779237915.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/05/18/0002791828_001_20260518090308259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/05/18/0002791828_001_20260518090308259.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4267,21 +4271,21 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>'우주항공 주간' 경남 곳곳서 정책·산업·문화 아우르는 연계행사 풍성</t>
+          <t>[기술간첩] ⑤ '23조 원' 소는 잃었어도 외양간은 계속 고쳐야…</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003429368?sid=102</t>
+          <t>https://www.bizhankook.com/bk/article/32273</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Wed, 20 May 2026 08:59:00 +0900</t>
+          <t>Fri, 15 May 2026 16:16:00 +0900</t>
         </is>
       </c>
       <c r="E160">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/20/0003429368_001_20260520085910062.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/20/0003429368_001_20260520085910062.png?type=w800"))</f>
+        <f>HYPERLINK("https://www.bizhankook.com/upload/bk/article/202605/thumb/32273-78198-sample.jpg", IMAGE("https://www.bizhankook.com/upload/bk/article/202605/thumb/32273-78198-sample.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4291,23 +4295,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>[Who Is ?] 박재석 SNT다이내믹스 대표이사 사장</t>
+          <t>글로벌 AI-방산-반도체 인재 양성… 매머드급 국가거점국립대로 새 도약</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=438134</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003719813?sid=102</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Wed, 20 May 2026 07:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Fri, 15 May 2026 04:34:00 +0900</t>
+        </is>
+      </c>
+      <c r="E161">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/05/15/0003719813_001_20260515043415656.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/05/15/0003719813_001_20260515043415656.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="162">
@@ -4316,21 +4319,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>'우주항공의 날' 경남 곳곳 행사 다채</t>
+          <t>5월 14일 베이징 회담은 결승전이 아니다</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>http://www.gndomin.com/news/articleView.html?idxno=476080</t>
+          <t>https://n.news.naver.com/mnews/article/047/0002515553?sid=104</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 18:22:00 +0900</t>
+          <t>Wed, 13 May 2026 17:31:00 +0900</t>
         </is>
       </c>
       <c r="E162">
-        <f>HYPERLINK("http://www.gndomin.com/image/logo/snslogo_20240325100844.png", IMAGE("http://www.gndomin.com/image/logo/snslogo_20240325100844.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/047/2026/05/13/0002515553_001_20260513173110461.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/047/2026/05/13/0002515553_001_20260513173110461.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4340,22 +4343,23 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>국립창원대 과학기술원 공약, '신설' 아닌 '전환'이 문제 [6.3 쟁점 점검...</t>
+          <t>[Who Is ?] 손경석 퍼스텍 대표이사 사장</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://www.idomin.com/news/articleView.html?idxno=2006078</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=437052</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E163">
-        <f>HYPERLINK("https://cdn.idomin.com/news/photo/202605/2006078_709045_2504.jpg", IMAGE("https://cdn.idomin.com/news/photo/202605/2006078_709045_2504.jpg"))</f>
-        <v/>
+          <t>Wed, 13 May 2026 07:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -4364,21 +4368,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>경남도 '제2회 우주항공의 날' 주간 연계 행사 추진</t>
+          <t>[인터뷰]김태흠 &amp;quot;대전-충남 통합, 9조원 국세·권한 이양되면 추진&amp;quot;</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://www.ulsanpress.net/news/articleView.html?idxno=575488</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001142666?sid=162</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:26:00 +0900</t>
+          <t>Tue, 12 May 2026 05:21:00 +0900</t>
         </is>
       </c>
       <c r="E164">
-        <f>HYPERLINK("https://cdn.ulsanpress.net/news/thumbnail/202605/575488_273004_2441_v150.jpg", IMAGE("https://cdn.ulsanpress.net/news/thumbnail/202605/575488_273004_2441_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/05/12/0001142666_001_20260512072307509.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/05/12/0001142666_001_20260512072307509.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4388,21 +4392,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>경남도, '제2회 우주항공의 날' 맞아 정책·산업·문화 아우르는 '우주항...</t>
+          <t>국립창원대, 인도 조선해양 고위급 대표단 방문</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://www.newsgn.com/news/articleView.html?idxno=552950</t>
+          <t>http://www.breaknews.com/1206310</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 16:26:00 +0900</t>
+          <t>Mon, 11 May 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E165">
-        <f>HYPERLINK("https://cdn.newsgn.com/news/thumbnail/202605/552950_359588_3749_v150.jpg", IMAGE("https://cdn.newsgn.com/news/thumbnail/202605/552950_359588_3749_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.breaknewsgn.com/imgdata/breaknewsgn_com/202605/2026051150412533.jpg", IMAGE("https://www.breaknewsgn.com/imgdata/breaknewsgn_com/202605/2026051150412533.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4412,21 +4416,21 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>경남 전역서 ‘우주항공 주간’ 연계 행사 풍성</t>
+          <t>물가·청년일자리로 쏠린 민심…경기지사 후보들 해법 경쟁</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260519010005201</t>
+          <t>https://www.kgnews.co.kr/news/article.html?no=894943</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:22:00 +0900</t>
+          <t>Sun, 10 May 2026 20:00:00 +0900</t>
         </is>
       </c>
       <c r="E166">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/05m/20d/2026052001001022300056201.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/05m/20d/2026052001001022300056201.jpg"))</f>
+        <f>HYPERLINK("https://www.kgnews.co.kr/data/photos/20260519/art_17784002216015_6d0c30.png", IMAGE("https://www.kgnews.co.kr/data/photos/20260519/art_17784002216015_6d0c30.png"))</f>
         <v/>
       </c>
     </row>
@@ -4436,649 +4440,22 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>(박창식의 K-국방)한국 방위 역량, 이제 자기 비하를 멈출 때다</t>
+          <t>'라이즈' 재구조화 '앵커' 체계…진학·취업·정주 선순환</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1301220&amp;inflow=N</t>
+          <t>https://www.hidomin.com/news/articleView.html?idxno=704332</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 06:02:00 +0900</t>
+          <t>Thu, 07 May 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E167">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/19/1301220/attach.jpg?v=202605181605", IMAGE("https://image.newstomato.com/newsimg/2026/5/19/1301220/attach.jpg?v=202605181605"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>167</v>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>방위사업청, 美 국방획득대학교와 공동 워크숍 개최… &amp;quot;첨단 획득역량 ...</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>https://www.gukjenews.com/news/articleView.html?idxno=3585775</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Tue, 19 May 2026 03:38:00 +0900</t>
-        </is>
-      </c>
-      <c r="E168">
-        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202605/3585775_3741735_5024_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202605/3585775_3741735_5024_v150.jpg"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>168</v>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>강원대 첨단군사과학기술연구소 ‘국방사업관리사 자격증 과정 운영대...</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441873?sid=102</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Mon, 18 May 2026 18:36:00 +0900</t>
-        </is>
-      </c>
-      <c r="E169">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/18/0002441873_001_20260518183616443.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/18/0002441873_001_20260518183616443.jpg?type=w800"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>169</v>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>방사청, 미 국방획득대학교와 실무급 워크숍</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260519/1/ATCE_CTGR_0010020000/view.do</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Mon, 18 May 2026 16:18:00 +0900</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>170</v>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>인·태 시대의 '평화 거점' 한국, 갈등의 파고를 넘는 가교가 될 것인가...</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>http://www.tongilnews.com/news/articleView.html?idxno=216521</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Mon, 18 May 2026 14:06:00 +0900</t>
-        </is>
-      </c>
-      <c r="E171">
-        <f>HYPERLINK("https://cdn.tongilnews.com/news/thumbnail/202605/216521_115974_247_v150.jpg", IMAGE("https://cdn.tongilnews.com/news/thumbnail/202605/216521_115974_247_v150.jpg"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>171</v>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>전북대학교, 방사청 '국방사업관리사' 교육기관 2년 연속 선정…방산 전...</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=202591</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Mon, 18 May 2026 12:36:00 +0900</t>
-        </is>
-      </c>
-      <c r="E172">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202605/202591_469341_365_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202605/202591_469341_365_v150.jpg"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>172</v>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>방사청, 美 국방획득대학과 '애자일 무기획득' 5일 합숙 토론</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>https://www.newspim.com/news/view/20260518000484</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Mon, 18 May 2026 10:56:00 +0900</t>
-        </is>
-      </c>
-      <c r="E173">
-        <f>HYPERLINK("https://img.newspim.com/news/2026/05/18/2605181053393780_t1.jpg", IMAGE("https://img.newspim.com/news/2026/05/18/2605181053393780_t1.jpg"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>173</v>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>방사청, 美 국방획득대와 공동 워크숍…획득인력 양성체계 공유</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005359123?sid=100</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Mon, 18 May 2026 10:27:00 +0900</t>
-        </is>
-      </c>
-      <c r="E174">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/05/18/0005359123_001_20260518102817596.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/05/18/0005359123_001_20260518102817596.jpg?type=w800"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>174</v>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>방사청·美 국방획득대, 韓美 국방획득인력 양성체계 및 첨단 획득제도...</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002791828?sid=100</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Mon, 18 May 2026 09:03:00 +0900</t>
-        </is>
-      </c>
-      <c r="E175">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/05/18/0002791828_001_20260518090308259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/05/18/0002791828_001_20260518090308259.jpg?type=w800"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>175</v>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>[기술간첩] ⑤ '23조 원' 소는 잃었어도 외양간은 계속 고쳐야…</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>https://www.bizhankook.com/bk/article/32273</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Fri, 15 May 2026 16:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E176">
-        <f>HYPERLINK("https://www.bizhankook.com/upload/bk/article/202605/thumb/32273-78198-sample.jpg", IMAGE("https://www.bizhankook.com/upload/bk/article/202605/thumb/32273-78198-sample.jpg"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>176</v>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>글로벌 AI-방산-반도체 인재 양성… 매머드급 국가거점국립대로 새 도약</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003719813?sid=102</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Fri, 15 May 2026 04:34:00 +0900</t>
-        </is>
-      </c>
-      <c r="E177">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/05/15/0003719813_001_20260515043415656.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/05/15/0003719813_001_20260515043415656.jpg?type=w800"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>177</v>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>대진대학교, 개교 34주년 기념식 개최… ‘K-방산·AI 선도대학’ 도약...</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202605141437242740775</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Thu, 14 May 2026 20:22:00 +0900</t>
-        </is>
-      </c>
-      <c r="E178">
-        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/05/14/202605141437242740775-2-665578.jpg", IMAGE("https://image.dnews.co.kr/photo/photo/2026/05/14/202605141437242740775-2-665578.jpg"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>178</v>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>대진대, 개교 34주년…&amp;quot;K-방산·AI 선도대학 도약&amp;quot; 선언</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/666/0000107051?sid=102</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Thu, 14 May 2026 18:49:00 +0900</t>
-        </is>
-      </c>
-      <c r="E179">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/666/2026/05/14/0000107051_001_20260514184921026.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/666/2026/05/14/0000107051_001_20260514184921026.jpg?type=w800"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>179</v>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>폴리텍대-한화에어로스페이스, 우주항공·방산 인재 양성 협약 체결</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>http://www.lawissue.co.kr/view.php?ud=202605141722574466f4ab64559d_12</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Thu, 14 May 2026 17:24:00 +0900</t>
-        </is>
-      </c>
-      <c r="E180">
-        <f>HYPERLINK("https://cliimage.commutil.kr/lawissue_www/nimg/default_bimg.png?p=003", IMAGE("https://cliimage.commutil.kr/lawissue_www/nimg/default_bimg.png?p=003"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>180</v>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>한화에어로-폴리텍대, 항공우주·방산 기술인재 양성 '맞손'</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004147018?sid=102</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Thu, 14 May 2026 17:12:00 +0900</t>
-        </is>
-      </c>
-      <c r="E181">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/079/2026/05/14/0004147018_001_20260514171216898.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/079/2026/05/14/0004147018_001_20260514171216898.jpg?type=w800"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>181</v>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>대진대 개교 34주년 기념식 개최...  'K-방산/AI 선도대학' 도약 선포</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=610088</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Thu, 14 May 2026 14:24:00 +0900</t>
-        </is>
-      </c>
-      <c r="E182">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202605/610088_523297_2359_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202605/610088_523297_2359_v150.jpg"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>182</v>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>5월 14일 베이징 회담은 결승전이 아니다</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/047/0002515553?sid=104</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Wed, 13 May 2026 17:31:00 +0900</t>
-        </is>
-      </c>
-      <c r="E183">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/047/2026/05/13/0002515553_001_20260513173110461.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/047/2026/05/13/0002515553_001_20260513173110461.jpg?type=w800"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>183</v>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>[Who Is ?] 손경석 퍼스텍 대표이사 사장</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=437052</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Wed, 13 May 2026 07:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>184</v>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>경북도 ‘앵커’ 대학 지원 사업..청년 지역 정착 견인</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/009/0005679052?sid=102</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Tue, 12 May 2026 18:59:00 +0900</t>
-        </is>
-      </c>
-      <c r="E185">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/009/2026/05/12/0005679052_001_20260512185909544.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/009/2026/05/12/0005679052_001_20260512185909544.jpg?type=w800"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>185</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>[부산ㆍ경남 대학 브리핑 모음(5월12일)] 국립창원대 “인도 고위급 대...</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202605111705002220305</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Tue, 12 May 2026 08:40:00 +0900</t>
-        </is>
-      </c>
-      <c r="E186">
-        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/05/11/202605111705002220305-2-664832.jpg", IMAGE("https://image.dnews.co.kr/photo/photo/2026/05/11/202605111705002220305-2-664832.jpg"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>186</v>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>[인터뷰]김태흠 &amp;quot;대전-충남 통합, 9조원 국세·권한 이양되면 추진&amp;quot;</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001142666?sid=162</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Tue, 12 May 2026 05:21:00 +0900</t>
-        </is>
-      </c>
-      <c r="E187">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/05/12/0001142666_001_20260512072307509.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/05/12/0001142666_001_20260512072307509.jpg?type=w800"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>187</v>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>국립창원대, 인도 조선해양 고위급 대표단 방문</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>http://www.breaknews.com/1206310</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Mon, 11 May 2026 16:38:00 +0900</t>
-        </is>
-      </c>
-      <c r="E188">
-        <f>HYPERLINK("https://www.breaknewsgn.com/imgdata/breaknewsgn_com/202605/2026051150412533.jpg", IMAGE("https://www.breaknewsgn.com/imgdata/breaknewsgn_com/202605/2026051150412533.jpg"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>188</v>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>물가·청년일자리로 쏠린 민심…경기지사 후보들 해법 경쟁</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>https://www.kgnews.co.kr/news/article.html?no=894943</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Sun, 10 May 2026 20:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E189">
-        <f>HYPERLINK("https://www.kgnews.co.kr/data/photos/20260519/art_17784002216015_6d0c30.png", IMAGE("https://www.kgnews.co.kr/data/photos/20260519/art_17784002216015_6d0c30.png"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>189</v>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>경북도 ‘앵커 사업’ 성과 가시화… 지역대학·기업 상생 모델 주목</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>http://www.breaknews.com/1205573</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Thu, 07 May 2026 17:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E190">
-        <f>HYPERLINK("https://dk.breaknews.com/imgdata/dk_breaknews_com/202605/2026050745561906.jpg", IMAGE("https://dk.breaknews.com/imgdata/dk_breaknews_com/202605/2026050745561906.jpg"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>190</v>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>지역대학서 키운 인재, 지역기업 취업으로…경북형 청년 정주모델 성과</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>https://www.kyongbuk.co.kr/news/articleView.html?idxno=4072122</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Thu, 07 May 2026 16:24:00 +0900</t>
-        </is>
-      </c>
-      <c r="E191">
-        <f>HYPERLINK("https://cdn.kyongbuk.co.kr/news/photo/202605/4072122_803539_2151.jpg", IMAGE("https://cdn.kyongbuk.co.kr/news/photo/202605/4072122_803539_2151.jpg"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>191</v>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>'라이즈' 재구조화 '앵커' 체계…진학·취업·정주 선순환</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>https://www.hidomin.com/news/articleView.html?idxno=704332</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Thu, 07 May 2026 14:18:00 +0900</t>
-        </is>
-      </c>
-      <c r="E192">
         <f>HYPERLINK("https://cdn.hidomin.com/news/photo/202605/704332_404734_0928.jpg", IMAGE("https://cdn.hidomin.com/news/photo/202605/704332_404734_0928.jpg"))</f>
         <v/>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>192</v>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>경북도 ‘앵커’ 사업 성과…청년 정착·기업 경쟁력 동시 강화</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>https://www.kukinews.com/article/view/kuk202605070060</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Thu, 07 May 2026 11:58:00 +0900</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -5092,7 +4469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5153,21 +4530,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>** [장원준 칼럼] 차기 한미 정상회담 의제로 ‘방산 공동생산 동맹’ 제안...</t>
+          <t>** [기고]교육부 최초 승인 '첨단방위산업학과', 지역 방산혁신의 새 희망</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260527500120</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006292697?sid=110</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 11:16:00 +0900</t>
+          <t>Fri, 29 May 2026 06:01:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/05/27/.cache/512/20260527500119.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/05/27/.cache/512/20260527500119.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/018/2026/05/29/0006292697_001_20260529060107244.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/018/2026/05/29/0006292697_001_20260529060107244.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -5177,21 +4554,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>K방산 수출, 이제는 정보다 [기고]</t>
+          <t>** [장원준 칼럼] 차기 한미 정상회담 의제로 ‘방산 공동생산 동맹’ 제안...</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000927039?sid=110</t>
+          <t>https://www.news2day.co.kr/article/20260527500120</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 04:31:00 +0900</t>
+          <t>Wed, 27 May 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/05/27/.cache/512/20260527500119.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/05/27/.cache/512/20260527500119.png"))</f>
         <v/>
       </c>
     </row>
@@ -5201,21 +4578,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>전쟁은 '생산능력'이다 : 미국의 무기 부족이 던지는 경고[기고]</t>
+          <t>K방산 수출, 이제는 정보다 [기고]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026042014032324372</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000927039?sid=110</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 14:12:00 +0900</t>
+          <t>Thu, 23 Apr 2026 04:31:00 +0900</t>
         </is>
       </c>
       <c r="E5">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -5225,21 +4602,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>첨단항공엔진, 지금 시작하지 않으면 골든타임 놓친다 [기고]</t>
+          <t>전쟁은 '생산능력'이다 : 미국의 무기 부족이 던지는 경고[기고]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026033015455091764</t>
+          <t>https://news.mtn.co.kr/news-detail/2026042014032324372</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 15:52:00 +0900</t>
+          <t>Mon, 20 Apr 2026 14:12:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/04/20/2026042014032324372_00_777.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -5321,21 +4698,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[기고]교육부 최초 승인 '첨단방위산업학과', 지역 방산혁신의 새 희망</t>
+          <t>[최기일 칼럼] 軍 방독면 입찰 계약 구조 개선해야</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006292697?sid=110</t>
+          <t>https://www.news2day.co.kr/article/20260518500244</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 06:01:00 +0900</t>
+          <t>Mon, 18 May 2026 20:54:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/018/2026/05/29/0006292697_001_20260529060107244.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/018/2026/05/29/0006292697_001_20260529060107244.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/05/18/.cache/512/20260518500243.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/05/18/.cache/512/20260518500243.png"))</f>
         <v/>
       </c>
     </row>
@@ -5345,44 +4722,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[최기일 칼럼] 軍 방독면 입찰 계약 구조 개선해야</t>
+          <t>미국도 중국도 원하지 않는 최악의 시나리오 [김영근 교수 칼럼]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260518500244</t>
+          <t>https://www.mediafine.co.kr/news/articleView.html?idxno=78947</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 18 May 2026 20:54:00 +0900</t>
+          <t>Fri, 15 May 2026 17:58:00 +0900</t>
         </is>
       </c>
       <c r="E11">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/05/18/.cache/512/20260518500243.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/05/18/.cache/512/20260518500243.png"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>미국도 중국도 원하지 않는 최악의 시나리오 [김영근 교수 칼럼]</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://www.mediafine.co.kr/news/articleView.html?idxno=78947</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Fri, 15 May 2026 17:58:00 +0900</t>
-        </is>
-      </c>
-      <c r="E12">
         <f>HYPERLINK("https://cdn.mediafine.co.kr/news/photo/202605/78947_115306_5142.jpg", IMAGE("https://cdn.mediafine.co.kr/news/photo/202605/78947_115306_5142.jpg"))</f>
         <v/>
       </c>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E167"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,21 +462,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
+          <t>** AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
+          <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
+          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
         </is>
       </c>
       <c r="E2">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
         <v/>
       </c>
     </row>
@@ -486,21 +486,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -510,21 +510,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+          <t>Tue, 19 May 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -534,21 +534,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>전북대, 국방사업관리사 교육기관 2년 연속 선정</t>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=839163</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 07:56:00 +0900</t>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
         </is>
       </c>
       <c r="E5">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -558,21 +558,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+          <t>전북대, 국방사업관리사 교육기관 2년 연속 선정</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=839163</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+          <t>Sun, 17 May 2026 07:56:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -582,21 +582,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -606,21 +606,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
       <c r="E8">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -630,21 +630,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E9">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -654,21 +654,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -678,21 +678,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E11">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -702,21 +702,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E12">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -726,21 +726,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E13">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -750,21 +750,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E14">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -774,21 +774,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E15">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -798,21 +798,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E16">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -846,21 +846,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E18">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -870,23 +870,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+        </is>
+      </c>
+      <c r="E19">
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -895,22 +894,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
-        </is>
-      </c>
-      <c r="E20">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
-        <v/>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -919,21 +919,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -943,21 +943,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -967,21 +967,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -991,21 +991,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1015,21 +1015,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1039,21 +1039,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1063,21 +1063,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1087,21 +1087,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E28">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1111,21 +1111,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1135,21 +1135,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>“AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
+          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
+          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1159,21 +1159,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
+          <t>“AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
+          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
         </is>
       </c>
       <c r="E31">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1183,21 +1183,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
+          <t>전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
+          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1207,21 +1207,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
+          <t>K-방산, ‘수출 호황’ 넘어 지속 성장으로…정책·산업 생태계 재설계...</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
+          <t>https://www.asiatoday.co.kr/view.php?key=20260225010007356</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
+          <t>Wed, 25 Feb 2026 11:46:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/02m/25d/2026022501001345400073561.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1231,21 +1231,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
+          <t>'백발백중' K2, 독일 레오파르트 꺾고 1등했는데...6개월 방치하다 수주...</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000915993?sid=100</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
+          <t>Tue, 24 Feb 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/24/0000915993_001_20260224140119313.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1255,21 +1255,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
+          <t>압도적 성능 K2 전차, 폴란드 장관이 '러브샷'까지 제안한 배경은</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000913811?sid=100</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
+          <t>Tue, 10 Feb 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/02/10/0000913811_001_20260210140113235.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1279,21 +1279,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
+          <t>10년 난제 K2 전차 변속기...외국선 '호평' 국내선 '불합격' 이유는?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000911207?sid=102</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
+          <t>Tue, 27 Jan 2026 14:02:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/27/0000911207_001_20260128123007493.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1303,21 +1303,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
+          <t>전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
+          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1327,21 +1327,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
+          <t>전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
+          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
+          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>HYPERLINK("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png", IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1351,21 +1351,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
+          <t>전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
+          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
+          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png", IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png"))</f>
         <v/>
       </c>
     </row>
@@ -1375,21 +1375,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
+          <t>전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
+          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1399,21 +1399,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>배틀그라운드 기술이 전장으로...K-방산, 게임사와 'AI 전쟁' 준비한다</t>
+          <t>K2 전차, 6번 실패하고 7번째는 아예 포기...대통령 한 마디에 실마리 찾...</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.newsquest.co.kr/news/articleView.html?idxno=267287</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000908662?sid=102</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Thu, 04 Jun 2026 15:00:00 +0900</t>
+          <t>Tue, 13 Jan 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg", IMAGE("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/01/13/0000908662_001_20260113140115946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1423,21 +1423,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[단독] 4월에 국방과학연구소 합동 안전검사도 못 막은 한화에어로 참사</t>
+          <t>배틀그라운드 기술이 전장으로...K-방산, 게임사와 'AI 전쟁' 준비한다</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934274?sid=102</t>
+          <t>https://www.newsquest.co.kr/news/articleView.html?idxno=267287</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 03 Jun 2026 17:01:00 +0900</t>
+          <t>Thu, 04 Jun 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg", IMAGE("https://cdn.newsquest.co.kr/news/thumbnail/202606/267287_168427_93_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1447,21 +1447,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>한화에어로 참사, 미국·EU 방산 입찰 발목 잡나...'대전 사고' 도마 위</t>
+          <t>[단독] 4월에 국방과학연구소 합동 안전검사도 못 막은 한화에어로 참사</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=247498</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934274?sid=102</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 16:02:00 +0900</t>
+          <t>Wed, 03 Jun 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/03/0000934274_001_20260604061345168.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1471,21 +1471,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>반복된 폭발사고…K방산 신뢰도 ‘악영향’</t>
+          <t>한화에어로 참사, 미국·EU 방산 입찰 발목 잡나...'대전 사고' 도마 위</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1302742&amp;inflow=N</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=247498</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:48:00 +0900</t>
+          <t>Tue, 02 Jun 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231", IMAGE("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202606/247498_257207_2618_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1495,23 +1495,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KDDX 보안 감점 공방이 던진 질문…방산 조달 사업의 大원칙은</t>
+          <t>반복된 폭발사고…K방산 신뢰도 ‘악영향’</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/108042</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1302742&amp;inflow=N</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 13:04:00 +0900</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 02 Jun 2026 14:48:00 +0900</t>
+        </is>
+      </c>
+      <c r="E45">
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231", IMAGE("https://image.newstomato.com/newsimg/2026/6/2/1302742/attach.jpg?v=202606031231"))</f>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -1520,21 +1519,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[상생의 힘, 기업가치를 올린다] 김동관의 한화, 방산 넘어 안보 기업으...</t>
+          <t>KDDX 보안 감점 공방이 던진 질문…방산 조달 사업의 大원칙은</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260601151511969112616b072_1</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/108042</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 19:12:00 +0900</t>
+          <t>Tue, 02 Jun 2026 13:04:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://cdn.www.smarttoday.co.kr/w1200/q100/f_jpg/article-images/2026-02-19/8c960c9e-5b3e-44c2-9519-e2d3eb0c56dd.jpg", IMAGE("https://cdn.www.smarttoday.co.kr/w1200/q100/f_jpg/article-images/2026-02-19/8c960c9e-5b3e-44c2-9519-e2d3eb0c56dd.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1544,21 +1543,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[상생의 힘, 기업가치를 올린다] 한화, 방산·조선·우주 국가전략산업...</t>
+          <t>[상생의 힘, 기업가치를 올린다] 김동관의 한화, 방산 넘어 안보 기업으...</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202606011338107634112616b072_1</t>
+          <t>https://www.g-enews.com/view.php?ud=20260601151511969112616b072_1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 19:08:00 +0900</t>
+          <t>Mon, 01 Jun 2026 19:12:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060115333606850112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1568,21 +1567,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>‘K-잠수함’ 1만4000km 잠항, 獨 꺾고 60조 잭팟 터뜨릴까</t>
+          <t>[상생의 힘, 기업가치를 올린다] 한화, 방산·조선·우주 국가전략산업...</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260601500751</t>
+          <t>https://www.g-enews.com/view.php?ud=202606011338107634112616b072_1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 15:32:00 +0900</t>
+          <t>Mon, 01 Jun 2026 19:08:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604180245", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604180245"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026060113574008964112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1592,21 +1591,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
+          <t>‘K-잠수함’ 1만4000km 잠항, 獨 꺾고 60조 잭팟 터뜨릴까</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
+          <t>https://www.viva100.com/article/20260601500751</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 17:40:00 +0900</t>
+          <t>Mon, 01 Jun 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604181551", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/06/01/.cache/512/20260601500736.jpg?v=20260604181551"))</f>
         <v/>
       </c>
     </row>
@@ -1616,21 +1615,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
+          <t>60조 캐나다 잠수함 수주전…K조선 ‘원팀’ 총공세</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052916113069731</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 15:14:00 +0900</t>
+          <t>Fri, 29 May 2026 17:40:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/bFFgrVmxPqSESQuu/image/20260529_172011//10213-1780042722694_08.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1640,21 +1639,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
+          <t>[K-방산 빅뱅/②]한화의 KAI 인수, 독점이 아닌 6가지 근거</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
+          <t>https://www.businessplus.kr/news/articleView.html?idxno=112382</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 17:38:00 +0900</t>
+          <t>Fri, 29 May 2026 15:14:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
+        <f>HYPERLINK("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg", IMAGE("https://cdn.businessplus.kr/news/thumbnail/202605/112382_108441_231_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1664,21 +1663,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
+          <t>美 탄약난 현실화 …&amp;quot;지금이 K방산 진출 적기&amp;quot;</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026052816405142132</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 15:29:00 +0900</t>
+          <t>Thu, 28 May 2026 17:38:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/s0ht1PytIsSgkss6/image/20260528_172308//10160-1779956488104_10.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1688,21 +1687,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
+          <t>KDDX 사업 입찰에서 보안감점이 왜 중요한 변수인가</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031528?sid=101</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Thu, 28 May 2026 10:35:00 +0900</t>
+          <t>Thu, 28 May 2026 15:29:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031528_001_20260528154506997.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1712,21 +1711,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
+          <t>한화오션·HD현대重, 한국형 핵잠 수주전 준비⋯원팀 가능성도</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001031422?sid=101</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 17:23:00 +0900</t>
+          <t>Thu, 28 May 2026 10:35:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/28/0001031422_001_20260528104708912.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1736,23 +1735,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
+          <t>‘2년 표류’ KDDX 2파전 공식화…HD현대重, 입찰 전격 참여 동시에 가처...</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
+          <t>https://n.news.naver.com/mnews/article/117/0004068665?sid=103</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Wed, 27 May 2026 17:23:00 +0900</t>
+        </is>
+      </c>
+      <c r="E55">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/117/2026/05/27/0004068665_001_20260528083608050.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -1761,22 +1759,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
+          <t>‘감점’ vs 설계 공백’…HD현대 ‧ 한화 7조 KDDX 2차 입찰 격돌</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202605260176</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 18:21:00 +0900</t>
-        </is>
-      </c>
-      <c r="E56">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
-        <v/>
+          <t>Wed, 27 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -1785,21 +1784,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
+          <t>한화에어로, KAI 지분 확대… '한국판 스페이스X' 꿈꾼다</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526660?sid=101</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 14:57:00 +0900</t>
+          <t>Tue, 26 May 2026 18:21:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526660_001_20260526182113359.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1809,21 +1808,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
+          <t>한화, KAI 지분 또 샀다… '한국판 스페이스X' 향한 거침없는 직진</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005526446?sid=101</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 10:00:00 +0900</t>
+          <t>Tue, 26 May 2026 14:57:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/014/2026/05/26/0005526446_001_20260526145734135.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1833,21 +1832,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
+          <t>日, K방산 텃밭 노린다…'국가 주도 패키지'로 판도 흔들어</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
+          <t>http://www.srtimes.kr/news/articleView.html?idxno=203841</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:56:00 +0900</t>
+          <t>Sat, 23 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
+        <f>HYPERLINK("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg", IMAGE("https://cdn.srtimes.kr/news/thumbnail/202605/203841_208414_2450_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1857,21 +1856,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
+          <t>'현대重 단골고객' 필리핀 해군 노리는 日…'방산 한일전' 가능성</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026051917503113175</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 08:20:00 +0900</t>
+          <t>Tue, 19 May 2026 17:56:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/Nw8mfrT9bU6eiCw6/image/20260519_175046//1dd15-cc27a-8da96-e20f80.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1881,21 +1880,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
+          <t>한화, KAI 경영참여 공식화...찬반 의견은 엇갈려</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001027882?sid=101</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 15:46:00 +0900</t>
+          <t>Tue, 12 May 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/05/12/0001027882_001_20260512082008012.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1905,21 +1904,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
+          <t>드론 위협 관리하는 미·중…비행규제만 하는 한국</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1300486&amp;inflow=N</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:54:00 +0900</t>
+          <t>Mon, 11 May 2026 15:46:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556", IMAGE("https://image.newstomato.com/newsimg/2026/5/11/1300486/attach.jpg?v=202605111556"))</f>
         <v/>
       </c>
     </row>
@@ -1929,21 +1928,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
+          <t>한화, 체급 키워 방산 ‘글로벌 톱10’ 노린다</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002641645?sid=101</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 07:30:00 +0900</t>
+          <t>Mon, 11 May 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/11/0002641645_001_20260511115413820.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1953,21 +1952,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
+          <t>한화 '경영참여'에 불붙는 'KAI 인수설'…&amp;quot;스페이스X냐 독과점이냐&amp;quot;</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008935178?sid=101</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sat, 09 May 2026 07:30:00 +0900</t>
+          <t>Sun, 10 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/10/0008935178_001_20260510073018254.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1977,21 +1976,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
+          <t>방산 빅딜설 중심에 선 한화…“독점 논쟁 소모적, 체급 키워 세계 무대...</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002640984?sid=101</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+          <t>Sat, 09 May 2026 07:30:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/05/09/0002640984_001_20260509073014857.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2001,23 +2000,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
+          <t>[초점] 한화 &amp;quot;통합 방산기업&amp;quot; 야심에…KAI 내부 강한 반발 왜</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
+          <t>http://www.newswatch.kr/news/articleView.html?idxno=79614</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 07 May 2026 16:58:00 +0900</t>
+        </is>
+      </c>
+      <c r="E66">
+        <f>HYPERLINK("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg", IMAGE("https://cdn.newswatch.kr/news/thumbnail/202605/79614_85479_4430_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -2026,22 +2024,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
+          <t>일본 ‘살상무기 수출’ 60년 빗장 해제… K-해양방산 ‘진검승부’ 예...</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
+          <t>https://www.kukinews.com/article/view/kuk202605060160</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 15:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E67">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
-        <v/>
+          <t>Thu, 07 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -2050,21 +2049,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
+          <t>'한국판 BAE' 현실화하나…한화가 쏘아올린 통합 방산회사 출범 신호탄</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
+          <t>https://news.mtn.co.kr/news-detail/2026050614582776801</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 11:30:00 +0900</t>
+          <t>Wed, 06 May 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/05/vYdnpxl68UO40qgc/image/20260506_145802//202605061457JeBrDw5b_05.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2074,21 +2073,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
+          <t>미 조선 협력 본격화…기자재 '원산지 입증'이 새 변수</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1369861</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 06:00:00 +0900</t>
+          <t>Tue, 05 May 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202605/1369861_1156625_5843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2098,21 +2097,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
+          <t>얼음 해쳐 '북극 항로' 뚫는 쇄빙선…'K-방산'에도 기회 요인?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008923272?sid=100</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
+          <t>Sat, 02 May 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/05/02/0008923272_001_20260502060027545.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2122,21 +2121,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>“한·일 함정 분야 경쟁 가능성”</t>
+          <t>[K방산, 미래 조준]③현대무기 대형화 불가피…韓방산 '설계'에 달렸다</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005757193?sid=101</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
+          <t>Thu, 30 Apr 2026 11:24:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/04/30/0005757193_001_20260430134429328.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2146,21 +2145,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
+          <t>“한·일 함정 분야 경쟁 가능성”</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002636450?sid=101</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+          <t>Tue, 28 Apr 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2170,21 +2169,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
+          <t>'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2194,21 +2193,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
+          <t>전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2218,21 +2217,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
+          <t>전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2242,21 +2241,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
+          <t>15조 美 해군 훈련기 사업, 결국 '미국산 규정'에 막혔다</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423678</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423678_1257282_447_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2266,21 +2265,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
+          <t>日 살상무기 수출 해제에 K방산 위협?…“함정 분야는 경쟁 가능성” [...</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002635127?sid=101</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
+          <t>Sat, 25 Apr 2026 07:01:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/25/0002635127_001_20260425070117077.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2290,21 +2289,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
+          <t>&amp;quot;쪼개 팔면 경쟁력 상실&amp;quot; KAI 분할매각론, 현실성·실익 의문</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1367119</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+          <t>Thu, 23 Apr 2026 14:26:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202604/1367119_1153735_1415_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2314,23 +2313,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
+          <t>트럼프 'NATO' 탈퇴 위협···유럽 자력화 가속에 'K방산' 역할 커지나</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2420829</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 21 Apr 2026 08:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E79">
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2420829_1254079_189_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -2339,22 +2337,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
+          <t>한화·삼성, 美 해군 ‘혈관’ 설계한다…NGLS 수주로 마스가 본게임 ‘...</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
+          <t>https://www.kukinews.com/article/view/kuk202604200181</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E80">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
-        <v/>
+          <t>Tue, 21 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -2363,21 +2362,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
+          <t>K조선, 미 해군 MRO 잇따라 수주…마스가 협력 ‘가속’</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1298412&amp;inflow=N</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
+          <t>Mon, 20 Apr 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549", IMAGE("https://image.newstomato.com/newsimg/2026/4/20/1298412/attach.jpg?v=202604211549"))</f>
         <v/>
       </c>
     </row>
@@ -2387,21 +2386,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
+          <t>갈 길 먼 K드론...부품·소재 자체 공급망? K표준화부터</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104881?sid=101</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
+          <t>Fri, 17 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/17/0000104881_001_20260417210112266.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2411,21 +2410,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
+          <t>‘K드론’ 소프트웨어는 자립 가능, 그러나…</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2575581</t>
+          <t>https://n.news.naver.com/mnews/article/024/0000104851?sid=101</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
+          <t>Thu, 16 Apr 2026 21:01:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/024/2026/04/16/0000104851_001_20260416210109576.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2435,21 +2434,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
+          <t>“한국형 팔란티어 나오려면” 지재권·전력화 보장이 관건 [K-방산, 그...</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
+          <t>https://www.etoday.co.kr/news/view/2575581</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 16 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260415162002_2322127_913_401.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2483,21 +2482,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
+          <t>K-방산 강국 도약, &amp;quot;국방 첨단 복합소재 공급망 내재화해야&amp;quot;</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797541</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+          <t>Tue, 14 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797541_185388_1449_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2507,23 +2506,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
+          <t>“K-방산 강국 도약 위해 첨단 복합소재 공급망 자립 최우선 과제”</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417816?sid=102</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 14 Apr 2026 17:07:00 +0900</t>
+        </is>
+      </c>
+      <c r="E87">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417816_001_20260414170712500.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="88">
@@ -2532,23 +2530,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
+          <t>한화의 방산 퍼즐 맞추기…KAI 지분 확보·풍산 인수 무산 속 전략은</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>http://amenews.kr/news/view.php?idx=66331</t>
+          <t>https://www.smarttoday.co.kr/ko-kr/articles/106484</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 14 Apr 2026 16:11:00 +0900</t>
+        </is>
+      </c>
+      <c r="E88">
+        <f>HYPERLINK("https://cdn.www.smarttoday.co.kr/w1200/q100/f_jpg/article-images/2026-04-14/667462e6-dfdb-41d4-8ffd-4d53a6db22b0.png", IMAGE("https://cdn.www.smarttoday.co.kr/w1200/q100/f_jpg/article-images/2026-04-14/667462e6-dfdb-41d4-8ffd-4d53a6db22b0.png"))</f>
+        <v/>
       </c>
     </row>
     <row r="89">
@@ -2557,21 +2554,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
+          <t>“K-방산 경쟁력 좌우 첨단복합소재 내재화 가속 시급”</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
+          <t>http://amenews.kr/news/view.php?idx=66331</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
+          <t>Tue, 14 Apr 2026 15:54:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg", IMAGE("http://amenews.kr/data/cheditor4/2604/3554368046_Jb5WKZYk_001.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2581,21 +2578,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
+          <t>첨단 복합소재 공급망 자립 K-방산 강국 도약 최우선 과제</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
+          <t>https://n.news.naver.com/mnews/article/119/0003080479?sid=101</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
+          <t>Tue, 14 Apr 2026 14:33:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/119/2026/04/14/0003080479_001_20260414143308903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2605,21 +2602,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
+          <t>걸프국, 천궁Ⅱ 맹활약에 방공전력 '脫美' 가속</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=832512</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
+          <t>Mon, 13 Apr 2026 17:22:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/832512_841252_248_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2629,21 +2626,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
+          <t>대한항공, '무인기 시대' 게임체인저 노린다</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=126464</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202604/126464_110528_1132_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2653,21 +2650,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
+          <t>한화, 풍산 탄약사업부 인수...득과 실은?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=831575</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+          <t>Thu, 09 Apr 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/831575_839875_1833_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2677,23 +2674,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
+          <t>한화에어로, 풍산 탄약사업부 인수 추진⋯포·탄 패키지 전략</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020040?sid=101</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 06 Apr 2026 18:25:00 +0900</t>
+        </is>
+      </c>
+      <c r="E94">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/06/0001020040_001_20260406182512259.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -2702,22 +2698,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
+          <t>한화에어로 풍산 탄약사업 매각 '단독 입찰', 성사는 정부와 풍산 소액...</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2573034</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=435054</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
-        </is>
-      </c>
-      <c r="E95">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
-        <v/>
+          <t>Mon, 06 Apr 2026 16:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -2726,21 +2723,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
+          <t>한화, ‘포·탄’ 시너지에 풍산 탄약 품나…방산 생태계 독주 본격화</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
+          <t>https://www.etoday.co.kr/news/view/2573034</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
+          <t>Mon, 06 Apr 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260406161152_2318138_1199_621.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2750,23 +2747,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
+          <t>'천궁-Ⅱ', 중동서 실전 검증...美 독점 구조 바뀌나</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=830334</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 06 Apr 2026 06:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E97">
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202604/830334_837980_2628_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="98">
@@ -2775,22 +2771,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
+          <t>KF-21 날았지만 KAI는 ‘구조 시험대’…민영화 불씨 재점화</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
+          <t>https://www.kukinews.com/article/view/kuk202604020177</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E98">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
-        <v/>
+          <t>Fri, 03 Apr 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -2799,21 +2796,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
+          <t>佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260401154708093</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2823,21 +2820,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
+          <t>커지는 방산시장, 높아지는 장벽…&amp;quot;현지화 없인 수출 없다&amp;quot;</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
+          <t>https://www.ajunews.com/view/20260401154708093</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
+          <t>Thu, 02 Apr 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg", IMAGE("https://image.ajunews.com/content/image/2026/04/01/20260401162724635722.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2847,21 +2844,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
+          <t>[단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2571395</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2871,21 +2868,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
+          <t>방산 스타트업 키우는 정부…현장은 생태계·제도 개선 주문[K-방산, 안...</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
+          <t>https://www.etoday.co.kr/news/view/2571395</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg", IMAGE("https://img.etoday.co.kr/pto_db/2026/04/20260401171434_2316308_1200_400.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2895,21 +2892,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
+          <t>KF-21 잡음에도 한·인니 방산 협력 강화…&amp;quot;K-방산 거점 국가&amp;quot;</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005338374?sid=100</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
+          <t>Wed, 01 Apr 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/04/01/0005338374_001_20260401160617420.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2919,21 +2916,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
+          <t>인도네시아 대통령 방한…KF-21 협력 재정비 본격화</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1360208</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
+          <t>Tue, 31 Mar 2026 15:04:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1360208_1146405_5919_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2943,21 +2940,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
+          <t>[기획]K-방산 내홍에 사라지는 골든타임…&amp;quot;출혈 경쟁 멈춰야&amp;quot;</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1359223</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
+          <t>Sun, 29 Mar 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202603/1359223_1145375_5310_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2967,21 +2964,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
+          <t>&amp;quot;경쟁사에 영업비밀 왜 넘기냐&amp;quot;…7.8조 KDDX 사업, 또 공정성 논란</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003512325?sid=101</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
+          <t>Sun, 29 Mar 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/29/0003512325_001_20260330110812946.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2991,21 +2988,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>기본설계(기밀포함?) 공개당한 HD현대…방사청은 &amp;quot;이래야 공정&amp;quot;</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260326500334</t>
+          <t>https://news.mtn.co.kr/news-detail/2026032716375252491</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
+          <t>Fri, 27 Mar 2026 17:48:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/03/Yx7psR3iSksCmo4M/image/20260327_172518//8455-1774599878914_07.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3488,10 +3485,9 @@
           <t>Thu, 19 Feb 2026 15:20:00 +0900</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+      <c r="E127">
+        <f>HYPERLINK("https://cdn.www.smarttoday.co.kr/w1200/q100/f_jpg/article-images/2026-02-19/d68827cf-ea01-4a94-9a56-ea2ac38d4e88.png", IMAGE("https://cdn.www.smarttoday.co.kr/w1200/q100/f_jpg/article-images/2026-02-19/d68827cf-ea01-4a94-9a56-ea2ac38d4e88.png"))</f>
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -3573,21 +3569,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>“AI 판 뒤집히면 민주주의 붕괴”…中에 쫓기는 美 ‘섬뜩 경고’ [팩...</t>
+          <t>경남정보대, 간호학과 취업박람회·국방산업학과 특강 잇달아...'지역 맞...</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003527926?sid=105</t>
+          <t>https://www.ajunews.com/view/20260604140251194</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Thu, 04 Jun 2026 06:00:00 +0900</t>
+          <t>Thu, 04 Jun 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/06/04/0003527926_001_20260604060112525.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/06/04/0003527926_001_20260604060112525.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/06/04/20260604140756601033.jpg", IMAGE("https://image.ajunews.com/content/image/2026/06/04/20260604140756601033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3597,21 +3593,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[6·3지선] 권익현, 부안군수 3선 성공…&amp;quot;하나된 대통합의 부안 만들겠다...</t>
+          <t>[부산ㆍ경남 대학 브리핑 모음(6월4일)] 국립창원대, ‘TUG Campus 유·무인...</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008983941?sid=162</t>
+          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202606031021265380946</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Thu, 04 Jun 2026 03:00:00 +0900</t>
+          <t>Thu, 04 Jun 2026 10:02:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/04/0008983941_001_20260604030132821.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/04/0008983941_001_20260604030132821.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/06/03/202606031021265380946-2-669126.JPG", IMAGE("https://image.dnews.co.kr/photo/photo/2026/06/03/202606031021265380946-2-669126.JPG"))</f>
         <v/>
       </c>
     </row>
@@ -3621,21 +3617,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>15개월 시정공백 끝낼 창원특례시 시장후보 4인 공약</t>
+          <t>“AI 판 뒤집히면 민주주의 붕괴”…中에 쫓기는 美 ‘섬뜩 경고’ [팩...</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://www.newsgn.com/news/articleView.html?idxno=554981</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003527926?sid=105</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mon, 01 Jun 2026 18:24:00 +0900</t>
+          <t>Thu, 04 Jun 2026 06:00:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://cdn.newsgn.com/news/thumbnail/202606/554981_361763_2345_v150.jpg", IMAGE("https://cdn.newsgn.com/news/thumbnail/202606/554981_361763_2345_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/06/04/0003527926_001_20260604060112525.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/06/04/0003527926_001_20260604060112525.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3645,21 +3641,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>동양대, Yes-UP DYU 취창업전문가 특강 운영</t>
+          <t>[6·3지선] 권익현, 부안군수 3선 성공…&amp;quot;하나된 대통합의 부안 만들겠다...</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://www.kgnews.co.kr/news/article.html?no=898019</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008983941?sid=162</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Sun, 31 May 2026 13:42:00 +0900</t>
+          <t>Thu, 04 Jun 2026 03:00:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://www.kgnews.co.kr/data/photos/20260522/art_17801971535159_6edc3a.jpg", IMAGE("https://www.kgnews.co.kr/data/photos/20260522/art_17801971535159_6edc3a.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/04/0008983941_001_20260604030132821.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/04/0008983941_001_20260604030132821.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3669,21 +3665,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>동양대 군사학과, 방위산업·국방 R&amp;amp;D 진로 특강 개최</t>
+          <t>“K-방산 미래 인재 키운다”… 경남정보대, 방산 전문가 초청 특강</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://www.gukjenews.com/news/articleView.html?idxno=3595705</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005771069?sid=102</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 18:48:00 +0900</t>
+          <t>Tue, 02 Jun 2026 15:02:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202605/3595705_3753692_4549_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202605/3595705_3753692_4549_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/06/02/0005771069_001_20260602150313293.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/06/02/0005771069_001_20260602150313293.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3693,21 +3689,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>K-핵잠이 던진 새판…HD현대·한화 '협력과 경쟁' 딜레마</t>
+          <t>[부산교육종합] 동의과학대·경남정보대, 각종 수상 및 특강 개최 눈길</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=127309</t>
+          <t>https://www.g-enews.com/view.php?ud=20260602144105335537f21df127_1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 14:26:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:52:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202605/127309_112204_2951_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202605/127309_112204_2951_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202606021442280788837f21df12711222312362.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202606021442280788837f21df12711222312362.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3717,21 +3713,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Creating a business-friendly policy ecosystem is key to Korea’s manufac...</t>
+          <t>부울경 방산 인재 육성 본격화.. 경남정보대, 특강 화제</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/640/0000089168?sid=110</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=842079</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 10:00:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:44:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/640/2026/05/29/0000089168_001_20260529100110885.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/640/2026/05/29/0000089168_001_20260529100110885.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202606/842079_855400_2824_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202606/842079_855400_2824_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3741,21 +3737,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>[김동원의 이코노믹스] 기업 친화적 정책 생태계 만들어야 한국 제조업...</t>
+          <t>15개월 시정공백 끝낼 창원특례시 시장후보 4인 공약</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003526556?sid=110</t>
+          <t>https://www.newsgn.com/news/articleView.html?idxno=554981</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 00:14:00 +0900</t>
+          <t>Mon, 01 Jun 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/05/29/0003526556_001_20260529053237448.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/05/29/0003526556_001_20260529053237448.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsgn.com/news/thumbnail/202606/554981_361763_2345_v150.jpg", IMAGE("https://cdn.newsgn.com/news/thumbnail/202606/554981_361763_2345_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3765,21 +3761,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>기업이 캠퍼스로 왔다···전북대·탈레스코리아 '산학협력'에 속도</t>
+          <t>[부산ㆍ경남 대학 브리핑 모음(6월1일)] 동의대 K-뷰티학과, 베트남 인트...</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2433457</t>
+          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202605310842445790568</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 15:54:00 +0900</t>
+          <t>Mon, 01 Jun 2026 08:02:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2433457_1268751_5344_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2433457_1268751_5344_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/05/31/202605310842445790568-2-668491.jpg", IMAGE("https://image.dnews.co.kr/photo/photo/2026/05/31/202605310842445790568-2-668491.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3789,21 +3785,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>[정책의 맥]산업 新르네상스, 기업과 함께 싸워줄 공학교육 전환기</t>
+          <t>동양대, Yes-UP DYU 취창업전문가 특강 운영</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005768122?sid=110</t>
+          <t>https://www.kgnews.co.kr/news/article.html?no=898019</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Wed, 27 May 2026 09:27:00 +0900</t>
+          <t>Sun, 31 May 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/05/27/0005768122_001_20260527151111337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/05/27/0005768122_001_20260527151111337.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.kgnews.co.kr/data/photos/20260522/art_17801971535159_6edc3a.jpg", IMAGE("https://www.kgnews.co.kr/data/photos/20260522/art_17801971535159_6edc3a.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3813,21 +3809,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>전북대, ‘학부생부터 글로벌 방산기업과 연결’…K-방산 인재양성 새 ...</t>
+          <t>동양대 군사학과, 방위산업·국방 R&amp;amp;D 진로 특강 개최</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260526500712</t>
+          <t>https://www.gukjenews.com/news/articleView.html?idxno=3595705</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 14:42:00 +0900</t>
+          <t>Fri, 29 May 2026 18:48:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/05/26/.cache/512/20260526500704.jpg?v=20260604180646", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/05/26/.cache/512/20260526500704.jpg?v=20260604180646"))</f>
+        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202605/3595705_3753692_4549_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202605/3595705_3753692_4549_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3837,21 +3833,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>전북대-탈레스코리아, 글로벌 방산·우주 인재양성 협력 '속도'</t>
+          <t>K-핵잠이 던진 새판…HD현대·한화 '협력과 경쟁' 딜레마</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003431295?sid=102</t>
+          <t>https://www.ntoday.co.kr/news/articleView.html?idxno=127309</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 14:37:00 +0900</t>
+          <t>Fri, 29 May 2026 14:26:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/26/0003431295_001_20260526143710089.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/26/0003431295_001_20260526143710089.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.ntoday.co.kr/news/thumbnail/202605/127309_112204_2951_v150.jpg", IMAGE("https://cdn.ntoday.co.kr/news/thumbnail/202605/127309_112204_2951_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3861,21 +3857,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>전북대·탈레스코리아 &amp;quot;방산·우주 인재 양성 협력 확대&amp;quot;</t>
+          <t>Creating a business-friendly policy ecosystem is key to Korea’s manufac...</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013967151?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/640/0000089168?sid=110</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 11:38:00 +0900</t>
+          <t>Fri, 29 May 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/05/26/NISI20260526_0002144874_web_20260526113009_20260526113916721.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/05/26/NISI20260526_0002144874_web_20260526113009_20260526113916721.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/640/2026/05/29/0000089168_001_20260529100110885.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/640/2026/05/29/0000089168_001_20260529100110885.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3885,21 +3881,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[윤은기의 X경영(80)] 초가속 시대, '시간 압축'이 승패를 가른다</t>
+          <t>[김동원의 이코노믹스] 기업 친화적 정책 생태계 만들어야 한국 제조업...</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=203091</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003526556?sid=110</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Tue, 26 May 2026 09:50:00 +0900</t>
+          <t>Fri, 29 May 2026 00:14:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202605/203091_470025_4822_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202605/203091_470025_4822_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/05/29/0003526556_001_20260529053237448.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/05/29/0003526556_001_20260529053237448.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3909,21 +3905,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>“증시만 호황인 건 비정상, 실물경제도 같이 살아야 선진국형”</t>
+          <t>[부산ㆍ경남 대학 브리핑 모음(5월28일)] 동서대 디자인대학, 미국 패션...</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/262/0000019395?sid=101</t>
+          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202605271640520080204</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Mon, 25 May 2026 07:01:00 +0900</t>
+          <t>Thu, 28 May 2026 08:02:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/05/25/0000019395_001_20260525070110630.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/05/25/0000019395_001_20260525070110630.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/05/27/202605271640520080204-2-667920.jpg", IMAGE("https://image.dnews.co.kr/photo/photo/2026/05/27/202605271640520080204-2-667920.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3933,21 +3929,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>“한국 2000억 달러 흑자, 미국이 그냥 둘까”</t>
+          <t>기업이 캠퍼스로 왔다···전북대·탈레스코리아 '산학협력'에 속도</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/353/0000055533?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2433457</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Sat, 23 May 2026 00:54:00 +0900</t>
+          <t>Wed, 27 May 2026 15:54:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/353/2026/05/23/0000055533_001_20260523013423648.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/353/2026/05/23/0000055533_001_20260523013423648.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2433457_1268751_5344_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2433457_1268751_5344_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3957,21 +3953,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>주가 신기루와 반도체 착시 걷어내야 하는 이유</t>
+          <t>[정책의 맥]산업 新르네상스, 기업과 함께 싸워줄 공학교육 전환기</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/036/0000053637?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005768122?sid=110</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Thu, 21 May 2026 18:54:00 +0900</t>
+          <t>Wed, 27 May 2026 09:27:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/036/2026/05/21/0000053637_001_20260601094213980.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/036/2026/05/21/0000053637_001_20260601094213980.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/05/27/0005768122_001_20260527151111337.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/05/27/0005768122_001_20260527151111337.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3981,21 +3977,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>'방산 불모지' 전북, 탄소 입고 다시 뛴다...첨단소재로 판 바꾼 전북 방...</t>
+          <t>'제2회 우주항공의 날' 기념식 27일 사천서 개최</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=440278</t>
+          <t>http://www.gndomin.com/news/articleView.html?idxno=476754</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Thu, 21 May 2026 16:20:00 +0900</t>
+          <t>Tue, 26 May 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E148">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/440278_149320_1654_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/440278_149320_1654_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.gndomin.com/image/logo/snslogo_20240325100844.png", IMAGE("http://www.gndomin.com/image/logo/snslogo_20240325100844.png"))</f>
         <v/>
       </c>
     </row>
@@ -4005,23 +4001,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>[Who Is ?] 박재석 SNT다이내믹스 대표이사 사장</t>
+          <t>전북대, ‘학부생부터 글로벌 방산기업과 연결’…K-방산 인재양성 새 ...</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=438134</t>
+          <t>https://www.viva100.com/article/20260526500712</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Wed, 20 May 2026 07:02:00 +0900</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 26 May 2026 14:42:00 +0900</t>
+        </is>
+      </c>
+      <c r="E149">
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/05/26/.cache/512/20260526500704.jpg?v=20260604181942", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/05/26/.cache/512/20260526500704.jpg?v=20260604181942"))</f>
+        <v/>
       </c>
     </row>
     <row r="150">
@@ -4030,21 +4025,21 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>국립창원대 과학기술원 공약, '신설' 아닌 '전환'이 문제 [6.3 쟁점 점검...</t>
+          <t>전북대-탈레스코리아, 글로벌 방산·우주 인재양성 협력 '속도'</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://www.idomin.com/news/articleView.html?idxno=2006078</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003431295?sid=102</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:46:00 +0900</t>
+          <t>Tue, 26 May 2026 14:37:00 +0900</t>
         </is>
       </c>
       <c r="E150">
-        <f>HYPERLINK("https://cdn.idomin.com/news/photo/202605/2006078_709045_2504.jpg", IMAGE("https://cdn.idomin.com/news/photo/202605/2006078_709045_2504.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/26/0003431295_001_20260526143710089.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/26/0003431295_001_20260526143710089.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4054,21 +4049,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>(박창식의 K-국방)한국 방위 역량, 이제 자기 비하를 멈출 때다</t>
+          <t>전북대·탈레스코리아 &amp;quot;방산·우주 인재 양성 협력 확대&amp;quot;</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1301220&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013967151?sid=102</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 06:02:00 +0900</t>
+          <t>Tue, 26 May 2026 11:38:00 +0900</t>
         </is>
       </c>
       <c r="E151">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/19/1301220/attach.jpg?v=202605181605", IMAGE("https://image.newstomato.com/newsimg/2026/5/19/1301220/attach.jpg?v=202605181605"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/05/26/NISI20260526_0002144874_web_20260526113009_20260526113916721.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/05/26/NISI20260526_0002144874_web_20260526113009_20260526113916721.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4078,21 +4073,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>방위사업청, 美 국방획득대학교와 공동 워크숍 개최… &amp;quot;첨단 획득역량 ...</t>
+          <t>[윤은기의 X경영(80)] 초가속 시대, '시간 압축'이 승패를 가른다</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://www.gukjenews.com/news/articleView.html?idxno=3585775</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=203091</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 03:38:00 +0900</t>
+          <t>Tue, 26 May 2026 09:50:00 +0900</t>
         </is>
       </c>
       <c r="E152">
-        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202605/3585775_3741735_5024_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202605/3585775_3741735_5024_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202605/203091_470025_4822_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202605/203091_470025_4822_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4102,21 +4097,21 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>강원대 첨단군사과학기술연구소 ‘국방사업관리사 자격증 과정 운영대...</t>
+          <t>“증시만 호황인 건 비정상, 실물경제도 같이 살아야 선진국형”</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441873?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/262/0000019395?sid=101</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Mon, 18 May 2026 18:36:00 +0900</t>
+          <t>Mon, 25 May 2026 07:01:00 +0900</t>
         </is>
       </c>
       <c r="E153">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/18/0002441873_001_20260518183616443.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/18/0002441873_001_20260518183616443.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/05/25/0000019395_001_20260525070110630.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/05/25/0000019395_001_20260525070110630.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4126,23 +4121,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>방사청, 미 국방획득대학교와 실무급 워크숍</t>
+          <t>“한국 2000억 달러 흑자, 미국이 그냥 둘까”</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260519/1/ATCE_CTGR_0010020000/view.do</t>
+          <t>https://n.news.naver.com/mnews/article/353/0000055533?sid=102</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Mon, 18 May 2026 16:18:00 +0900</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sat, 23 May 2026 00:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E154">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/353/2026/05/23/0000055533_001_20260523013423648.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/353/2026/05/23/0000055533_001_20260523013423648.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="155">
@@ -4151,21 +4145,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>인·태 시대의 '평화 거점' 한국, 갈등의 파고를 넘는 가교가 될 것인가...</t>
+          <t>주가 신기루와 반도체 착시 걷어내야 하는 이유</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>http://www.tongilnews.com/news/articleView.html?idxno=216521</t>
+          <t>https://n.news.naver.com/mnews/article/036/0000053637?sid=101</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Mon, 18 May 2026 14:06:00 +0900</t>
+          <t>Thu, 21 May 2026 18:54:00 +0900</t>
         </is>
       </c>
       <c r="E155">
-        <f>HYPERLINK("https://cdn.tongilnews.com/news/thumbnail/202605/216521_115974_247_v150.jpg", IMAGE("https://cdn.tongilnews.com/news/thumbnail/202605/216521_115974_247_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/036/2026/05/21/0000053637_001_20260601094213980.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/036/2026/05/21/0000053637_001_20260601094213980.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4175,21 +4169,21 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>전북대학교, 방사청 '국방사업관리사' 교육기관 2년 연속 선정…방산 전...</t>
+          <t>'방산 불모지' 전북, 탄소 입고 다시 뛴다...첨단소재로 판 바꾼 전북 방...</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=202591</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=440278</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Mon, 18 May 2026 12:36:00 +0900</t>
+          <t>Thu, 21 May 2026 16:20:00 +0900</t>
         </is>
       </c>
       <c r="E156">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202605/202591_469341_365_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202605/202591_469341_365_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/440278_149320_1654_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/440278_149320_1654_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4199,21 +4193,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>방사청, 美 국방획득대학과 '애자일 무기획득' 5일 합숙 토론</t>
+          <t>사천서 우주 체험하고, 김해서 별 보고</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://www.newspim.com/news/view/20260518000484</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003721222?sid=102</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Mon, 18 May 2026 10:56:00 +0900</t>
+          <t>Thu, 21 May 2026 04:33:00 +0900</t>
         </is>
       </c>
       <c r="E157">
-        <f>HYPERLINK("https://img.newspim.com/news/2026/05/18/2605181053393780_t1.jpg", IMAGE("https://img.newspim.com/news/2026/05/18/2605181053393780_t1.jpg"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4223,21 +4217,21 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>방사청, 美 국방획득대와 공동 워크숍…획득인력 양성체계 공유</t>
+          <t>제2회 우주항공의 날, 경남 곳곳서 우주항공 체험 행사 풍성</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005359123?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003720980?sid=102</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Mon, 18 May 2026 10:27:00 +0900</t>
+          <t>Wed, 20 May 2026 10:19:00 +0900</t>
         </is>
       </c>
       <c r="E158">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/05/18/0005359123_001_20260518102817596.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/05/18/0005359123_001_20260518102817596.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/05/20/0003720980_001_20260520101916617.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/05/20/0003720980_001_20260520101916617.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4247,21 +4241,21 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>방사청·美 국방획득대, 韓美 국방획득인력 양성체계 및 첨단 획득제도...</t>
+          <t>경남도, 우주항공의 날·주간 맞아 도내 전역서 기념행사 다채</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002791828?sid=100</t>
+          <t>https://www.cnbnews.com/news/articleView.html?idxno=1002192</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Mon, 18 May 2026 09:03:00 +0900</t>
+          <t>Wed, 20 May 2026 10:04:00 +0900</t>
         </is>
       </c>
       <c r="E159">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/05/18/0002791828_001_20260518090308259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/05/18/0002791828_001_20260518090308259.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.cnbnews.com/news/photo/202605/1002192_502105_1779237915.jpg", IMAGE("https://cdn.cnbnews.com/news/photo/202605/1002192_502105_1779237915.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4271,21 +4265,21 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>[기술간첩] ⑤ '23조 원' 소는 잃었어도 외양간은 계속 고쳐야…</t>
+          <t>'우주항공 주간' 경남 곳곳서 정책·산업·문화 아우르는 연계행사 풍성</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://www.bizhankook.com/bk/article/32273</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003429368?sid=102</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 16:16:00 +0900</t>
+          <t>Wed, 20 May 2026 08:59:00 +0900</t>
         </is>
       </c>
       <c r="E160">
-        <f>HYPERLINK("https://www.bizhankook.com/upload/bk/article/202605/thumb/32273-78198-sample.jpg", IMAGE("https://www.bizhankook.com/upload/bk/article/202605/thumb/32273-78198-sample.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/05/20/0003429368_001_20260520085910062.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/05/20/0003429368_001_20260520085910062.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4295,22 +4289,23 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>글로벌 AI-방산-반도체 인재 양성… 매머드급 국가거점국립대로 새 도약</t>
+          <t>[Who Is ?] 박재석 SNT다이내믹스 대표이사 사장</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003719813?sid=102</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=438134</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 04:34:00 +0900</t>
-        </is>
-      </c>
-      <c r="E161">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/05/15/0003719813_001_20260515043415656.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/05/15/0003719813_001_20260515043415656.jpg?type=w800"))</f>
-        <v/>
+          <t>Wed, 20 May 2026 07:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -4319,21 +4314,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5월 14일 베이징 회담은 결승전이 아니다</t>
+          <t>'우주항공의 날' 경남 곳곳 행사 다채</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/047/0002515553?sid=104</t>
+          <t>http://www.gndomin.com/news/articleView.html?idxno=476080</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 17:31:00 +0900</t>
+          <t>Tue, 19 May 2026 18:22:00 +0900</t>
         </is>
       </c>
       <c r="E162">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/047/2026/05/13/0002515553_001_20260513173110461.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/047/2026/05/13/0002515553_001_20260513173110461.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.gndomin.com/image/logo/snslogo_20240325100844.png", IMAGE("http://www.gndomin.com/image/logo/snslogo_20240325100844.png"))</f>
         <v/>
       </c>
     </row>
@@ -4343,23 +4338,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>[Who Is ?] 손경석 퍼스텍 대표이사 사장</t>
+          <t>국립창원대 과학기술원 공약, '신설' 아닌 '전환'이 문제 [6.3 쟁점 점검...</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=437052</t>
+          <t>https://www.idomin.com/news/articleView.html?idxno=2006078</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 07:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 19 May 2026 17:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E163">
+        <f>HYPERLINK("https://cdn.idomin.com/news/photo/202605/2006078_709045_2504.jpg", IMAGE("https://cdn.idomin.com/news/photo/202605/2006078_709045_2504.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="164">
@@ -4368,21 +4362,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>[인터뷰]김태흠 &amp;quot;대전-충남 통합, 9조원 국세·권한 이양되면 추진&amp;quot;</t>
+          <t>경남도 '제2회 우주항공의 날' 주간 연계 행사 추진</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001142666?sid=162</t>
+          <t>https://www.ulsanpress.net/news/articleView.html?idxno=575488</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 05:21:00 +0900</t>
+          <t>Tue, 19 May 2026 17:26:00 +0900</t>
         </is>
       </c>
       <c r="E164">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/05/12/0001142666_001_20260512072307509.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/05/12/0001142666_001_20260512072307509.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.ulsanpress.net/news/thumbnail/202605/575488_273004_2441_v150.jpg", IMAGE("https://cdn.ulsanpress.net/news/thumbnail/202605/575488_273004_2441_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4392,21 +4386,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>국립창원대, 인도 조선해양 고위급 대표단 방문</t>
+          <t>경남도, '제2회 우주항공의 날' 맞아 정책·산업·문화 아우르는 '우주항...</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>http://www.breaknews.com/1206310</t>
+          <t>https://www.newsgn.com/news/articleView.html?idxno=552950</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 16:38:00 +0900</t>
+          <t>Tue, 19 May 2026 16:26:00 +0900</t>
         </is>
       </c>
       <c r="E165">
-        <f>HYPERLINK("https://www.breaknewsgn.com/imgdata/breaknewsgn_com/202605/2026051150412533.jpg", IMAGE("https://www.breaknewsgn.com/imgdata/breaknewsgn_com/202605/2026051150412533.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsgn.com/news/thumbnail/202605/552950_359588_3749_v150.jpg", IMAGE("https://cdn.newsgn.com/news/thumbnail/202605/552950_359588_3749_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4416,21 +4410,21 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>물가·청년일자리로 쏠린 민심…경기지사 후보들 해법 경쟁</t>
+          <t>경남 전역서 ‘우주항공 주간’ 연계 행사 풍성</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://www.kgnews.co.kr/news/article.html?no=894943</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260519010005201</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 20:00:00 +0900</t>
+          <t>Tue, 19 May 2026 14:22:00 +0900</t>
         </is>
       </c>
       <c r="E166">
-        <f>HYPERLINK("https://www.kgnews.co.kr/data/photos/20260519/art_17784002216015_6d0c30.png", IMAGE("https://www.kgnews.co.kr/data/photos/20260519/art_17784002216015_6d0c30.png"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/05m/20d/2026052001001022300056201.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/05m/20d/2026052001001022300056201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4440,22 +4434,649 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
+          <t>(박창식의 K-국방)한국 방위 역량, 이제 자기 비하를 멈출 때다</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1301220&amp;inflow=N</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 06:02:00 +0900</t>
+        </is>
+      </c>
+      <c r="E167">
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/5/19/1301220/attach.jpg?v=202605181605", IMAGE("https://image.newstomato.com/newsimg/2026/5/19/1301220/attach.jpg?v=202605181605"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>방위사업청, 美 국방획득대학교와 공동 워크숍 개최… &amp;quot;첨단 획득역량 ...</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>https://www.gukjenews.com/news/articleView.html?idxno=3585775</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 03:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E168">
+        <f>HYPERLINK("https://cdn.gukjenews.com/news/thumbnail/202605/3585775_3741735_5024_v150.jpg", IMAGE("https://cdn.gukjenews.com/news/thumbnail/202605/3585775_3741735_5024_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>강원대 첨단군사과학기술연구소 ‘국방사업관리사 자격증 과정 운영대...</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/002/0002441873?sid=102</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 18:36:00 +0900</t>
+        </is>
+      </c>
+      <c r="E169">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/18/0002441873_001_20260518183616443.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/18/0002441873_001_20260518183616443.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>방사청, 미 국방획득대학교와 실무급 워크숍</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260519/1/ATCE_CTGR_0010020000/view.do</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 16:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>인·태 시대의 '평화 거점' 한국, 갈등의 파고를 넘는 가교가 될 것인가...</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>http://www.tongilnews.com/news/articleView.html?idxno=216521</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 14:06:00 +0900</t>
+        </is>
+      </c>
+      <c r="E171">
+        <f>HYPERLINK("https://cdn.tongilnews.com/news/thumbnail/202605/216521_115974_247_v150.jpg", IMAGE("https://cdn.tongilnews.com/news/thumbnail/202605/216521_115974_247_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>전북대학교, 방사청 '국방사업관리사' 교육기관 2년 연속 선정…방산 전...</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=202591</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 12:36:00 +0900</t>
+        </is>
+      </c>
+      <c r="E172">
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202605/202591_469341_365_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202605/202591_469341_365_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>방사청, 美 국방획득대학과 '애자일 무기획득' 5일 합숙 토론</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>https://www.newspim.com/news/view/20260518000484</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 10:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E173">
+        <f>HYPERLINK("https://img.newspim.com/news/2026/05/18/2605181053393780_t1.jpg", IMAGE("https://img.newspim.com/news/2026/05/18/2605181053393780_t1.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>방사청, 美 국방획득대와 공동 워크숍…획득인력 양성체계 공유</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/008/0005359123?sid=100</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 10:27:00 +0900</t>
+        </is>
+      </c>
+      <c r="E174">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/05/18/0005359123_001_20260518102817596.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/05/18/0005359123_001_20260518102817596.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>방사청·美 국방획득대, 韓美 국방획득인력 양성체계 및 첨단 획득제도...</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/021/0002791828?sid=100</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 09:03:00 +0900</t>
+        </is>
+      </c>
+      <c r="E175">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/05/18/0002791828_001_20260518090308259.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/05/18/0002791828_001_20260518090308259.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>[기술간첩] ⑤ '23조 원' 소는 잃었어도 외양간은 계속 고쳐야…</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://www.bizhankook.com/bk/article/32273</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 16:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E176">
+        <f>HYPERLINK("https://www.bizhankook.com/upload/bk/article/202605/thumb/32273-78198-sample.jpg", IMAGE("https://www.bizhankook.com/upload/bk/article/202605/thumb/32273-78198-sample.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>글로벌 AI-방산-반도체 인재 양성… 매머드급 국가거점국립대로 새 도약</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/020/0003719813?sid=102</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 04:34:00 +0900</t>
+        </is>
+      </c>
+      <c r="E177">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/05/15/0003719813_001_20260515043415656.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/05/15/0003719813_001_20260515043415656.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>대진대학교, 개교 34주년 기념식 개최… ‘K-방산·AI 선도대학’ 도약...</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202605141437242740775</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 20:22:00 +0900</t>
+        </is>
+      </c>
+      <c r="E178">
+        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/05/14/202605141437242740775-2-665578.jpg", IMAGE("https://image.dnews.co.kr/photo/photo/2026/05/14/202605141437242740775-2-665578.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>대진대, 개교 34주년…&amp;quot;K-방산·AI 선도대학 도약&amp;quot; 선언</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/666/0000107051?sid=102</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 18:49:00 +0900</t>
+        </is>
+      </c>
+      <c r="E179">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/666/2026/05/14/0000107051_001_20260514184921026.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/666/2026/05/14/0000107051_001_20260514184921026.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>폴리텍대-한화에어로스페이스, 우주항공·방산 인재 양성 협약 체결</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>http://www.lawissue.co.kr/view.php?ud=202605141722574466f4ab64559d_12</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 17:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E180">
+        <f>HYPERLINK("https://cliimage.commutil.kr/lawissue_www/nimg/default_bimg.png?p=003", IMAGE("https://cliimage.commutil.kr/lawissue_www/nimg/default_bimg.png?p=003"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>한화에어로-폴리텍대, 항공우주·방산 기술인재 양성 '맞손'</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/079/0004147018?sid=102</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 17:12:00 +0900</t>
+        </is>
+      </c>
+      <c r="E181">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/079/2026/05/14/0004147018_001_20260514171216898.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/079/2026/05/14/0004147018_001_20260514171216898.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>대진대 개교 34주년 기념식 개최...  'K-방산/AI 선도대학' 도약 선포</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=610088</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 14:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E182">
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202605/610088_523297_2359_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202605/610088_523297_2359_v150.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5월 14일 베이징 회담은 결승전이 아니다</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/047/0002515553?sid=104</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 17:31:00 +0900</t>
+        </is>
+      </c>
+      <c r="E183">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/047/2026/05/13/0002515553_001_20260513173110461.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/047/2026/05/13/0002515553_001_20260513173110461.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>[Who Is ?] 손경석 퍼스텍 대표이사 사장</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=437052</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 07:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>경북도 ‘앵커’ 대학 지원 사업..청년 지역 정착 견인</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/009/0005679052?sid=102</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 18:59:00 +0900</t>
+        </is>
+      </c>
+      <c r="E185">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/009/2026/05/12/0005679052_001_20260512185909544.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/009/2026/05/12/0005679052_001_20260512185909544.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>[부산ㆍ경남 대학 브리핑 모음(5월12일)] 국립창원대 “인도 고위급 대...</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://www.dnews.co.kr/uhtml/view.jsp?idxno=202605111705002220305</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 08:40:00 +0900</t>
+        </is>
+      </c>
+      <c r="E186">
+        <f>HYPERLINK("https://image.dnews.co.kr/photo/photo/2026/05/11/202605111705002220305-2-664832.jpg", IMAGE("https://image.dnews.co.kr/photo/photo/2026/05/11/202605111705002220305-2-664832.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>[인터뷰]김태흠 &amp;quot;대전-충남 통합, 9조원 국세·권한 이양되면 추진&amp;quot;</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/417/0001142666?sid=162</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 05:21:00 +0900</t>
+        </is>
+      </c>
+      <c r="E187">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/05/12/0001142666_001_20260512072307509.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/05/12/0001142666_001_20260512072307509.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>국립창원대, 인도 조선해양 고위급 대표단 방문</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>http://www.breaknews.com/1206310</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 16:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E188">
+        <f>HYPERLINK("https://www.breaknewsgn.com/imgdata/breaknewsgn_com/202605/2026051150412533.jpg", IMAGE("https://www.breaknewsgn.com/imgdata/breaknewsgn_com/202605/2026051150412533.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>물가·청년일자리로 쏠린 민심…경기지사 후보들 해법 경쟁</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>https://www.kgnews.co.kr/news/article.html?no=894943</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Sun, 10 May 2026 20:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E189">
+        <f>HYPERLINK("https://www.kgnews.co.kr/data/photos/20260519/art_17784002216015_6d0c30.png", IMAGE("https://www.kgnews.co.kr/data/photos/20260519/art_17784002216015_6d0c30.png"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>경북도 ‘앵커 사업’ 성과 가시화… 지역대학·기업 상생 모델 주목</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>http://www.breaknews.com/1205573</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 17:16:00 +0900</t>
+        </is>
+      </c>
+      <c r="E190">
+        <f>HYPERLINK("https://dk.breaknews.com/imgdata/dk_breaknews_com/202605/2026050745561906.jpg", IMAGE("https://dk.breaknews.com/imgdata/dk_breaknews_com/202605/2026050745561906.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>지역대학서 키운 인재, 지역기업 취업으로…경북형 청년 정주모델 성과</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>https://www.kyongbuk.co.kr/news/articleView.html?idxno=4072122</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 16:24:00 +0900</t>
+        </is>
+      </c>
+      <c r="E191">
+        <f>HYPERLINK("https://cdn.kyongbuk.co.kr/news/photo/202605/4072122_803539_2151.jpg", IMAGE("https://cdn.kyongbuk.co.kr/news/photo/202605/4072122_803539_2151.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
           <t>'라이즈' 재구조화 '앵커' 체계…진학·취업·정주 선순환</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C192" t="inlineStr">
         <is>
           <t>https://www.hidomin.com/news/articleView.html?idxno=704332</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D192" t="inlineStr">
         <is>
           <t>Thu, 07 May 2026 14:18:00 +0900</t>
         </is>
       </c>
-      <c r="E167">
+      <c r="E192">
         <f>HYPERLINK("https://cdn.hidomin.com/news/photo/202605/704332_404734_0928.jpg", IMAGE("https://cdn.hidomin.com/news/photo/202605/704332_404734_0928.jpg"))</f>
         <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>경북도 ‘앵커’ 사업 성과…청년 정착·기업 경쟁력 동시 강화</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>https://www.kukinews.com/article/view/kuk202605070060</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 11:58:00 +0900</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4469,7 +5090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4626,21 +5247,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[기고] K방산 롱런의 조건 '현지 생산'</t>
+          <t>첨단항공엔진, 지금 시작하지 않으면 골든타임 놓친다 [기고]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/009/0005646852?sid=110</t>
+          <t>https://news.mtn.co.kr/news-detail/2026033015455091764</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:19:00 +0900</t>
+          <t>Mon, 30 Mar 2026 15:52:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/009/2026/03/08/0005646852_001_20260308175312269.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/009/2026/03/08/0005646852_001_20260308175312269.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/30/2026033015455091764_00_861.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4650,21 +5271,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>가성비 전쟁 시대, 한국은 준비됐나 [기고]</t>
+          <t>[기고] K방산 롱런의 조건 '현지 생산'</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026030610261598884</t>
+          <t>https://n.news.naver.com/mnews/article/009/0005646852?sid=110</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fri, 06 Mar 2026 10:46:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E8">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/06/2026030610261598884_00_643.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/06/2026030610261598884_00_643.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/009/2026/03/08/0005646852_001_20260308175312269.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/009/2026/03/08/0005646852_001_20260308175312269.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4674,21 +5295,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>반복되는 방산 폭발사고…위험공정 자동화·원가제도 개혁해야[기고]</t>
+          <t>가성비 전쟁 시대, 한국은 준비됐나 [기고]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026060416345488076</t>
+          <t>https://news.mtn.co.kr/news-detail/2026030610261598884</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thu, 04 Jun 2026 17:06:00 +0900</t>
+          <t>Fri, 06 Mar 2026 10:46:00 +0900</t>
         </is>
       </c>
       <c r="E9">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/06/04/2026060416345488076_00_159.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/06/04/2026060416345488076_00_159.jpg"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/03/06/2026030610261598884_00_643.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/03/06/2026030610261598884_00_643.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4698,21 +5319,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[최기일 칼럼] 軍 방독면 입찰 계약 구조 개선해야</t>
+          <t>반복되는 방산 폭발사고…위험공정 자동화·원가제도 개혁해야[기고]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260518500244</t>
+          <t>https://news.mtn.co.kr/news-detail/2026060416345488076</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 18 May 2026 20:54:00 +0900</t>
+          <t>Thu, 04 Jun 2026 17:06:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/05/18/.cache/512/20260518500243.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/05/18/.cache/512/20260518500243.png"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/06/04/2026060416345488076_00_159.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/06/04/2026060416345488076_00_159.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4722,20 +5343,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>[최기일 칼럼] 軍 방독면 입찰 계약 구조 개선해야</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.news2day.co.kr/article/20260518500244</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 20:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E11">
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/05/18/.cache/512/20260518500243.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/05/18/.cache/512/20260518500243.png"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>미국도 중국도 원하지 않는 최악의 시나리오 [김영근 교수 칼럼]</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>https://www.mediafine.co.kr/news/articleView.html?idxno=78947</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 17:58:00 +0900</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E12">
         <f>HYPERLINK("https://cdn.mediafine.co.kr/news/photo/202605/78947_115306_5142.jpg", IMAGE("https://cdn.mediafine.co.kr/news/photo/202605/78947_115306_5142.jpg"))</f>
         <v/>
       </c>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,21 +462,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>** AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
+          <t>** 전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260326500334</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
         </is>
       </c>
       <c r="E2">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -486,21 +486,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
+          <t>** 전북대, 국방사업관리사 교육기관 2년 연속 선정</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=839163</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
+          <t>Sun, 17 May 2026 07:56:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -510,21 +510,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+          <t>** '방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -534,21 +534,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>** “방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
       <c r="E5">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -558,21 +558,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전북대, 국방사업관리사 교육기관 2년 연속 선정</t>
+          <t>** 전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=839163</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 07:56:00 +0900</t>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202605/839163_851144_5429_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -582,21 +582,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+          <t>** 전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -606,21 +606,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+          <t>** 전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E8">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -630,21 +630,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>** 피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E9">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -654,21 +654,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>** 전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -678,21 +678,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>** 전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E11">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -702,21 +702,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>** 전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E12">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -726,21 +726,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>** 전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
         </is>
       </c>
       <c r="E13">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -750,21 +750,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>** “AI·방산 인재 키운다”…전북대, 71억 ‘첨단인재양성 부트캠프’ 선...</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002430291?sid=102</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Wed, 04 Mar 2026 16:47:00 +0900</t>
         </is>
       </c>
       <c r="E14">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/03/04/0002430291_001_20260304164714692.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -774,21 +774,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>** 전북대, 실무형 방산 AI 전문인력 양성 나선다</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=793790</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Wed, 04 Mar 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E15">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202603/793790_181909_109_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -798,21 +798,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>** 전북대학교, 세계 최고 방산 AI기업 '쉴드 AI'와 전략적 협력 추진</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=194930</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Sun, 18 Jan 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E16">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202601/194930_459178_2040_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>** 전북대, 방산 AI 유니콘 ‘쉴드 AI’와 전략 협력 추진</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>https://www.naeil.com/news/read/574819?ref=naver</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Sat, 17 Jan 2026 15:28:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -846,21 +846,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>** 전북대, 세계 3대 방산 유니콘 '쉴드 AI'와 맞손</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>http://www.gjdream.com/news/articleView.html?idxno=666107</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Thu, 15 Jan 2026 15:14:00 +0900</t>
         </is>
       </c>
       <c r="E18">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png", IMAGE("https://cdn.gjdream.com/news/photo/202601/666107_278726_559.png"))</f>
         <v/>
       </c>
     </row>
@@ -870,21 +870,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>** 전북대, 유니콘 '쉴드 AI'와 협력…피지컬 AI·방산 교육 연계</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013712078?sid=102</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Thu, 15 Jan 2026 10:57:00 +0900</t>
         </is>
       </c>
       <c r="E19">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/01/15/NISI20260115_0002041291_web_20260115105424_20260115105822871.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -894,23 +894,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>** 'AI·MUM-T' 핵심 기술 놓고 머리 맞댔다···전북대-한화시스템 협력 시...</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2423794</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 27 Apr 2026 17:33:00 +0900</t>
+        </is>
+      </c>
+      <c r="E20">
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202604/2423794_1257408_3245_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -919,21 +918,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>** 전북대·한화시스템, 첨단 방산기술 협력 본격화</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013912488?sid=102</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+          <t>Mon, 27 Apr 2026 16:11:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/04/27/NISI20260427_0002121681_web_20260427152739_20260427161245058.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -943,21 +942,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>** 전북대-한화시스템, 첨단 방산기술 협력 본격화…교수진-임원진 기술교...</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003422061?sid=102</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Mon, 27 Apr 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/27/0003422061_001_20260427152412782.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -967,21 +966,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>** 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623635?sid=101</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 02 Apr 2026 11:16:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/02/0002623635_001_20260402224616149.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -991,21 +990,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>** [단독] 佛 방산기업 탈레스, 카이스트·전북대 장학금 지원…K-인재 유치...</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002623210?sid=101</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Wed, 01 Apr 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/016/2026/04/01/0002623210_001_20260402224408711.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1015,21 +1014,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>** AI·드론 시대 맞아 ‘첨단전력 획득절차’ 달라진다</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>https://www.news2day.co.kr/article/20260326500334</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Thu, 26 Mar 2026 21:26:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/03/26/.cache/512/20260326500333.png"))</f>
         <v/>
       </c>
     </row>
@@ -1039,21 +1038,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>** 전북대학교 한재익 교수, 생물다양성 보전 공로로 대통령 표창 수상</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=203632</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Thu, 04 Jun 2026 17:36:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202606/203632_470828_1240_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202606/203632_470828_1240_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1063,21 +1062,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[창